--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -661,7 +661,7 @@
     <t>Estoril Praia</t>
   </si>
   <si>
-    <t>2026-09-12 01:18:18</t>
+    <t>2026-09-12 03:52:16</t>
   </si>
 </sst>
 </file>
@@ -1255,46 +1255,46 @@
         <v>172</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
         <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R2">
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
         <v>1.69</v>
@@ -1303,7 +1303,7 @@
         <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
         <v>1.72</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
@@ -1506,7 +1506,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
         <v>2.72</v>
@@ -1527,10 +1527,10 @@
         <v>1.61</v>
       </c>
       <c r="P3">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Q3">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R3">
         <v>1.13</v>
@@ -1695,7 +1695,7 @@
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU3">
         <v>4.8</v>
@@ -1742,7 +1742,7 @@
         <v>1.28</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
         <v>3.45</v>
@@ -1751,7 +1751,7 @@
         <v>4</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>4.5</v>
@@ -1981,16 +1981,16 @@
         <v>175</v>
       </c>
       <c r="F5">
+        <v>2.7</v>
+      </c>
+      <c r="G5">
+        <v>2.84</v>
+      </c>
+      <c r="H5">
+        <v>2.52</v>
+      </c>
+      <c r="I5">
         <v>2.64</v>
-      </c>
-      <c r="G5">
-        <v>2.76</v>
-      </c>
-      <c r="H5">
-        <v>2.58</v>
-      </c>
-      <c r="I5">
-        <v>2.7</v>
       </c>
       <c r="J5">
         <v>3.85</v>
@@ -2014,31 +2014,31 @@
         <v>2.78</v>
       </c>
       <c r="Q5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S5">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T5">
         <v>1.46</v>
       </c>
       <c r="U5">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W5">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X5">
         <v>50</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z5">
         <v>30</v>
@@ -2062,16 +2062,16 @@
         <v>32</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
         <v>42</v>
       </c>
       <c r="AJ5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK5">
         <v>34</v>
@@ -2080,10 +2080,10 @@
         <v>46</v>
       </c>
       <c r="AM5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO5">
         <v>15.5</v>
@@ -2098,7 +2098,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AT5">
         <v>14</v>
@@ -2125,13 +2125,13 @@
         <v>18</v>
       </c>
       <c r="BB5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE5">
         <v>26</v>
@@ -2226,7 +2226,7 @@
         <v>1.51</v>
       </c>
       <c r="G6">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H6">
         <v>5.1</v>
@@ -2265,16 +2265,16 @@
         <v>2.6</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U6">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V6">
         <v>1.14</v>
       </c>
       <c r="W6">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2331,7 +2331,7 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6">
         <v>1.6</v>
@@ -2465,22 +2465,22 @@
         <v>177</v>
       </c>
       <c r="F7">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="G7">
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="I7">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="J7">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="K7">
-        <v>5.2</v>
+        <v>900</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2489,22 +2489,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
         <v>1.98</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2513,7 +2513,7 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="W7">
         <v>1.01</v>
@@ -2949,16 +2949,16 @@
         <v>179</v>
       </c>
       <c r="F9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G9">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H9">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
         <v>3.7</v>
@@ -3197,7 +3197,7 @@
         <v>1.86</v>
       </c>
       <c r="H10">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
         <v>8.199999999999999</v>
@@ -3206,7 +3206,7 @@
         <v>3.55</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3448,7 +3448,7 @@
         <v>1.01</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q14">
         <v>2.14</v>
@@ -4422,28 +4422,28 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15">
         <v>4.3</v>
       </c>
       <c r="O15">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
         <v>1.81</v>
       </c>
       <c r="R15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S15">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T15">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U15">
         <v>2.02</v>
@@ -4455,34 +4455,34 @@
         <v>1.17</v>
       </c>
       <c r="X15">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y15">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z15">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AA15">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AB15">
+        <v>24</v>
+      </c>
+      <c r="AC15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15">
+        <v>11</v>
+      </c>
+      <c r="AE15">
+        <v>17.5</v>
+      </c>
+      <c r="AF15">
+        <v>70</v>
+      </c>
+      <c r="AG15">
         <v>30</v>
-      </c>
-      <c r="AC15">
-        <v>970</v>
-      </c>
-      <c r="AD15">
-        <v>12</v>
-      </c>
-      <c r="AE15">
-        <v>19.5</v>
-      </c>
-      <c r="AF15">
-        <v>280</v>
-      </c>
-      <c r="AG15">
-        <v>34</v>
       </c>
       <c r="AH15">
         <v>21</v>
@@ -4494,73 +4494,73 @@
         <v>1000</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO15">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AP15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15">
         <v>8.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS15">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT15">
         <v>19</v>
       </c>
       <c r="AU15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW15">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX15">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="AY15">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AZ15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB15">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BC15">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BD15">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE15">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF15">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4658,7 +4658,7 @@
         <v>6.6</v>
       </c>
       <c r="K16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>1.32</v>
@@ -4667,22 +4667,22 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R16">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S16">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T16">
         <v>2.52</v>
@@ -4697,82 +4697,82 @@
         <v>4.8</v>
       </c>
       <c r="X16">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y16">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC16">
+        <v>16.5</v>
+      </c>
+      <c r="AD16">
+        <v>75</v>
+      </c>
+      <c r="AE16">
+        <v>470</v>
+      </c>
+      <c r="AF16">
+        <v>7.4</v>
+      </c>
+      <c r="AG16">
         <v>12.5</v>
       </c>
-      <c r="AC16">
-        <v>65</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>9.6</v>
-      </c>
-      <c r="AG16">
-        <v>25</v>
-      </c>
       <c r="AH16">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AJ16">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AK16">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="AL16">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN16">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AQ16">
         <v>26</v>
       </c>
       <c r="AR16">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS16">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="AT16">
         <v>7.4</v>
       </c>
       <c r="AU16">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AV16">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="AW16">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AX16">
         <v>6.6</v>
@@ -4781,28 +4781,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BA16">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BB16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD16">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="BE16">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BF16">
         <v>4.4</v>
       </c>
       <c r="BG16">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH16">
         <v>4.3</v>
@@ -4888,7 +4888,7 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -4927,10 +4927,10 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U17">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>1.53</v>
       </c>
       <c r="AT17">
-        <v>12</v>
+        <v>1.58</v>
       </c>
       <c r="AU17">
         <v>7</v>
@@ -5402,7 +5402,7 @@
         <v>1.89</v>
       </c>
       <c r="Q19">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5617,16 +5617,16 @@
         <v>3.1</v>
       </c>
       <c r="H20">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="I20">
         <v>3.45</v>
       </c>
       <c r="J20">
-        <v>2.58</v>
+        <v>3.55</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -6095,19 +6095,19 @@
         <v>192</v>
       </c>
       <c r="F22">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="G22">
         <v>1.71</v>
       </c>
       <c r="H22">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
         <v>5.3</v>
@@ -6125,10 +6125,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q22">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -8524,7 +8524,7 @@
         <v>4</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J32">
         <v>3.5</v>
@@ -8760,10 +8760,10 @@
         <v>2.28</v>
       </c>
       <c r="G33">
+        <v>2.88</v>
+      </c>
+      <c r="H33">
         <v>2.84</v>
-      </c>
-      <c r="H33">
-        <v>2.88</v>
       </c>
       <c r="I33">
         <v>3.85</v>
@@ -8999,7 +8999,7 @@
         <v>204</v>
       </c>
       <c r="F34">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="G34">
         <v>1.29</v>
@@ -9008,13 +9008,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I34">
-        <v>880</v>
+        <v>250</v>
       </c>
       <c r="J34">
         <v>5.8</v>
       </c>
       <c r="K34">
-        <v>11</v>
+        <v>880</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9244,16 +9244,16 @@
         <v>2.86</v>
       </c>
       <c r="G35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H35">
         <v>2.62</v>
       </c>
       <c r="I35">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J35">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>3.4</v>
@@ -9271,10 +9271,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q35">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U35">
         <v>1.94</v>
@@ -10475,22 +10475,22 @@
         <v>1.04</v>
       </c>
       <c r="N40">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O40">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P40">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q40">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S40">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T40">
         <v>2.12</v>
@@ -10505,70 +10505,70 @@
         <v>0</v>
       </c>
       <c r="X40">
+        <v>29</v>
+      </c>
+      <c r="Y40">
+        <v>50</v>
+      </c>
+      <c r="Z40">
+        <v>1000</v>
+      </c>
+      <c r="AA40">
+        <v>1000</v>
+      </c>
+      <c r="AB40">
+        <v>10.5</v>
+      </c>
+      <c r="AC40">
+        <v>16</v>
+      </c>
+      <c r="AD40">
+        <v>55</v>
+      </c>
+      <c r="AE40">
+        <v>1000</v>
+      </c>
+      <c r="AF40">
+        <v>8.4</v>
+      </c>
+      <c r="AG40">
+        <v>12</v>
+      </c>
+      <c r="AH40">
+        <v>34</v>
+      </c>
+      <c r="AI40">
+        <v>1000</v>
+      </c>
+      <c r="AJ40">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK40">
+        <v>14.5</v>
+      </c>
+      <c r="AL40">
+        <v>42</v>
+      </c>
+      <c r="AM40">
+        <v>1000</v>
+      </c>
+      <c r="AN40">
+        <v>4.1</v>
+      </c>
+      <c r="AO40">
+        <v>350</v>
+      </c>
+      <c r="AP40">
+        <v>18.5</v>
+      </c>
+      <c r="AQ40">
         <v>38</v>
       </c>
-      <c r="Y40">
-        <v>95</v>
-      </c>
-      <c r="Z40">
-        <v>1000</v>
-      </c>
-      <c r="AA40">
-        <v>1000</v>
-      </c>
-      <c r="AB40">
-        <v>18.5</v>
-      </c>
-      <c r="AC40">
-        <v>970</v>
-      </c>
-      <c r="AD40">
-        <v>200</v>
-      </c>
-      <c r="AE40">
-        <v>1000</v>
-      </c>
-      <c r="AF40">
-        <v>13</v>
-      </c>
-      <c r="AG40">
-        <v>24</v>
-      </c>
-      <c r="AH40">
-        <v>40</v>
-      </c>
-      <c r="AI40">
-        <v>1000</v>
-      </c>
-      <c r="AJ40">
-        <v>15.5</v>
-      </c>
-      <c r="AK40">
-        <v>42</v>
-      </c>
-      <c r="AL40">
-        <v>70</v>
-      </c>
-      <c r="AM40">
-        <v>1000</v>
-      </c>
-      <c r="AN40">
-        <v>4.7</v>
-      </c>
-      <c r="AO40">
-        <v>1000</v>
-      </c>
-      <c r="AP40">
-        <v>20</v>
-      </c>
-      <c r="AQ40">
-        <v>4.9</v>
-      </c>
       <c r="AR40">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AS40">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="AT40">
         <v>9.4</v>
@@ -10577,13 +10577,13 @@
         <v>13.5</v>
       </c>
       <c r="AV40">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="AW40">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AX40">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY40">
         <v>10.5</v>
@@ -10592,25 +10592,25 @@
         <v>21</v>
       </c>
       <c r="BA40">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BB40">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC40">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD40">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BE40">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF40">
         <v>3.8</v>
       </c>
       <c r="BG40">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BH40">
         <v>4.8</v>
@@ -10693,7 +10693,7 @@
         <v>211</v>
       </c>
       <c r="F41">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G41">
         <v>2.44</v>
@@ -10738,7 +10738,7 @@
         <v>1.68</v>
       </c>
       <c r="U41">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>14</v>
       </c>
       <c r="Z41">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA41">
         <v>55</v>
@@ -10762,7 +10762,7 @@
         <v>11.5</v>
       </c>
       <c r="AC41">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD41">
         <v>13</v>
@@ -10795,10 +10795,10 @@
         <v>70</v>
       </c>
       <c r="AN41">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO41">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP41">
         <v>15</v>
@@ -10810,13 +10810,13 @@
         <v>21</v>
       </c>
       <c r="AS41">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT41">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU41">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV41">
         <v>12</v>
@@ -10825,7 +10825,7 @@
         <v>30</v>
       </c>
       <c r="AX41">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY41">
         <v>10.5</v>
@@ -10834,7 +10834,7 @@
         <v>14.5</v>
       </c>
       <c r="BA41">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB41">
         <v>30</v>
@@ -10846,7 +10846,7 @@
         <v>30</v>
       </c>
       <c r="BE41">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF41">
         <v>16</v>
@@ -10935,19 +10935,19 @@
         <v>212</v>
       </c>
       <c r="F42">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G42">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H42">
         <v>3.9</v>
       </c>
       <c r="I42">
+        <v>3.95</v>
+      </c>
+      <c r="J42">
         <v>4.1</v>
-      </c>
-      <c r="J42">
-        <v>4</v>
       </c>
       <c r="K42">
         <v>4.2</v>
@@ -10962,19 +10962,19 @@
         <v>5.3</v>
       </c>
       <c r="O42">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P42">
+        <v>2.52</v>
+      </c>
+      <c r="Q42">
+        <v>1.63</v>
+      </c>
+      <c r="R42">
+        <v>1.58</v>
+      </c>
+      <c r="S42">
         <v>2.44</v>
-      </c>
-      <c r="Q42">
-        <v>1.58</v>
-      </c>
-      <c r="R42">
-        <v>1.59</v>
-      </c>
-      <c r="S42">
-        <v>2.46</v>
       </c>
       <c r="T42">
         <v>1.55</v>
@@ -10983,118 +10983,118 @@
         <v>2.6</v>
       </c>
       <c r="V42">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
         <v>2.02</v>
       </c>
       <c r="X42">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="Y42">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Z42">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AA42">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB42">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="AC42">
+        <v>10</v>
+      </c>
+      <c r="AD42">
+        <v>16.5</v>
+      </c>
+      <c r="AE42">
+        <v>42</v>
+      </c>
+      <c r="AF42">
         <v>15</v>
-      </c>
-      <c r="AD42">
-        <v>60</v>
-      </c>
-      <c r="AE42">
-        <v>90</v>
-      </c>
-      <c r="AF42">
-        <v>42</v>
       </c>
       <c r="AG42">
         <v>10.5</v>
       </c>
       <c r="AH42">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="AI42">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AJ42">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AK42">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AL42">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AM42">
-        <v>670</v>
+        <v>75</v>
       </c>
       <c r="AN42">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="AO42">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AP42">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ42">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR42">
         <v>21</v>
       </c>
       <c r="AS42">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AT42">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU42">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW42">
         <v>23</v>
       </c>
       <c r="AX42">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY42">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA42">
         <v>24</v>
       </c>
       <c r="BB42">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC42">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD42">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BE42">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="BF42">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG42">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH42">
         <v>4.8</v>
@@ -11177,7 +11177,7 @@
         <v>213</v>
       </c>
       <c r="F43">
-        <v>1.49</v>
+        <v>2.28</v>
       </c>
       <c r="G43">
         <v>2.94</v>
@@ -11186,7 +11186,7 @@
         <v>3.15</v>
       </c>
       <c r="I43">
-        <v>36</v>
+        <v>3.9</v>
       </c>
       <c r="J43">
         <v>3.1</v>
@@ -11428,10 +11428,10 @@
         <v>7</v>
       </c>
       <c r="I44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J44">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K44">
         <v>5.7</v>
@@ -11449,7 +11449,7 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q44">
         <v>1.68</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -661,7 +661,7 @@
     <t>Estoril Praia</t>
   </si>
   <si>
-    <t>2026-09-12 03:52:16</t>
+    <t>2026-09-12 06:26:41</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1258,7 @@
         <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H2">
         <v>3.6</v>
@@ -1267,7 +1267,7 @@
         <v>4.5</v>
       </c>
       <c r="J2">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K2">
         <v>3.6</v>
@@ -1306,7 +1306,7 @@
         <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1506,7 +1506,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
         <v>2.72</v>
@@ -1742,7 +1742,7 @@
         <v>1.28</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="H4">
         <v>3.45</v>
@@ -1751,7 +1751,7 @@
         <v>4</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
         <v>4.5</v>
@@ -1781,10 +1781,10 @@
         <v>1.01</v>
       </c>
       <c r="T4">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="U4">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1853,10 +1853,10 @@
         <v>11</v>
       </c>
       <c r="AR4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AS4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AT4">
         <v>8.6</v>
@@ -1868,7 +1868,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AX4">
         <v>9.6</v>
@@ -1880,25 +1880,25 @@
         <v>10</v>
       </c>
       <c r="BA4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BB4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BC4">
         <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BE4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BF4">
         <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BH4">
         <v>4.7</v>
@@ -1981,16 +1981,16 @@
         <v>175</v>
       </c>
       <c r="F5">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G5">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H5">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I5">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J5">
         <v>3.85</v>
@@ -2023,31 +2023,31 @@
         <v>2.3</v>
       </c>
       <c r="T5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U5">
         <v>2.88</v>
       </c>
       <c r="V5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X5">
         <v>50</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA5">
         <v>95</v>
       </c>
       <c r="AB5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
@@ -2056,7 +2056,7 @@
         <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF5">
         <v>32</v>
@@ -2065,10 +2065,10 @@
         <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ5">
         <v>110</v>
@@ -2080,13 +2080,13 @@
         <v>46</v>
       </c>
       <c r="AM5">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP5">
         <v>19.5</v>
@@ -2098,10 +2098,10 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AT5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU5">
         <v>8.4</v>
@@ -2113,10 +2113,10 @@
         <v>16</v>
       </c>
       <c r="AX5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
         <v>11.5</v>
@@ -2125,19 +2125,19 @@
         <v>18</v>
       </c>
       <c r="BB5">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE5">
         <v>26</v>
       </c>
       <c r="BF5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG5">
         <v>11</v>
@@ -2226,7 +2226,7 @@
         <v>1.51</v>
       </c>
       <c r="G6">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H6">
         <v>5.1</v>
@@ -2238,7 +2238,7 @@
         <v>4.5</v>
       </c>
       <c r="K6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L6">
         <v>1.29</v>
@@ -2268,13 +2268,13 @@
         <v>1.79</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V6">
         <v>1.14</v>
       </c>
       <c r="W6">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2331,7 +2331,7 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
         <v>1.6</v>
@@ -2465,22 +2465,22 @@
         <v>177</v>
       </c>
       <c r="F7">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>6.2</v>
       </c>
       <c r="H7">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="I7">
         <v>2.02</v>
       </c>
       <c r="J7">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
-        <v>900</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2495,7 +2495,7 @@
         <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
         <v>1.98</v>
@@ -2516,7 +2516,7 @@
         <v>1.98</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2949,16 +2949,16 @@
         <v>179</v>
       </c>
       <c r="F9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G9">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
         <v>3.7</v>
@@ -3224,7 +3224,7 @@
         <v>2</v>
       </c>
       <c r="Q10">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -4419,31 +4419,31 @@
         <v>4.4</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M15">
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O15">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P15">
         <v>2.18</v>
       </c>
       <c r="Q15">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
         <v>1.43</v>
       </c>
       <c r="S15">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T15">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U15">
         <v>2.02</v>
@@ -4464,7 +4464,7 @@
         <v>12.5</v>
       </c>
       <c r="AA15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB15">
         <v>24</v>
@@ -4482,7 +4482,7 @@
         <v>70</v>
       </c>
       <c r="AG15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH15">
         <v>21</v>
@@ -4545,19 +4545,19 @@
         <v>23</v>
       </c>
       <c r="BB15">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC15">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD15">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE15">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF15">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG15">
         <v>7.2</v>
@@ -4643,46 +4643,46 @@
         <v>186</v>
       </c>
       <c r="F16">
+        <v>1.24</v>
+      </c>
+      <c r="G16">
         <v>1.25</v>
-      </c>
-      <c r="G16">
-        <v>1.26</v>
       </c>
       <c r="H16">
         <v>17.5</v>
       </c>
       <c r="I16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L16">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M16">
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>1.23</v>
       </c>
       <c r="P16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R16">
         <v>1.52</v>
       </c>
       <c r="S16">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="T16">
         <v>2.52</v>
@@ -4694,34 +4694,34 @@
         <v>1.05</v>
       </c>
       <c r="W16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y16">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z16">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD16">
         <v>75</v>
       </c>
       <c r="AE16">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AF16">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG16">
         <v>12.5</v>
@@ -4745,34 +4745,34 @@
         <v>350</v>
       </c>
       <c r="AN16">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AR16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS16">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV16">
         <v>30</v>
       </c>
       <c r="AW16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX16">
         <v>6.6</v>
@@ -4784,25 +4784,25 @@
         <v>36</v>
       </c>
       <c r="BA16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB16">
         <v>7.6</v>
       </c>
       <c r="BC16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD16">
         <v>28</v>
       </c>
       <c r="BE16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF16">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH16">
         <v>4.3</v>
@@ -4888,19 +4888,19 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H17">
         <v>1.5</v>
       </c>
       <c r="I17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4918,7 +4918,7 @@
         <v>2.08</v>
       </c>
       <c r="Q17">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4927,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U17">
         <v>1.92</v>
@@ -5127,28 +5127,28 @@
         <v>188</v>
       </c>
       <c r="F18">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G18">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5160,7 +5160,7 @@
         <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5169,10 +5169,10 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>1000</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH18">
         <v>1000</v>
@@ -5229,7 +5229,7 @@
         <v>1000</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO18">
         <v>1000</v>
@@ -5283,7 +5283,7 @@
         <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG18">
         <v>1.01</v>
@@ -5623,10 +5623,10 @@
         <v>3.45</v>
       </c>
       <c r="J20">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -6095,13 +6095,13 @@
         <v>192</v>
       </c>
       <c r="F22">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G22">
         <v>1.71</v>
       </c>
       <c r="H22">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I22">
         <v>8.4</v>
@@ -8760,10 +8760,10 @@
         <v>2.28</v>
       </c>
       <c r="G33">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H33">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I33">
         <v>3.85</v>
@@ -8787,7 +8787,7 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -8999,22 +8999,22 @@
         <v>204</v>
       </c>
       <c r="F34">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="G34">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="H34">
         <v>9.800000000000001</v>
       </c>
       <c r="I34">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="J34">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="K34">
-        <v>880</v>
+        <v>12</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9241,10 +9241,10 @@
         <v>205</v>
       </c>
       <c r="F35">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G35">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H35">
         <v>2.62</v>
@@ -9313,7 +9313,7 @@
         <v>970</v>
       </c>
       <c r="AD35">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE35">
         <v>1000</v>
@@ -9725,7 +9725,7 @@
         <v>207</v>
       </c>
       <c r="F37">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G37">
         <v>3.6</v>
@@ -9740,7 +9740,7 @@
         <v>3.55</v>
       </c>
       <c r="K37">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9967,13 +9967,13 @@
         <v>208</v>
       </c>
       <c r="F38">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G38">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="H38">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I38">
         <v>11</v>
@@ -9982,7 +9982,7 @@
         <v>4.5</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>209</v>
       </c>
       <c r="F39">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="G39">
         <v>3.4</v>
@@ -10218,13 +10218,13 @@
         <v>2.66</v>
       </c>
       <c r="I39">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="J39">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K39">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10460,7 +10460,7 @@
         <v>14</v>
       </c>
       <c r="I40">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J40">
         <v>6.6</v>
@@ -10475,7 +10475,7 @@
         <v>1.04</v>
       </c>
       <c r="N40">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O40">
         <v>1.18</v>
@@ -10508,7 +10508,7 @@
         <v>29</v>
       </c>
       <c r="Y40">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z40">
         <v>1000</v>
@@ -10547,7 +10547,7 @@
         <v>14.5</v>
       </c>
       <c r="AL40">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM40">
         <v>1000</v>
@@ -10565,10 +10565,10 @@
         <v>38</v>
       </c>
       <c r="AR40">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS40">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT40">
         <v>9.4</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="AW40">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX40">
         <v>7.6</v>
@@ -10601,7 +10601,7 @@
         <v>12.5</v>
       </c>
       <c r="BD40">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BE40">
         <v>12.5</v>
@@ -10610,7 +10610,7 @@
         <v>3.8</v>
       </c>
       <c r="BG40">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH40">
         <v>4.8</v>
@@ -10693,10 +10693,10 @@
         <v>211</v>
       </c>
       <c r="F41">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G41">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H41">
         <v>3.15</v>
@@ -10717,7 +10717,7 @@
         <v>1.06</v>
       </c>
       <c r="N41">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O41">
         <v>1.28</v>
@@ -10750,28 +10750,28 @@
         <v>16.5</v>
       </c>
       <c r="Y41">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z41">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA41">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB41">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC41">
         <v>8</v>
       </c>
       <c r="AD41">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE41">
         <v>36</v>
       </c>
       <c r="AF41">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG41">
         <v>11</v>
@@ -10780,7 +10780,7 @@
         <v>15.5</v>
       </c>
       <c r="AI41">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ41">
         <v>34</v>
@@ -10795,10 +10795,10 @@
         <v>70</v>
       </c>
       <c r="AN41">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO41">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP41">
         <v>15</v>
@@ -10813,19 +10813,19 @@
         <v>48</v>
       </c>
       <c r="AT41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU41">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV41">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW41">
         <v>30</v>
       </c>
       <c r="AX41">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY41">
         <v>10.5</v>
@@ -10846,13 +10846,13 @@
         <v>30</v>
       </c>
       <c r="BE41">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF41">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH41">
         <v>4.1</v>
@@ -10953,31 +10953,31 @@
         <v>4.2</v>
       </c>
       <c r="L42">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M42">
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O42">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P42">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q42">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R42">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S42">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T42">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U42">
         <v>2.6</v>
@@ -10989,109 +10989,109 @@
         <v>2.02</v>
       </c>
       <c r="X42">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Y42">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Z42">
+        <v>55</v>
+      </c>
+      <c r="AA42">
+        <v>1000</v>
+      </c>
+      <c r="AB42">
         <v>34</v>
       </c>
-      <c r="AA42">
+      <c r="AC42">
+        <v>15</v>
+      </c>
+      <c r="AD42">
+        <v>60</v>
+      </c>
+      <c r="AE42">
         <v>85</v>
       </c>
-      <c r="AB42">
-        <v>14</v>
-      </c>
-      <c r="AC42">
-        <v>10</v>
-      </c>
-      <c r="AD42">
-        <v>16.5</v>
-      </c>
-      <c r="AE42">
+      <c r="AF42">
         <v>42</v>
-      </c>
-      <c r="AF42">
-        <v>15</v>
       </c>
       <c r="AG42">
         <v>10.5</v>
       </c>
       <c r="AH42">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AI42">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ42">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AK42">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL42">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AM42">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN42">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AO42">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AP42">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AQ42">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR42">
         <v>21</v>
       </c>
       <c r="AS42">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AT42">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU42">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW42">
         <v>23</v>
       </c>
       <c r="AX42">
+        <v>12</v>
+      </c>
+      <c r="AY42">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ42">
         <v>12.5</v>
-      </c>
-      <c r="AY42">
-        <v>9.6</v>
-      </c>
-      <c r="AZ42">
-        <v>13.5</v>
       </c>
       <c r="BA42">
         <v>24</v>
       </c>
       <c r="BB42">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BC42">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BD42">
         <v>18</v>
       </c>
       <c r="BE42">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="BF42">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG42">
         <v>19.5</v>
@@ -11177,7 +11177,7 @@
         <v>213</v>
       </c>
       <c r="F43">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="G43">
         <v>2.94</v>
@@ -11186,7 +11186,7 @@
         <v>3.15</v>
       </c>
       <c r="I43">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J43">
         <v>3.1</v>
@@ -11210,7 +11210,7 @@
         <v>1.25</v>
       </c>
       <c r="Q43">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11434,7 +11434,7 @@
         <v>4.7</v>
       </c>
       <c r="K44">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11449,7 +11449,7 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q44">
         <v>1.68</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -661,7 +661,7 @@
     <t>Estoril Praia</t>
   </si>
   <si>
-    <t>2026-09-12 06:26:41</t>
+    <t>2026-09-12 08:59:03</t>
   </si>
 </sst>
 </file>
@@ -1255,22 +1255,22 @@
         <v>172</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G2">
         <v>2.52</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
         <v>4.5</v>
       </c>
       <c r="J2">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1288,7 +1288,7 @@
         <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R2">
         <v>1.29</v>
@@ -1300,7 +1300,7 @@
         <v>1.69</v>
       </c>
       <c r="U2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>1.29</v>
@@ -1324,7 +1324,7 @@
         <v>18.5</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1390,7 +1390,7 @@
         <v>9.6</v>
       </c>
       <c r="AY2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2">
         <v>10</v>
@@ -1497,19 +1497,19 @@
         <v>173</v>
       </c>
       <c r="F3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G3">
         <v>2.86</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K3">
         <v>3.3</v>
@@ -1530,7 +1530,7 @@
         <v>1.36</v>
       </c>
       <c r="Q3">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
         <v>1.13</v>
@@ -1545,7 +1545,7 @@
         <v>1.59</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
         <v>1.53</v>
@@ -1742,10 +1742,10 @@
         <v>1.28</v>
       </c>
       <c r="G4">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>1.28</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -1984,7 +1984,7 @@
         <v>2.72</v>
       </c>
       <c r="G5">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H5">
         <v>2.5</v>
@@ -2014,10 +2014,10 @@
         <v>2.78</v>
       </c>
       <c r="Q5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S5">
         <v>2.3</v>
@@ -2026,7 +2026,7 @@
         <v>1.45</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V5">
         <v>1.62</v>
@@ -2038,13 +2038,13 @@
         <v>50</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB5">
         <v>26</v>
@@ -2053,52 +2053,52 @@
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
         <v>30</v>
       </c>
       <c r="AF5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG5">
         <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
         <v>40</v>
       </c>
       <c r="AJ5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN5">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO5">
         <v>15</v>
       </c>
       <c r="AP5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS5">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AT5">
         <v>14.5</v>
@@ -2107,10 +2107,10 @@
         <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
@@ -2125,10 +2125,10 @@
         <v>18</v>
       </c>
       <c r="BB5">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD5">
         <v>19</v>
@@ -2140,7 +2140,7 @@
         <v>11.5</v>
       </c>
       <c r="BG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
         <v>5.5</v>
@@ -2223,22 +2223,22 @@
         <v>176</v>
       </c>
       <c r="F6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G6">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I6">
         <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L6">
         <v>1.29</v>
@@ -2268,13 +2268,13 @@
         <v>1.79</v>
       </c>
       <c r="U6">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W6">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2468,13 +2468,13 @@
         <v>4.4</v>
       </c>
       <c r="G7">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="H7">
         <v>1.83</v>
       </c>
       <c r="I7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J7">
         <v>1.01</v>
@@ -2495,13 +2495,13 @@
         <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q7">
         <v>1.98</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S7">
         <v>3.5</v>
@@ -2513,7 +2513,7 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W7">
         <v>1.21</v>
@@ -2949,19 +2949,19 @@
         <v>179</v>
       </c>
       <c r="F9">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="H9">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
         <v>4.8</v>
@@ -3194,16 +3194,16 @@
         <v>1.68</v>
       </c>
       <c r="G10">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H10">
         <v>3.2</v>
       </c>
       <c r="I10">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K10">
         <v>11</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q10">
         <v>1.8</v>
@@ -3675,22 +3675,22 @@
         <v>182</v>
       </c>
       <c r="F12">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G12">
         <v>3.3</v>
       </c>
       <c r="H12">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I12">
         <v>3.65</v>
       </c>
       <c r="J12">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K12">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q12">
         <v>1.86</v>
@@ -3917,19 +3917,19 @@
         <v>183</v>
       </c>
       <c r="F13">
+        <v>1.37</v>
+      </c>
+      <c r="G13">
+        <v>5.8</v>
+      </c>
+      <c r="H13">
+        <v>1.37</v>
+      </c>
+      <c r="I13">
+        <v>2.92</v>
+      </c>
+      <c r="J13">
         <v>3.15</v>
-      </c>
-      <c r="G13">
-        <v>4.6</v>
-      </c>
-      <c r="H13">
-        <v>1.97</v>
-      </c>
-      <c r="I13">
-        <v>2.42</v>
-      </c>
-      <c r="J13">
-        <v>3.2</v>
       </c>
       <c r="K13">
         <v>3.7</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q14">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>70</v>
       </c>
       <c r="AG15">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AH15">
         <v>21</v>
@@ -4545,19 +4545,19 @@
         <v>23</v>
       </c>
       <c r="BB15">
+        <v>7.4</v>
+      </c>
+      <c r="BC15">
         <v>7.2</v>
       </c>
-      <c r="BC15">
-        <v>7</v>
-      </c>
       <c r="BD15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG15">
         <v>7.2</v>
@@ -4646,19 +4646,19 @@
         <v>1.24</v>
       </c>
       <c r="G16">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J16">
         <v>6.8</v>
       </c>
       <c r="K16">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>1.34</v>
@@ -4673,13 +4673,13 @@
         <v>1.23</v>
       </c>
       <c r="P16">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
         <v>1.7</v>
       </c>
       <c r="R16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16">
         <v>2.84</v>
@@ -4694,7 +4694,7 @@
         <v>1.05</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="X16">
         <v>23</v>
@@ -4712,10 +4712,10 @@
         <v>8.4</v>
       </c>
       <c r="AC16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD16">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE16">
         <v>480</v>
@@ -4724,25 +4724,25 @@
         <v>7.2</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH16">
         <v>46</v>
       </c>
       <c r="AI16">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AJ16">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL16">
         <v>60</v>
       </c>
       <c r="AM16">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AN16">
         <v>4.6</v>
@@ -4751,16 +4751,16 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR16">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="AS16">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT16">
         <v>7.6</v>
@@ -4769,10 +4769,10 @@
         <v>13.5</v>
       </c>
       <c r="AV16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AW16">
-        <v>12.5</v>
+        <v>90</v>
       </c>
       <c r="AX16">
         <v>6.6</v>
@@ -4781,13 +4781,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BA16">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="BB16">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC16">
         <v>13.5</v>
@@ -4796,13 +4796,13 @@
         <v>28</v>
       </c>
       <c r="BE16">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BF16">
         <v>4.3</v>
       </c>
       <c r="BG16">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="BH16">
         <v>4.3</v>
@@ -4888,10 +4888,10 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H17">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="I17">
         <v>1.62</v>
@@ -4900,7 +4900,7 @@
         <v>4.7</v>
       </c>
       <c r="K17">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4918,7 +4918,7 @@
         <v>2.08</v>
       </c>
       <c r="Q17">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4930,7 +4930,7 @@
         <v>1.81</v>
       </c>
       <c r="U17">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -5133,7 +5133,7 @@
         <v>1.59</v>
       </c>
       <c r="H18">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>10.5</v>
@@ -5142,13 +5142,13 @@
         <v>4.4</v>
       </c>
       <c r="K18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5157,10 +5157,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q18">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5369,22 +5369,22 @@
         <v>189</v>
       </c>
       <c r="F19">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G19">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H19">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I19">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J19">
         <v>3.2</v>
       </c>
       <c r="K19">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5399,10 +5399,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5611,22 +5611,22 @@
         <v>190</v>
       </c>
       <c r="F20">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G20">
         <v>3.1</v>
       </c>
       <c r="H20">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J20">
         <v>3.4</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5865,10 +5865,10 @@
         <v>13</v>
       </c>
       <c r="J21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -6095,19 +6095,19 @@
         <v>192</v>
       </c>
       <c r="F22">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="G22">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="H22">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I22">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K22">
         <v>5.3</v>
@@ -6337,22 +6337,22 @@
         <v>193</v>
       </c>
       <c r="F23">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G23">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H23">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J23">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6367,10 +6367,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="Q23">
-        <v>1.97</v>
+        <v>1.3</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6821,22 +6821,22 @@
         <v>195</v>
       </c>
       <c r="F25">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G25">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H25">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="I25">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J25">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6851,10 +6851,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q25">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7063,22 +7063,22 @@
         <v>196</v>
       </c>
       <c r="F26">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G26">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H26">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I26">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J26">
         <v>3.4</v>
       </c>
       <c r="K26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7314,10 +7314,10 @@
         <v>1.05</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J27">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="K27">
         <v>20</v>
@@ -7338,7 +7338,7 @@
         <v>3.85</v>
       </c>
       <c r="Q27">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7550,19 +7550,19 @@
         <v>3.35</v>
       </c>
       <c r="G28">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H28">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I28">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="J28">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K28">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q28">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7792,16 +7792,16 @@
         <v>1.9</v>
       </c>
       <c r="G29">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H29">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I29">
         <v>4.5</v>
       </c>
       <c r="J29">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K29">
         <v>4.4</v>
@@ -8034,16 +8034,16 @@
         <v>4.4</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="H30">
         <v>1.67</v>
       </c>
       <c r="I30">
-        <v>1.86</v>
+        <v>110</v>
       </c>
       <c r="J30">
-        <v>3.9</v>
+        <v>1.11</v>
       </c>
       <c r="K30">
         <v>5.8</v>
@@ -8061,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="Q30">
         <v>1.65</v>
@@ -8515,7 +8515,7 @@
         <v>202</v>
       </c>
       <c r="F32">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G32">
         <v>1.9</v>
@@ -8524,13 +8524,13 @@
         <v>4</v>
       </c>
       <c r="I32">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J32">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K32">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8545,10 +8545,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q32">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8760,16 +8760,16 @@
         <v>2.28</v>
       </c>
       <c r="G33">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H33">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I33">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J33">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K33">
         <v>4.3</v>
@@ -8787,7 +8787,7 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q33">
         <v>1.56</v>
@@ -8999,7 +8999,7 @@
         <v>204</v>
       </c>
       <c r="F34">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="G34">
         <v>1.32</v>
@@ -9008,13 +9008,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I34">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J34">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>12</v>
+        <v>880</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9029,10 +9029,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q34">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9241,10 +9241,10 @@
         <v>205</v>
       </c>
       <c r="F35">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G35">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H35">
         <v>2.62</v>
@@ -9271,10 +9271,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q35">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9486,19 +9486,19 @@
         <v>2.2</v>
       </c>
       <c r="G36">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H36">
         <v>2.74</v>
       </c>
       <c r="I36">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="J36">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K36">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9725,22 +9725,22 @@
         <v>207</v>
       </c>
       <c r="F37">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G37">
-        <v>3.6</v>
+        <v>17.5</v>
       </c>
       <c r="H37">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="I37">
         <v>2.82</v>
       </c>
       <c r="J37">
-        <v>3.55</v>
+        <v>1.69</v>
       </c>
       <c r="K37">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9755,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q37">
         <v>1.26</v>
@@ -9967,22 +9967,22 @@
         <v>208</v>
       </c>
       <c r="F38">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G38">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="H38">
         <v>5.9</v>
       </c>
       <c r="I38">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="J38">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K38">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10000,7 +10000,7 @@
         <v>2.02</v>
       </c>
       <c r="Q38">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10209,13 +10209,13 @@
         <v>209</v>
       </c>
       <c r="F39">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="G39">
         <v>3.4</v>
       </c>
       <c r="H39">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="I39">
         <v>3.95</v>
@@ -10242,7 +10242,7 @@
         <v>1.74</v>
       </c>
       <c r="Q39">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10454,13 +10454,13 @@
         <v>1.27</v>
       </c>
       <c r="G40">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H40">
         <v>14</v>
       </c>
       <c r="I40">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J40">
         <v>6.6</v>
@@ -10496,7 +10496,7 @@
         <v>2.12</v>
       </c>
       <c r="U40">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -10508,7 +10508,7 @@
         <v>29</v>
       </c>
       <c r="Y40">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z40">
         <v>1000</v>
@@ -10601,7 +10601,7 @@
         <v>12.5</v>
       </c>
       <c r="BD40">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BE40">
         <v>12.5</v>
@@ -10693,10 +10693,10 @@
         <v>211</v>
       </c>
       <c r="F41">
+        <v>2.4</v>
+      </c>
+      <c r="G41">
         <v>2.42</v>
-      </c>
-      <c r="G41">
-        <v>2.46</v>
       </c>
       <c r="H41">
         <v>3.15</v>
@@ -10735,10 +10735,10 @@
         <v>3.15</v>
       </c>
       <c r="T41">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U41">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -10747,16 +10747,16 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y41">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA41">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AB41">
         <v>12</v>
@@ -10768,7 +10768,7 @@
         <v>13.5</v>
       </c>
       <c r="AE41">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF41">
         <v>17</v>
@@ -10783,7 +10783,7 @@
         <v>38</v>
       </c>
       <c r="AJ41">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK41">
         <v>24</v>
@@ -10795,22 +10795,22 @@
         <v>70</v>
       </c>
       <c r="AN41">
-        <v>18.5</v>
+        <v>140</v>
       </c>
       <c r="AO41">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AP41">
         <v>15</v>
       </c>
       <c r="AQ41">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR41">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS41">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT41">
         <v>10.5</v>
@@ -10822,7 +10822,7 @@
         <v>12.5</v>
       </c>
       <c r="AW41">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AX41">
         <v>15</v>
@@ -10834,7 +10834,7 @@
         <v>14.5</v>
       </c>
       <c r="BA41">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB41">
         <v>30</v>
@@ -10843,13 +10843,13 @@
         <v>21</v>
       </c>
       <c r="BD41">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BE41">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF41">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG41">
         <v>26</v>
@@ -10941,7 +10941,7 @@
         <v>1.98</v>
       </c>
       <c r="H42">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I42">
         <v>3.95</v>
@@ -10977,7 +10977,7 @@
         <v>2.56</v>
       </c>
       <c r="T42">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U42">
         <v>2.6</v>
@@ -10992,7 +10992,7 @@
         <v>36</v>
       </c>
       <c r="Y42">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z42">
         <v>55</v>
@@ -11019,10 +11019,10 @@
         <v>10.5</v>
       </c>
       <c r="AH42">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI42">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AJ42">
         <v>34</v>
@@ -11031,10 +11031,10 @@
         <v>970</v>
       </c>
       <c r="AL42">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM42">
-        <v>580</v>
+        <v>660</v>
       </c>
       <c r="AN42">
         <v>15</v>
@@ -11052,7 +11052,7 @@
         <v>21</v>
       </c>
       <c r="AS42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT42">
         <v>11.5</v>
@@ -11079,7 +11079,7 @@
         <v>24</v>
       </c>
       <c r="BB42">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC42">
         <v>13.5</v>
@@ -11088,7 +11088,7 @@
         <v>18</v>
       </c>
       <c r="BE42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF42">
         <v>8</v>
@@ -11186,7 +11186,7 @@
         <v>3.15</v>
       </c>
       <c r="I43">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J43">
         <v>3.1</v>
@@ -11419,7 +11419,7 @@
         <v>214</v>
       </c>
       <c r="F44">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G44">
         <v>1.54</v>
@@ -11428,13 +11428,13 @@
         <v>7</v>
       </c>
       <c r="I44">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J44">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11452,7 +11452,7 @@
         <v>2.06</v>
       </c>
       <c r="Q44">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11509,7 +11509,7 @@
         <v>1000</v>
       </c>
       <c r="AJ44">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK44">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="222">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Ukrainian Premier League</t>
   </si>
   <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
@@ -364,6 +367,9 @@
     <t>12:30:00</t>
   </si>
   <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -424,6 +430,9 @@
     <t>Dynamo Kiev</t>
   </si>
   <si>
+    <t>El Geish</t>
+  </si>
+  <si>
     <t>FC Inter Turku</t>
   </si>
   <si>
@@ -469,30 +478,33 @@
     <t>Zemun</t>
   </si>
   <si>
+    <t>Sporting Lisbon B</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Bodo Glimt</t>
+  </si>
+  <si>
+    <t>Hapoel Kiryat Shmona</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Digenis Ypsona</t>
+  </si>
+  <si>
     <t>Porto B</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
-    <t>Bodo Glimt</t>
-  </si>
-  <si>
-    <t>Hapoel Kiryat Shmona</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Digenis Ypsona</t>
-  </si>
-  <si>
-    <t>Sporting Lisbon B</t>
-  </si>
-  <si>
     <t>Ostersunds FK</t>
   </si>
   <si>
@@ -553,6 +565,9 @@
     <t>FC Epicentr Dunaivtsi</t>
   </si>
   <si>
+    <t>Smouha</t>
+  </si>
+  <si>
     <t>VPS</t>
   </si>
   <si>
@@ -598,30 +613,33 @@
     <t>Radnik Surdulica</t>
   </si>
   <si>
+    <t>Lusitania Futebol Clube</t>
+  </si>
+  <si>
+    <t>Nieciecza</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>National Bank</t>
+  </si>
+  <si>
+    <t>Brondby</t>
+  </si>
+  <si>
+    <t>Aris FC Limassol</t>
+  </si>
+  <si>
     <t>Vizela</t>
   </si>
   <si>
-    <t>Nieciecza</t>
-  </si>
-  <si>
-    <t>Piast Gliwice</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Brondby</t>
-  </si>
-  <si>
-    <t>Aris FC Limassol</t>
-  </si>
-  <si>
-    <t>Lusitania Futebol Clube</t>
-  </si>
-  <si>
     <t>Helsingborgs</t>
   </si>
   <si>
@@ -661,7 +679,7 @@
     <t>Estoril Praia</t>
   </si>
   <si>
-    <t>2026-09-12 08:59:03</t>
+    <t>2026-09-12 11:31:29</t>
   </si>
 </sst>
 </file>
@@ -993,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB44"/>
+  <dimension ref="A1:CB46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1243,31 +1261,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K2">
         <v>3.75</v>
@@ -1288,7 +1306,7 @@
         <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
         <v>1.29</v>
@@ -1297,16 +1315,16 @@
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
         <v>2</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1375,7 +1393,7 @@
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU2">
         <v>5.3</v>
@@ -1477,7 +1495,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1485,34 +1503,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F3">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="G3">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H3">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="J3">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
         <v>1.64</v>
@@ -1521,142 +1539,142 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P3">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="Y3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z3">
+        <v>23</v>
+      </c>
+      <c r="AA3">
+        <v>630</v>
+      </c>
+      <c r="AB3">
+        <v>7.6</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>21</v>
+      </c>
+      <c r="AE3">
+        <v>320</v>
+      </c>
+      <c r="AF3">
+        <v>17.5</v>
+      </c>
+      <c r="AG3">
+        <v>16</v>
+      </c>
+      <c r="AH3">
+        <v>55</v>
+      </c>
+      <c r="AI3">
+        <v>980</v>
+      </c>
+      <c r="AJ3">
+        <v>90</v>
+      </c>
+      <c r="AK3">
+        <v>95</v>
+      </c>
+      <c r="AL3">
+        <v>980</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>340</v>
+      </c>
+      <c r="AO3">
+        <v>980</v>
+      </c>
+      <c r="AP3">
+        <v>6.6</v>
+      </c>
+      <c r="AQ3">
+        <v>7.2</v>
+      </c>
+      <c r="AR3">
+        <v>15</v>
+      </c>
+      <c r="AS3">
+        <v>5</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>6.6</v>
+      </c>
+      <c r="AV3">
+        <v>13</v>
+      </c>
+      <c r="AW3">
+        <v>5</v>
+      </c>
+      <c r="AX3">
         <v>12.5</v>
       </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>10.5</v>
-      </c>
-      <c r="AC3">
-        <v>9</v>
-      </c>
-      <c r="AD3">
-        <v>1000</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>60</v>
-      </c>
-      <c r="AG3">
-        <v>42</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>5.2</v>
-      </c>
-      <c r="AQ3">
-        <v>6.2</v>
-      </c>
-      <c r="AR3">
-        <v>1.77</v>
-      </c>
-      <c r="AS3">
-        <v>1.77</v>
-      </c>
-      <c r="AT3">
-        <v>5.6</v>
-      </c>
-      <c r="AU3">
-        <v>5.3</v>
-      </c>
-      <c r="AV3">
-        <v>10.5</v>
-      </c>
-      <c r="AW3">
-        <v>1.77</v>
-      </c>
-      <c r="AX3">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>1.77</v>
+        <v>4.6</v>
       </c>
       <c r="BA3">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="BB3">
-        <v>1.77</v>
+        <v>24</v>
       </c>
       <c r="BC3">
-        <v>1.77</v>
+        <v>25</v>
       </c>
       <c r="BD3">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="BE3">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="BF3">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="BG3">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="BH3">
         <v>2.56</v>
@@ -1719,7 +1737,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1727,64 +1745,64 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F4">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="H4">
-        <v>1.28</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
         <v>1.28</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.05</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S4">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1799,16 +1817,16 @@
         <v>1000</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB4">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AC4">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
         <v>55</v>
@@ -1817,10 +1835,10 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AH4">
         <v>65</v>
@@ -1838,67 +1856,67 @@
         <v>1000</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AS4">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AT4">
         <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="AX4">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AY4">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="BB4">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="BC4">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BD4">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="BE4">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG4">
-        <v>1.34</v>
+        <v>20</v>
       </c>
       <c r="BH4">
         <v>4.7</v>
@@ -1961,7 +1979,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1969,28 +1987,28 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F5">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G5">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H5">
         <v>2.5</v>
       </c>
       <c r="I5">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J5">
         <v>3.85</v>
@@ -2023,61 +2041,61 @@
         <v>2.3</v>
       </c>
       <c r="T5">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="U5">
         <v>2.84</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W5">
         <v>1.53</v>
       </c>
       <c r="X5">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Y5">
         <v>22</v>
       </c>
       <c r="Z5">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AA5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB5">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF5">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AL5">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>150</v>
@@ -2092,40 +2110,40 @@
         <v>19</v>
       </c>
       <c r="AQ5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR5">
         <v>15</v>
       </c>
       <c r="AS5">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="AT5">
         <v>14.5</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
       </c>
       <c r="AY5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA5">
         <v>18</v>
       </c>
       <c r="BB5">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="BC5">
         <v>17</v>
@@ -2134,7 +2152,7 @@
         <v>19</v>
       </c>
       <c r="BE5">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BF5">
         <v>11.5</v>
@@ -2143,10 +2161,10 @@
         <v>10.5</v>
       </c>
       <c r="BH5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ5">
         <v>13</v>
@@ -2161,7 +2179,7 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO5">
         <v>4.9</v>
@@ -2170,7 +2188,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -2179,16 +2197,16 @@
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -2203,7 +2221,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2211,34 +2229,34 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F6">
         <v>1.52</v>
       </c>
       <c r="G6">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L6">
         <v>1.29</v>
@@ -2247,34 +2265,34 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
         <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R6">
         <v>1.44</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U6">
         <v>2</v>
       </c>
       <c r="V6">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2313,7 +2331,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK6">
         <v>60</v>
@@ -2331,7 +2349,7 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6">
         <v>1.6</v>
@@ -2445,7 +2463,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2453,28 +2471,28 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F7">
         <v>4.4</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>5.9</v>
       </c>
       <c r="H7">
         <v>1.83</v>
       </c>
       <c r="I7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J7">
         <v>1.01</v>
@@ -2489,19 +2507,19 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
         <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
         <v>3.5</v>
@@ -2513,7 +2531,7 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W7">
         <v>1.21</v>
@@ -2687,7 +2705,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2695,16 +2713,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F8">
         <v>1.04</v>
@@ -2719,217 +2737,217 @@
         <v>1000</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K8">
         <v>890</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
         <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2937,241 +2955,241 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F9">
+        <v>2.98</v>
+      </c>
+      <c r="G9">
+        <v>3.4</v>
+      </c>
+      <c r="H9">
+        <v>3.3</v>
+      </c>
+      <c r="I9">
+        <v>3.95</v>
+      </c>
+      <c r="J9">
+        <v>2.4</v>
+      </c>
+      <c r="K9">
+        <v>2.7</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.18</v>
+      </c>
+      <c r="N9">
+        <v>2.12</v>
+      </c>
+      <c r="O9">
+        <v>1.69</v>
+      </c>
+      <c r="P9">
+        <v>1.31</v>
+      </c>
+      <c r="Q9">
+        <v>3.2</v>
+      </c>
+      <c r="R9">
+        <v>1.08</v>
+      </c>
+      <c r="S9">
+        <v>6.4</v>
+      </c>
+      <c r="T9">
+        <v>2.26</v>
+      </c>
+      <c r="U9">
         <v>1.6</v>
       </c>
-      <c r="G9">
-        <v>1.9</v>
-      </c>
-      <c r="H9">
-        <v>4.8</v>
-      </c>
-      <c r="I9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J9">
-        <v>3.8</v>
-      </c>
-      <c r="K9">
-        <v>4.8</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1.76</v>
-      </c>
-      <c r="Q9">
-        <v>1.8</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3179,34 +3197,34 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F10">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="G10">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="H10">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K10">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3221,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="Q10">
         <v>1.8</v>
@@ -3413,42 +3431,42 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="K11">
-        <v>900</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3463,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3655,42 +3673,42 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F12">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="K12">
-        <v>5.6</v>
+        <v>900</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3705,10 +3723,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="Q12">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3897,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3905,34 +3923,34 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F13">
-        <v>1.37</v>
+        <v>2.36</v>
       </c>
       <c r="G13">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="H13">
-        <v>1.37</v>
+        <v>2.52</v>
       </c>
       <c r="I13">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="J13">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3947,10 +3965,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4139,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4147,34 +4165,34 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F14">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G14">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="H14">
-        <v>3.85</v>
+        <v>1.96</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J14">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4189,10 +4207,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q14">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4381,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4389,232 +4407,232 @@
         <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F15">
-        <v>6.4</v>
+        <v>1.29</v>
       </c>
       <c r="G15">
-        <v>6.6</v>
+        <v>2.24</v>
       </c>
       <c r="H15">
-        <v>1.63</v>
+        <v>3.75</v>
       </c>
       <c r="I15">
-        <v>1.65</v>
+        <v>1000</v>
       </c>
       <c r="J15">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
         <v>4.4</v>
       </c>
       <c r="L15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="R15">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AO15">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BG15">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4623,240 +4641,240 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F16">
-        <v>1.24</v>
+        <v>6.4</v>
       </c>
       <c r="G16">
-        <v>1.26</v>
+        <v>6.6</v>
       </c>
       <c r="H16">
+        <v>1.63</v>
+      </c>
+      <c r="I16">
+        <v>1.65</v>
+      </c>
+      <c r="J16">
+        <v>4.2</v>
+      </c>
+      <c r="K16">
+        <v>4.3</v>
+      </c>
+      <c r="L16">
+        <v>1.37</v>
+      </c>
+      <c r="M16">
+        <v>1.06</v>
+      </c>
+      <c r="N16">
+        <v>4.3</v>
+      </c>
+      <c r="O16">
+        <v>1.28</v>
+      </c>
+      <c r="P16">
+        <v>2.2</v>
+      </c>
+      <c r="Q16">
+        <v>1.81</v>
+      </c>
+      <c r="R16">
+        <v>1.43</v>
+      </c>
+      <c r="S16">
+        <v>3.05</v>
+      </c>
+      <c r="T16">
+        <v>1.88</v>
+      </c>
+      <c r="U16">
+        <v>2.04</v>
+      </c>
+      <c r="V16">
+        <v>2.54</v>
+      </c>
+      <c r="W16">
+        <v>1.17</v>
+      </c>
+      <c r="X16">
+        <v>17.5</v>
+      </c>
+      <c r="Y16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z16">
+        <v>10.5</v>
+      </c>
+      <c r="AA16">
+        <v>15</v>
+      </c>
+      <c r="AB16">
+        <v>23</v>
+      </c>
+      <c r="AC16">
+        <v>9.6</v>
+      </c>
+      <c r="AD16">
+        <v>11</v>
+      </c>
+      <c r="AE16">
+        <v>16.5</v>
+      </c>
+      <c r="AF16">
+        <v>60</v>
+      </c>
+      <c r="AG16">
+        <v>25</v>
+      </c>
+      <c r="AH16">
+        <v>21</v>
+      </c>
+      <c r="AI16">
+        <v>42</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>8.6</v>
+      </c>
+      <c r="AP16">
+        <v>14.5</v>
+      </c>
+      <c r="AQ16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR16">
+        <v>9</v>
+      </c>
+      <c r="AS16">
+        <v>13.5</v>
+      </c>
+      <c r="AT16">
+        <v>19</v>
+      </c>
+      <c r="AU16">
+        <v>8.6</v>
+      </c>
+      <c r="AV16">
+        <v>9</v>
+      </c>
+      <c r="AW16">
+        <v>14</v>
+      </c>
+      <c r="AX16">
+        <v>28</v>
+      </c>
+      <c r="AY16">
+        <v>20</v>
+      </c>
+      <c r="AZ16">
         <v>18</v>
       </c>
-      <c r="I16">
-        <v>19.5</v>
-      </c>
-      <c r="J16">
-        <v>6.8</v>
-      </c>
-      <c r="K16">
-        <v>7</v>
-      </c>
-      <c r="L16">
-        <v>1.34</v>
-      </c>
-      <c r="M16">
-        <v>1.04</v>
-      </c>
-      <c r="N16">
-        <v>5</v>
-      </c>
-      <c r="O16">
-        <v>1.23</v>
-      </c>
-      <c r="P16">
-        <v>2.4</v>
-      </c>
-      <c r="Q16">
-        <v>1.7</v>
-      </c>
-      <c r="R16">
-        <v>1.53</v>
-      </c>
-      <c r="S16">
-        <v>2.84</v>
-      </c>
-      <c r="T16">
-        <v>2.52</v>
-      </c>
-      <c r="U16">
-        <v>1.61</v>
-      </c>
-      <c r="V16">
-        <v>1.05</v>
-      </c>
-      <c r="W16">
-        <v>4.9</v>
-      </c>
-      <c r="X16">
+      <c r="BA16">
         <v>23</v>
       </c>
-      <c r="Y16">
-        <v>50</v>
-      </c>
-      <c r="Z16">
-        <v>230</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>8.4</v>
-      </c>
-      <c r="AC16">
-        <v>16</v>
-      </c>
-      <c r="AD16">
-        <v>70</v>
-      </c>
-      <c r="AE16">
-        <v>480</v>
-      </c>
-      <c r="AF16">
+      <c r="BB16">
+        <v>44</v>
+      </c>
+      <c r="BC16">
+        <v>36</v>
+      </c>
+      <c r="BD16">
+        <v>36</v>
+      </c>
+      <c r="BE16">
+        <v>40</v>
+      </c>
+      <c r="BF16">
+        <v>38</v>
+      </c>
+      <c r="BG16">
         <v>7.2</v>
-      </c>
-      <c r="AG16">
-        <v>12</v>
-      </c>
-      <c r="AH16">
-        <v>46</v>
-      </c>
-      <c r="AI16">
-        <v>340</v>
-      </c>
-      <c r="AJ16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AK16">
-        <v>15.5</v>
-      </c>
-      <c r="AL16">
-        <v>60</v>
-      </c>
-      <c r="AM16">
-        <v>360</v>
-      </c>
-      <c r="AN16">
-        <v>4.6</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>19</v>
-      </c>
-      <c r="AQ16">
-        <v>36</v>
-      </c>
-      <c r="AR16">
-        <v>46</v>
-      </c>
-      <c r="AS16">
-        <v>15.5</v>
-      </c>
-      <c r="AT16">
-        <v>7.6</v>
-      </c>
-      <c r="AU16">
-        <v>13.5</v>
-      </c>
-      <c r="AV16">
-        <v>42</v>
-      </c>
-      <c r="AW16">
-        <v>90</v>
-      </c>
-      <c r="AX16">
-        <v>6.6</v>
-      </c>
-      <c r="AY16">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16">
-        <v>28</v>
-      </c>
-      <c r="BA16">
-        <v>95</v>
-      </c>
-      <c r="BB16">
-        <v>7.4</v>
-      </c>
-      <c r="BC16">
-        <v>13.5</v>
-      </c>
-      <c r="BD16">
-        <v>28</v>
-      </c>
-      <c r="BE16">
-        <v>50</v>
-      </c>
-      <c r="BF16">
-        <v>4.3</v>
-      </c>
-      <c r="BG16">
-        <v>90</v>
       </c>
       <c r="BH16">
         <v>4.3</v>
       </c>
       <c r="BI16">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>3.85</v>
+        <v>12</v>
       </c>
       <c r="BO16">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="BP16">
-        <v>970</v>
+        <v>70</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4865,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4873,232 +4891,232 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>1.24</v>
       </c>
       <c r="G17">
-        <v>7.2</v>
+        <v>1.26</v>
       </c>
       <c r="H17">
-        <v>1.55</v>
+        <v>18</v>
       </c>
       <c r="I17">
-        <v>1.62</v>
+        <v>20</v>
       </c>
       <c r="J17">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="K17">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M17">
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="Q17">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T17">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y17">
+        <v>50</v>
+      </c>
+      <c r="Z17">
+        <v>210</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>8.4</v>
+      </c>
+      <c r="AC17">
+        <v>16</v>
+      </c>
+      <c r="AD17">
+        <v>70</v>
+      </c>
+      <c r="AE17">
+        <v>470</v>
+      </c>
+      <c r="AF17">
+        <v>7.2</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>46</v>
+      </c>
+      <c r="AI17">
+        <v>330</v>
+      </c>
+      <c r="AJ17">
+        <v>8.4</v>
+      </c>
+      <c r="AK17">
+        <v>15.5</v>
+      </c>
+      <c r="AL17">
+        <v>60</v>
+      </c>
+      <c r="AM17">
+        <v>360</v>
+      </c>
+      <c r="AN17">
+        <v>4.6</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>19</v>
+      </c>
+      <c r="AQ17">
+        <v>38</v>
+      </c>
+      <c r="AR17">
+        <v>14</v>
+      </c>
+      <c r="AS17">
+        <v>15</v>
+      </c>
+      <c r="AT17">
+        <v>7.6</v>
+      </c>
+      <c r="AU17">
+        <v>14.5</v>
+      </c>
+      <c r="AV17">
+        <v>12</v>
+      </c>
+      <c r="AW17">
+        <v>14.5</v>
+      </c>
+      <c r="AX17">
+        <v>6.4</v>
+      </c>
+      <c r="AY17">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17">
+        <v>36</v>
+      </c>
+      <c r="BA17">
+        <v>14</v>
+      </c>
+      <c r="BB17">
+        <v>7.6</v>
+      </c>
+      <c r="BC17">
+        <v>13.5</v>
+      </c>
+      <c r="BD17">
+        <v>12</v>
+      </c>
+      <c r="BE17">
+        <v>14</v>
+      </c>
+      <c r="BF17">
+        <v>4.2</v>
+      </c>
+      <c r="BG17">
+        <v>15</v>
+      </c>
+      <c r="BH17">
+        <v>4.3</v>
+      </c>
+      <c r="BI17">
+        <v>3.1</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>3.85</v>
+      </c>
+      <c r="BO17">
+        <v>2.92</v>
+      </c>
+      <c r="BP17">
         <v>970</v>
       </c>
-      <c r="Z17">
-        <v>970</v>
-      </c>
-      <c r="AA17">
-        <v>970</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>970</v>
-      </c>
-      <c r="AD17">
-        <v>970</v>
-      </c>
-      <c r="AE17">
-        <v>970</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>970</v>
-      </c>
-      <c r="AP17">
-        <v>11</v>
-      </c>
-      <c r="AQ17">
-        <v>6.8</v>
-      </c>
-      <c r="AR17">
-        <v>7</v>
-      </c>
-      <c r="AS17">
-        <v>1.53</v>
-      </c>
-      <c r="AT17">
-        <v>1.58</v>
-      </c>
-      <c r="AU17">
-        <v>7</v>
-      </c>
-      <c r="AV17">
-        <v>7.2</v>
-      </c>
-      <c r="AW17">
-        <v>1.55</v>
-      </c>
-      <c r="AX17">
-        <v>1.58</v>
-      </c>
-      <c r="AY17">
-        <v>1.58</v>
-      </c>
-      <c r="AZ17">
-        <v>1.58</v>
-      </c>
-      <c r="BA17">
-        <v>1.58</v>
-      </c>
-      <c r="BB17">
-        <v>1.58</v>
-      </c>
-      <c r="BC17">
-        <v>1.58</v>
-      </c>
-      <c r="BD17">
-        <v>1.58</v>
-      </c>
-      <c r="BE17">
-        <v>1.58</v>
-      </c>
-      <c r="BF17">
-        <v>1.58</v>
-      </c>
-      <c r="BG17">
-        <v>6</v>
-      </c>
-      <c r="BH17">
-        <v>0</v>
-      </c>
-      <c r="BI17">
-        <v>0</v>
-      </c>
-      <c r="BJ17">
-        <v>0</v>
-      </c>
-      <c r="BK17">
-        <v>0</v>
-      </c>
-      <c r="BL17">
-        <v>0</v>
-      </c>
-      <c r="BM17">
-        <v>0</v>
-      </c>
-      <c r="BN17">
-        <v>0</v>
-      </c>
-      <c r="BO17">
-        <v>0</v>
-      </c>
-      <c r="BP17">
-        <v>0</v>
-      </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5107,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5115,179 +5133,179 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F18">
-        <v>1.47</v>
+        <v>6.2</v>
       </c>
       <c r="G18">
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <v>1.56</v>
+      </c>
+      <c r="I18">
         <v>1.59</v>
       </c>
-      <c r="H18">
+      <c r="J18">
+        <v>4.7</v>
+      </c>
+      <c r="K18">
+        <v>4.8</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1.04</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>2.02</v>
+      </c>
+      <c r="Q18">
+        <v>1.7</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1.8</v>
+      </c>
+      <c r="U18">
+        <v>1.87</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>970</v>
+      </c>
+      <c r="Z18">
+        <v>970</v>
+      </c>
+      <c r="AA18">
+        <v>970</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>970</v>
+      </c>
+      <c r="AD18">
+        <v>970</v>
+      </c>
+      <c r="AE18">
+        <v>970</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>970</v>
+      </c>
+      <c r="AP18">
+        <v>11</v>
+      </c>
+      <c r="AQ18">
+        <v>6.8</v>
+      </c>
+      <c r="AR18">
+        <v>7</v>
+      </c>
+      <c r="AS18">
+        <v>1.53</v>
+      </c>
+      <c r="AT18">
+        <v>1.58</v>
+      </c>
+      <c r="AU18">
+        <v>7</v>
+      </c>
+      <c r="AV18">
+        <v>7.2</v>
+      </c>
+      <c r="AW18">
+        <v>1.55</v>
+      </c>
+      <c r="AX18">
+        <v>1.58</v>
+      </c>
+      <c r="AY18">
+        <v>1.58</v>
+      </c>
+      <c r="AZ18">
+        <v>1.58</v>
+      </c>
+      <c r="BA18">
+        <v>1.58</v>
+      </c>
+      <c r="BB18">
+        <v>1.58</v>
+      </c>
+      <c r="BC18">
+        <v>1.58</v>
+      </c>
+      <c r="BD18">
+        <v>1.58</v>
+      </c>
+      <c r="BE18">
+        <v>1.58</v>
+      </c>
+      <c r="BF18">
+        <v>1.58</v>
+      </c>
+      <c r="BG18">
         <v>6</v>
       </c>
-      <c r="I18">
-        <v>10.5</v>
-      </c>
-      <c r="J18">
-        <v>4.4</v>
-      </c>
-      <c r="K18">
-        <v>6.4</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>1.02</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>2.12</v>
-      </c>
-      <c r="Q18">
-        <v>1.68</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>1.83</v>
-      </c>
-      <c r="U18">
-        <v>1.88</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>1000</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>19.5</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>9</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18">
-        <v>1.03</v>
-      </c>
-      <c r="AR18">
-        <v>1.03</v>
-      </c>
-      <c r="AS18">
-        <v>1.03</v>
-      </c>
-      <c r="AT18">
-        <v>1.03</v>
-      </c>
-      <c r="AU18">
-        <v>1.03</v>
-      </c>
-      <c r="AV18">
-        <v>1.03</v>
-      </c>
-      <c r="AW18">
-        <v>1.03</v>
-      </c>
-      <c r="AX18">
-        <v>1.03</v>
-      </c>
-      <c r="AY18">
-        <v>1.03</v>
-      </c>
-      <c r="AZ18">
-        <v>1.03</v>
-      </c>
-      <c r="BA18">
-        <v>1.03</v>
-      </c>
-      <c r="BB18">
-        <v>1.03</v>
-      </c>
-      <c r="BC18">
-        <v>1.03</v>
-      </c>
-      <c r="BD18">
-        <v>1.03</v>
-      </c>
-      <c r="BE18">
-        <v>1.03</v>
-      </c>
-      <c r="BF18">
-        <v>5.2</v>
-      </c>
-      <c r="BG18">
-        <v>1.01</v>
-      </c>
       <c r="BH18">
         <v>0</v>
       </c>
@@ -5349,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5357,40 +5375,40 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F19">
-        <v>2.62</v>
+        <v>1.43</v>
       </c>
       <c r="G19">
-        <v>3.6</v>
+        <v>1.58</v>
       </c>
       <c r="H19">
-        <v>2.32</v>
+        <v>6.4</v>
       </c>
       <c r="I19">
-        <v>2.9</v>
+        <v>14.5</v>
       </c>
       <c r="J19">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="K19">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5399,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="Q19">
         <v>1.67</v>
@@ -5411,10 +5429,10 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5423,112 +5441,112 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>0</v>
@@ -5591,42 +5609,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F20">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="G20">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H20">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5641,10 +5659,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q20">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5833,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5841,34 +5859,34 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F21">
-        <v>1.39</v>
+        <v>2.22</v>
       </c>
       <c r="G21">
-        <v>1.54</v>
+        <v>3.05</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="J21">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="K21">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5883,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="Q21">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6075,61 +6093,61 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F22">
+        <v>1.39</v>
+      </c>
+      <c r="G22">
+        <v>1.53</v>
+      </c>
+      <c r="H22">
+        <v>6</v>
+      </c>
+      <c r="I22">
+        <v>13</v>
+      </c>
+      <c r="J22">
+        <v>4.7</v>
+      </c>
+      <c r="K22">
+        <v>6.8</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.22</v>
+      </c>
+      <c r="Q22">
         <v>1.47</v>
       </c>
-      <c r="G22">
-        <v>1.83</v>
-      </c>
-      <c r="H22">
-        <v>4.8</v>
-      </c>
-      <c r="I22">
-        <v>7.6</v>
-      </c>
-      <c r="J22">
-        <v>4.1</v>
-      </c>
-      <c r="K22">
-        <v>5.3</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>2.24</v>
-      </c>
-      <c r="Q22">
-        <v>1.63</v>
-      </c>
       <c r="R22">
         <v>0</v>
       </c>
@@ -6317,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6325,40 +6343,40 @@
         <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F23">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>1.76</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="I23">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="J23">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -6367,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.42</v>
+        <v>2.24</v>
       </c>
       <c r="Q23">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6379,10 +6397,10 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6391,112 +6409,112 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH23">
         <v>0</v>
@@ -6559,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6567,40 +6585,40 @@
         <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -6609,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6621,10 +6639,10 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -6633,112 +6651,112 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
         <v>0</v>
@@ -6801,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6809,34 +6827,34 @@
         <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F25">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6851,10 +6869,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q25">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7043,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7051,34 +7069,34 @@
         <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F26">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="H26">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="I26">
         <v>3.45</v>
       </c>
       <c r="J26">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7093,10 +7111,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q26">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7285,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7293,34 +7311,34 @@
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F27">
-        <v>1.18</v>
+        <v>2.32</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="H27">
-        <v>1.05</v>
+        <v>2.84</v>
       </c>
       <c r="I27">
-        <v>60</v>
+        <v>3.55</v>
       </c>
       <c r="J27">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="K27">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7335,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>3.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q27">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7527,42 +7545,42 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E28" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F28">
-        <v>3.35</v>
+        <v>1.18</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H28">
-        <v>1.86</v>
+        <v>1.05</v>
       </c>
       <c r="I28">
-        <v>2.42</v>
+        <v>30</v>
       </c>
       <c r="J28">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="K28">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7577,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.04</v>
+        <v>3.85</v>
       </c>
       <c r="Q28">
         <v>1.01</v>
@@ -7769,42 +7787,42 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F29">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="G29">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="H29">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="I29">
-        <v>4.5</v>
+        <v>2.24</v>
       </c>
       <c r="J29">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7819,10 +7837,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="Q29">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8011,84 +8029,84 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F30">
-        <v>4.4</v>
+        <v>2.66</v>
       </c>
       <c r="G30">
+        <v>3.1</v>
+      </c>
+      <c r="H30">
+        <v>2.94</v>
+      </c>
+      <c r="I30">
+        <v>3.5</v>
+      </c>
+      <c r="J30">
+        <v>2.84</v>
+      </c>
+      <c r="K30">
+        <v>3.45</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1.11</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1.53</v>
+      </c>
+      <c r="Q30">
+        <v>2.46</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>1.91</v>
+      </c>
+      <c r="U30">
+        <v>1.8</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
         <v>970</v>
       </c>
-      <c r="H30">
-        <v>1.67</v>
-      </c>
-      <c r="I30">
-        <v>110</v>
-      </c>
-      <c r="J30">
-        <v>1.11</v>
-      </c>
-      <c r="K30">
-        <v>5.8</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>1.89</v>
-      </c>
-      <c r="Q30">
-        <v>1.65</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>1.01</v>
-      </c>
-      <c r="U30">
-        <v>1.01</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>1000</v>
-      </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z30">
         <v>1000</v>
@@ -8097,13 +8115,13 @@
         <v>1000</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE30">
         <v>1000</v>
@@ -8112,7 +8130,7 @@
         <v>1000</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH30">
         <v>1000</v>
@@ -8139,58 +8157,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AQ30">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AR30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AS30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AT30">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AU30">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV30">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AW30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AX30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AY30">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="AZ30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BA30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BB30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BC30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BD30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BE30">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -8253,42 +8271,42 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8303,10 +8321,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q31">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8495,61 +8513,61 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F32">
+        <v>4.4</v>
+      </c>
+      <c r="G32">
+        <v>6</v>
+      </c>
+      <c r="H32">
+        <v>1.66</v>
+      </c>
+      <c r="I32">
+        <v>1.86</v>
+      </c>
+      <c r="J32">
+        <v>3.9</v>
+      </c>
+      <c r="K32">
+        <v>5.9</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>2.14</v>
+      </c>
+      <c r="Q32">
         <v>1.65</v>
       </c>
-      <c r="G32">
-        <v>1.9</v>
-      </c>
-      <c r="H32">
-        <v>4</v>
-      </c>
-      <c r="I32">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J32">
-        <v>3.6</v>
-      </c>
-      <c r="K32">
-        <v>7</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>1.81</v>
-      </c>
-      <c r="Q32">
-        <v>1.73</v>
-      </c>
       <c r="R32">
         <v>0</v>
       </c>
@@ -8557,10 +8575,10 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -8569,112 +8587,112 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
         <v>0</v>
@@ -8737,42 +8755,42 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
         <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F33">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -8787,10 +8805,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q33">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -8979,42 +8997,42 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F34">
-        <v>1.15</v>
+        <v>1.86</v>
       </c>
       <c r="G34">
-        <v>1.32</v>
+        <v>2.18</v>
       </c>
       <c r="H34">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I34">
-        <v>85</v>
+        <v>6.4</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="K34">
-        <v>880</v>
+        <v>4.5</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9029,10 +9047,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q34">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9221,48 +9239,48 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F35">
-        <v>2.96</v>
+        <v>2.26</v>
       </c>
       <c r="G35">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="H35">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="I35">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K35">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -9271,10 +9289,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="Q35">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9283,10 +9301,10 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -9295,112 +9313,112 @@
         <v>0</v>
       </c>
       <c r="X35">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AQ35">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AR35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS35">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AT35">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU35">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AV35">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AW35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX35">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY35">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ35">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BA35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BG35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH35">
         <v>0</v>
@@ -9463,42 +9481,42 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
         <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F36">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="G36">
-        <v>2.52</v>
+        <v>1.32</v>
       </c>
       <c r="H36">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="I36">
-        <v>3.65</v>
+        <v>90</v>
       </c>
       <c r="J36">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="K36">
-        <v>5.3</v>
+        <v>880</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9513,10 +9531,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9705,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="CB36" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9713,40 +9731,40 @@
         <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F37">
+        <v>2.96</v>
+      </c>
+      <c r="G37">
+        <v>3.35</v>
+      </c>
+      <c r="H37">
         <v>2.62</v>
-      </c>
-      <c r="G37">
-        <v>17.5</v>
-      </c>
-      <c r="H37">
-        <v>1.11</v>
       </c>
       <c r="I37">
         <v>2.82</v>
       </c>
       <c r="J37">
-        <v>1.69</v>
+        <v>3.15</v>
       </c>
       <c r="K37">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -9755,10 +9773,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="Q37">
-        <v>1.26</v>
+        <v>2.16</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9767,10 +9785,10 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -9779,112 +9797,112 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BG37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BH37">
         <v>0</v>
@@ -9947,42 +9965,42 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F38">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="G38">
-        <v>1.62</v>
+        <v>2.54</v>
       </c>
       <c r="H38">
-        <v>5.9</v>
+        <v>2.74</v>
       </c>
       <c r="I38">
-        <v>34</v>
+        <v>3.35</v>
       </c>
       <c r="J38">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -9997,10 +10015,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="Q38">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10189,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="CB38" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10197,34 +10215,34 @@
         <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F39">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="G39">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H39">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="I39">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="J39">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K39">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10239,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>1.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q39">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10431,72 +10449,72 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F40">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="G40">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="I40">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="J40">
+        <v>4.9</v>
+      </c>
+      <c r="K40">
         <v>6.6</v>
       </c>
-      <c r="K40">
-        <v>7</v>
-      </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>2.66</v>
+        <v>2.06</v>
       </c>
       <c r="Q40">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R40">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -10505,166 +10523,166 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AL40">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN40">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AO40">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="AP40">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AQ40">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AR40">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AS40">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AT40">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AU40">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AV40">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AW40">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AX40">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AY40">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ40">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA40">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BB40">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC40">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD40">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE40">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BF40">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BG40">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BH40">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BI40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK40">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN40">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO40">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BP40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ40">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BR40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX40">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ40">
         <v>0</v>
@@ -10673,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10681,64 +10699,64 @@
         <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E41" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F41">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="G41">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="H41">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="I41">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J41">
+        <v>3.4</v>
+      </c>
+      <c r="K41">
         <v>3.65</v>
       </c>
-      <c r="K41">
-        <v>3.7</v>
-      </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R41">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -10747,366 +10765,366 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI41">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AL41">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN41">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AO41">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AP41">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ41">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR41">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AS41">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AT41">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU41">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV41">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW41">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AX41">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AY41">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ41">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA41">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB41">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BC41">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD41">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE41">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BF41">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BG41">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BH41">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BI41">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ41">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK41">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN41">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BO41">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ41">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT41">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BU41">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BV41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F42">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="G42">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="H42">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="I42">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="J42">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="K42">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M42">
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="O42">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P42">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q42">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="R42">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="S42">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T42">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="U42">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y42">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="Z42">
+        <v>1000</v>
+      </c>
+      <c r="AA42">
+        <v>1000</v>
+      </c>
+      <c r="AB42">
+        <v>10.5</v>
+      </c>
+      <c r="AC42">
+        <v>16</v>
+      </c>
+      <c r="AD42">
         <v>55</v>
       </c>
-      <c r="AA42">
-        <v>1000</v>
-      </c>
-      <c r="AB42">
+      <c r="AE42">
+        <v>1000</v>
+      </c>
+      <c r="AF42">
+        <v>8.4</v>
+      </c>
+      <c r="AG42">
+        <v>12</v>
+      </c>
+      <c r="AH42">
         <v>34</v>
       </c>
-      <c r="AC42">
-        <v>15</v>
-      </c>
-      <c r="AD42">
-        <v>60</v>
-      </c>
-      <c r="AE42">
-        <v>85</v>
-      </c>
-      <c r="AF42">
-        <v>42</v>
-      </c>
-      <c r="AG42">
+      <c r="AI42">
+        <v>1000</v>
+      </c>
+      <c r="AJ42">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK42">
+        <v>14.5</v>
+      </c>
+      <c r="AL42">
+        <v>40</v>
+      </c>
+      <c r="AM42">
+        <v>1000</v>
+      </c>
+      <c r="AN42">
+        <v>4.1</v>
+      </c>
+      <c r="AO42">
+        <v>340</v>
+      </c>
+      <c r="AP42">
+        <v>18.5</v>
+      </c>
+      <c r="AQ42">
+        <v>38</v>
+      </c>
+      <c r="AR42">
+        <v>12.5</v>
+      </c>
+      <c r="AS42">
+        <v>14</v>
+      </c>
+      <c r="AT42">
+        <v>9.4</v>
+      </c>
+      <c r="AU42">
+        <v>13.5</v>
+      </c>
+      <c r="AV42">
+        <v>27</v>
+      </c>
+      <c r="AW42">
+        <v>13</v>
+      </c>
+      <c r="AX42">
+        <v>7.6</v>
+      </c>
+      <c r="AY42">
         <v>10.5</v>
       </c>
-      <c r="AH42">
-        <v>60</v>
-      </c>
-      <c r="AI42">
-        <v>70</v>
-      </c>
-      <c r="AJ42">
-        <v>34</v>
-      </c>
-      <c r="AK42">
-        <v>970</v>
-      </c>
-      <c r="AL42">
-        <v>42</v>
-      </c>
-      <c r="AM42">
-        <v>660</v>
-      </c>
-      <c r="AN42">
-        <v>15</v>
-      </c>
-      <c r="AO42">
-        <v>50</v>
-      </c>
-      <c r="AP42">
-        <v>17.5</v>
-      </c>
-      <c r="AQ42">
-        <v>15.5</v>
-      </c>
-      <c r="AR42">
+      <c r="AZ42">
         <v>21</v>
       </c>
-      <c r="AS42">
-        <v>4.1</v>
-      </c>
-      <c r="AT42">
-        <v>11.5</v>
-      </c>
-      <c r="AU42">
-        <v>8</v>
-      </c>
-      <c r="AV42">
+      <c r="BA42">
         <v>13</v>
       </c>
-      <c r="AW42">
-        <v>23</v>
-      </c>
-      <c r="AX42">
-        <v>12</v>
-      </c>
-      <c r="AY42">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ42">
+      <c r="BB42">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC42">
         <v>12.5</v>
       </c>
-      <c r="BA42">
-        <v>24</v>
-      </c>
-      <c r="BB42">
-        <v>16.5</v>
-      </c>
-      <c r="BC42">
+      <c r="BD42">
+        <v>32</v>
+      </c>
+      <c r="BE42">
+        <v>13</v>
+      </c>
+      <c r="BF42">
+        <v>3.8</v>
+      </c>
+      <c r="BG42">
         <v>13.5</v>
-      </c>
-      <c r="BD42">
-        <v>18</v>
-      </c>
-      <c r="BE42">
-        <v>4.1</v>
-      </c>
-      <c r="BF42">
-        <v>8</v>
-      </c>
-      <c r="BG42">
-        <v>19.5</v>
       </c>
       <c r="BH42">
         <v>4.8</v>
       </c>
       <c r="BI42">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK42">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL42">
         <v>1000</v>
@@ -11115,16 +11133,16 @@
         <v>1.01</v>
       </c>
       <c r="BN42">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="BO42">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="BP42">
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR42">
         <v>1000</v>
@@ -11133,10 +11151,10 @@
         <v>1.01</v>
       </c>
       <c r="BT42">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU42">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV42">
         <v>1000</v>
@@ -11151,78 +11169,78 @@
         <v>1.01</v>
       </c>
       <c r="BZ42">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F43">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="G43">
-        <v>2.94</v>
+        <v>2.42</v>
       </c>
       <c r="H43">
         <v>3.15</v>
       </c>
       <c r="I43">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J43">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K43">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P43">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q43">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11231,417 +11249,901 @@
         <v>0</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH43">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI43">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN43">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP43">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU43">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV43">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX43">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY43">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ43">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA43">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC43">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE43">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF43">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH43">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ43">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK43">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN43">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO43">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BR43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT43">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU43">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB43" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E44" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F44">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="G44">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="H44">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="I44">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="J44">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="K44">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M44">
         <v>1.04</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P44">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="Q44">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T44">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="U44">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y44">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z44">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA44">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB44">
         <v>14</v>
       </c>
       <c r="AC44">
+        <v>15.5</v>
+      </c>
+      <c r="AD44">
+        <v>17</v>
+      </c>
+      <c r="AE44">
+        <v>42</v>
+      </c>
+      <c r="AF44">
+        <v>15.5</v>
+      </c>
+      <c r="AG44">
+        <v>10.5</v>
+      </c>
+      <c r="AH44">
+        <v>16</v>
+      </c>
+      <c r="AI44">
+        <v>44</v>
+      </c>
+      <c r="AJ44">
+        <v>24</v>
+      </c>
+      <c r="AK44">
+        <v>19</v>
+      </c>
+      <c r="AL44">
+        <v>28</v>
+      </c>
+      <c r="AM44">
+        <v>75</v>
+      </c>
+      <c r="AN44">
+        <v>15</v>
+      </c>
+      <c r="AO44">
+        <v>30</v>
+      </c>
+      <c r="AP44">
+        <v>21</v>
+      </c>
+      <c r="AQ44">
+        <v>17.5</v>
+      </c>
+      <c r="AR44">
         <v>20</v>
       </c>
-      <c r="AD44">
-        <v>1000</v>
-      </c>
-      <c r="AE44">
-        <v>1000</v>
-      </c>
-      <c r="AF44">
+      <c r="AS44">
+        <v>10</v>
+      </c>
+      <c r="AT44">
+        <v>11.5</v>
+      </c>
+      <c r="AU44">
+        <v>8.6</v>
+      </c>
+      <c r="AV44">
         <v>14</v>
       </c>
-      <c r="AG44">
+      <c r="AW44">
+        <v>23</v>
+      </c>
+      <c r="AX44">
+        <v>13</v>
+      </c>
+      <c r="AY44">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ44">
+        <v>13.5</v>
+      </c>
+      <c r="BA44">
+        <v>24</v>
+      </c>
+      <c r="BB44">
+        <v>20</v>
+      </c>
+      <c r="BC44">
+        <v>15.5</v>
+      </c>
+      <c r="BD44">
+        <v>18.5</v>
+      </c>
+      <c r="BE44">
+        <v>30</v>
+      </c>
+      <c r="BF44">
+        <v>8.6</v>
+      </c>
+      <c r="BG44">
+        <v>19</v>
+      </c>
+      <c r="BH44">
+        <v>4.8</v>
+      </c>
+      <c r="BI44">
+        <v>3.45</v>
+      </c>
+      <c r="BJ44">
+        <v>13</v>
+      </c>
+      <c r="BK44">
+        <v>6.4</v>
+      </c>
+      <c r="BL44">
+        <v>1000</v>
+      </c>
+      <c r="BM44">
+        <v>1.01</v>
+      </c>
+      <c r="BN44">
+        <v>5.9</v>
+      </c>
+      <c r="BO44">
+        <v>4</v>
+      </c>
+      <c r="BP44">
+        <v>1000</v>
+      </c>
+      <c r="BQ44">
+        <v>8.6</v>
+      </c>
+      <c r="BR44">
+        <v>1000</v>
+      </c>
+      <c r="BS44">
+        <v>1.01</v>
+      </c>
+      <c r="BT44">
+        <v>10.5</v>
+      </c>
+      <c r="BU44">
+        <v>5.7</v>
+      </c>
+      <c r="BV44">
+        <v>1000</v>
+      </c>
+      <c r="BW44">
+        <v>1.01</v>
+      </c>
+      <c r="BX44">
+        <v>1000</v>
+      </c>
+      <c r="BY44">
+        <v>1.01</v>
+      </c>
+      <c r="BZ44">
+        <v>1000</v>
+      </c>
+      <c r="CA44">
+        <v>1.01</v>
+      </c>
+      <c r="CB44" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:80">
+      <c r="A45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" t="s">
+        <v>219</v>
+      </c>
+      <c r="F45">
+        <v>2.24</v>
+      </c>
+      <c r="G45">
+        <v>2.94</v>
+      </c>
+      <c r="H45">
+        <v>3.15</v>
+      </c>
+      <c r="I45">
+        <v>3.95</v>
+      </c>
+      <c r="J45">
+        <v>2.9</v>
+      </c>
+      <c r="K45">
+        <v>3.35</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>1.25</v>
+      </c>
+      <c r="Q45">
+        <v>2.28</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
+        <v>0</v>
+      </c>
+      <c r="AP45">
+        <v>0</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45">
+        <v>0</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45">
+        <v>0</v>
+      </c>
+      <c r="AX45">
+        <v>0</v>
+      </c>
+      <c r="AY45">
+        <v>0</v>
+      </c>
+      <c r="AZ45">
+        <v>0</v>
+      </c>
+      <c r="BA45">
+        <v>0</v>
+      </c>
+      <c r="BB45">
+        <v>0</v>
+      </c>
+      <c r="BC45">
+        <v>0</v>
+      </c>
+      <c r="BD45">
+        <v>0</v>
+      </c>
+      <c r="BE45">
+        <v>0</v>
+      </c>
+      <c r="BF45">
+        <v>0</v>
+      </c>
+      <c r="BG45">
+        <v>0</v>
+      </c>
+      <c r="BH45">
+        <v>0</v>
+      </c>
+      <c r="BI45">
+        <v>0</v>
+      </c>
+      <c r="BJ45">
+        <v>0</v>
+      </c>
+      <c r="BK45">
+        <v>0</v>
+      </c>
+      <c r="BL45">
+        <v>0</v>
+      </c>
+      <c r="BM45">
+        <v>0</v>
+      </c>
+      <c r="BN45">
+        <v>0</v>
+      </c>
+      <c r="BO45">
+        <v>0</v>
+      </c>
+      <c r="BP45">
+        <v>0</v>
+      </c>
+      <c r="BQ45">
+        <v>0</v>
+      </c>
+      <c r="BR45">
+        <v>0</v>
+      </c>
+      <c r="BS45">
+        <v>0</v>
+      </c>
+      <c r="BT45">
+        <v>0</v>
+      </c>
+      <c r="BU45">
+        <v>0</v>
+      </c>
+      <c r="BV45">
+        <v>0</v>
+      </c>
+      <c r="BW45">
+        <v>0</v>
+      </c>
+      <c r="BX45">
+        <v>0</v>
+      </c>
+      <c r="BY45">
+        <v>0</v>
+      </c>
+      <c r="BZ45">
+        <v>0</v>
+      </c>
+      <c r="CA45">
+        <v>0</v>
+      </c>
+      <c r="CB45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:80">
+      <c r="A46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
+        <v>220</v>
+      </c>
+      <c r="F46">
+        <v>1.45</v>
+      </c>
+      <c r="G46">
+        <v>1.54</v>
+      </c>
+      <c r="H46">
+        <v>6.8</v>
+      </c>
+      <c r="I46">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J46">
+        <v>4.7</v>
+      </c>
+      <c r="K46">
+        <v>5.7</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>1.04</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>2.06</v>
+      </c>
+      <c r="Q46">
+        <v>1.71</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>1.85</v>
+      </c>
+      <c r="U46">
+        <v>1.9</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>1000</v>
+      </c>
+      <c r="Y46">
+        <v>1000</v>
+      </c>
+      <c r="Z46">
+        <v>1000</v>
+      </c>
+      <c r="AA46">
+        <v>1000</v>
+      </c>
+      <c r="AB46">
+        <v>14</v>
+      </c>
+      <c r="AC46">
+        <v>20</v>
+      </c>
+      <c r="AD46">
+        <v>1000</v>
+      </c>
+      <c r="AE46">
+        <v>1000</v>
+      </c>
+      <c r="AF46">
+        <v>14</v>
+      </c>
+      <c r="AG46">
         <v>17</v>
       </c>
-      <c r="AH44">
-        <v>1000</v>
-      </c>
-      <c r="AI44">
-        <v>1000</v>
-      </c>
-      <c r="AJ44">
+      <c r="AH46">
+        <v>1000</v>
+      </c>
+      <c r="AI46">
+        <v>1000</v>
+      </c>
+      <c r="AJ46">
         <v>40</v>
       </c>
-      <c r="AK44">
-        <v>1000</v>
-      </c>
-      <c r="AL44">
-        <v>1000</v>
-      </c>
-      <c r="AM44">
-        <v>1000</v>
-      </c>
-      <c r="AN44">
+      <c r="AK46">
+        <v>1000</v>
+      </c>
+      <c r="AL46">
+        <v>1000</v>
+      </c>
+      <c r="AM46">
+        <v>1000</v>
+      </c>
+      <c r="AN46">
         <v>9.4</v>
       </c>
-      <c r="AO44">
-        <v>1000</v>
-      </c>
-      <c r="AP44">
+      <c r="AO46">
+        <v>1000</v>
+      </c>
+      <c r="AP46">
         <v>1.62</v>
       </c>
-      <c r="AQ44">
+      <c r="AQ46">
         <v>1.62</v>
       </c>
-      <c r="AR44">
+      <c r="AR46">
         <v>1.62</v>
       </c>
-      <c r="AS44">
+      <c r="AS46">
         <v>1.62</v>
       </c>
-      <c r="AT44">
+      <c r="AT46">
         <v>6.4</v>
       </c>
-      <c r="AU44">
+      <c r="AU46">
         <v>7.6</v>
       </c>
-      <c r="AV44">
+      <c r="AV46">
         <v>1.62</v>
       </c>
-      <c r="AW44">
+      <c r="AW46">
         <v>1.62</v>
       </c>
-      <c r="AX44">
+      <c r="AX46">
         <v>6.4</v>
       </c>
-      <c r="AY44">
+      <c r="AY46">
         <v>7.2</v>
       </c>
-      <c r="AZ44">
+      <c r="AZ46">
         <v>1.62</v>
       </c>
-      <c r="BA44">
+      <c r="BA46">
         <v>1.62</v>
       </c>
-      <c r="BB44">
+      <c r="BB46">
         <v>1.55</v>
       </c>
-      <c r="BC44">
+      <c r="BC46">
         <v>1.62</v>
       </c>
-      <c r="BD44">
+      <c r="BD46">
         <v>1.62</v>
       </c>
-      <c r="BE44">
+      <c r="BE46">
         <v>1.62</v>
       </c>
-      <c r="BF44">
+      <c r="BF46">
         <v>5.4</v>
       </c>
-      <c r="BG44">
+      <c r="BG46">
         <v>1.62</v>
       </c>
-      <c r="BH44">
-        <v>0</v>
-      </c>
-      <c r="BI44">
-        <v>0</v>
-      </c>
-      <c r="BJ44">
-        <v>0</v>
-      </c>
-      <c r="BK44">
-        <v>0</v>
-      </c>
-      <c r="BL44">
-        <v>0</v>
-      </c>
-      <c r="BM44">
-        <v>0</v>
-      </c>
-      <c r="BN44">
-        <v>0</v>
-      </c>
-      <c r="BO44">
-        <v>0</v>
-      </c>
-      <c r="BP44">
-        <v>0</v>
-      </c>
-      <c r="BQ44">
-        <v>0</v>
-      </c>
-      <c r="BR44">
-        <v>0</v>
-      </c>
-      <c r="BS44">
-        <v>0</v>
-      </c>
-      <c r="BT44">
-        <v>0</v>
-      </c>
-      <c r="BU44">
-        <v>0</v>
-      </c>
-      <c r="BV44">
-        <v>0</v>
-      </c>
-      <c r="BW44">
-        <v>0</v>
-      </c>
-      <c r="BX44">
-        <v>0</v>
-      </c>
-      <c r="BY44">
-        <v>0</v>
-      </c>
-      <c r="BZ44">
-        <v>0</v>
-      </c>
-      <c r="CA44">
-        <v>0</v>
-      </c>
-      <c r="CB44" t="s">
-        <v>215</v>
+      <c r="BH46">
+        <v>0</v>
+      </c>
+      <c r="BI46">
+        <v>0</v>
+      </c>
+      <c r="BJ46">
+        <v>0</v>
+      </c>
+      <c r="BK46">
+        <v>0</v>
+      </c>
+      <c r="BL46">
+        <v>0</v>
+      </c>
+      <c r="BM46">
+        <v>0</v>
+      </c>
+      <c r="BN46">
+        <v>0</v>
+      </c>
+      <c r="BO46">
+        <v>0</v>
+      </c>
+      <c r="BP46">
+        <v>0</v>
+      </c>
+      <c r="BQ46">
+        <v>0</v>
+      </c>
+      <c r="BR46">
+        <v>0</v>
+      </c>
+      <c r="BS46">
+        <v>0</v>
+      </c>
+      <c r="BT46">
+        <v>0</v>
+      </c>
+      <c r="BU46">
+        <v>0</v>
+      </c>
+      <c r="BV46">
+        <v>0</v>
+      </c>
+      <c r="BW46">
+        <v>0</v>
+      </c>
+      <c r="BX46">
+        <v>0</v>
+      </c>
+      <c r="BY46">
+        <v>0</v>
+      </c>
+      <c r="BZ46">
+        <v>0</v>
+      </c>
+      <c r="CA46">
+        <v>0</v>
+      </c>
+      <c r="CB46" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -679,7 +679,7 @@
     <t>Estoril Praia</t>
   </si>
   <si>
-    <t>2026-09-12 11:31:29</t>
+    <t>2026-09-12 13:58:53</t>
   </si>
 </sst>
 </file>
@@ -1273,10 +1273,10 @@
         <v>176</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H2">
         <v>3.5</v>
@@ -1285,25 +1285,25 @@
         <v>3.85</v>
       </c>
       <c r="J2">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
         <v>2.02</v>
@@ -1324,7 +1324,7 @@
         <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1515,22 +1515,22 @@
         <v>177</v>
       </c>
       <c r="F3">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
         <v>2.92</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
         <v>1.64</v>
@@ -1539,124 +1539,124 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
         <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>1.15</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
         <v>1.68</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
         <v>1.54</v>
       </c>
       <c r="X3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA3">
-        <v>630</v>
+        <v>420</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AF3">
+        <v>16</v>
+      </c>
+      <c r="AG3">
         <v>17.5</v>
       </c>
-      <c r="AG3">
-        <v>16</v>
-      </c>
       <c r="AH3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AI3">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="AJ3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AK3">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AL3">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="AO3">
-        <v>980</v>
+        <v>920</v>
       </c>
       <c r="AP3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
       </c>
       <c r="AV3">
+        <v>13.5</v>
+      </c>
+      <c r="AW3">
+        <v>28</v>
+      </c>
+      <c r="AX3">
         <v>13</v>
       </c>
-      <c r="AW3">
-        <v>5</v>
-      </c>
-      <c r="AX3">
+      <c r="AY3">
         <v>12.5</v>
       </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
       <c r="AZ3">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="BB3">
         <v>24</v>
@@ -1665,16 +1665,16 @@
         <v>25</v>
       </c>
       <c r="BD3">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BE3">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="BF3">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="BG3">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BH3">
         <v>2.56</v>
@@ -1757,13 +1757,13 @@
         <v>178</v>
       </c>
       <c r="F4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
         <v>3.8</v>
@@ -1772,7 +1772,7 @@
         <v>3.85</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
         <v>1.28</v>
@@ -1781,7 +1781,7 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O4">
         <v>1.22</v>
@@ -1793,34 +1793,34 @@
         <v>1.65</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S4">
         <v>2.58</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U4">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB4">
         <v>13</v>
@@ -1829,55 +1829,55 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF4">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN4">
         <v>11</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP4">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
         <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>1.95</v>
+        <v>6.2</v>
       </c>
       <c r="AS4">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AU4">
         <v>8.4</v>
@@ -1886,7 +1886,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="AX4">
         <v>13.5</v>
@@ -1898,19 +1898,19 @@
         <v>14</v>
       </c>
       <c r="BA4">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="BC4">
         <v>17</v>
       </c>
       <c r="BD4">
-        <v>2.06</v>
+        <v>6</v>
       </c>
       <c r="BE4">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
         <v>9.800000000000001</v>
@@ -1999,22 +1999,22 @@
         <v>179</v>
       </c>
       <c r="F5">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G5">
         <v>2.86</v>
       </c>
       <c r="H5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.27</v>
@@ -2038,127 +2038,127 @@
         <v>1.72</v>
       </c>
       <c r="S5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T5">
         <v>1.5</v>
       </c>
       <c r="U5">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X5">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AA5">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AB5">
-        <v>60</v>
+        <v>19.5</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>13</v>
       </c>
       <c r="AE5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF5">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AG5">
+        <v>13.5</v>
+      </c>
+      <c r="AH5">
         <v>14</v>
       </c>
-      <c r="AH5">
-        <v>14.5</v>
-      </c>
       <c r="AI5">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AJ5">
         <v>110</v>
       </c>
       <c r="AK5">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM5">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO5">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AP5">
+        <v>22</v>
+      </c>
+      <c r="AQ5">
+        <v>15.5</v>
+      </c>
+      <c r="AR5">
+        <v>18</v>
+      </c>
+      <c r="AS5">
+        <v>23</v>
+      </c>
+      <c r="AT5">
+        <v>16.5</v>
+      </c>
+      <c r="AU5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV5">
+        <v>11</v>
+      </c>
+      <c r="AW5">
+        <v>19.5</v>
+      </c>
+      <c r="AX5">
+        <v>19.5</v>
+      </c>
+      <c r="AY5">
+        <v>12</v>
+      </c>
+      <c r="AZ5">
+        <v>12.5</v>
+      </c>
+      <c r="BA5">
         <v>19</v>
       </c>
-      <c r="AQ5">
-        <v>15</v>
-      </c>
-      <c r="AR5">
-        <v>15</v>
-      </c>
-      <c r="AS5">
-        <v>13</v>
-      </c>
-      <c r="AT5">
-        <v>14.5</v>
-      </c>
-      <c r="AU5">
-        <v>8.6</v>
-      </c>
-      <c r="AV5">
-        <v>10.5</v>
-      </c>
-      <c r="AW5">
-        <v>16</v>
-      </c>
-      <c r="AX5">
-        <v>16.5</v>
-      </c>
-      <c r="AY5">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5">
-        <v>12</v>
-      </c>
-      <c r="BA5">
-        <v>18</v>
-      </c>
       <c r="BB5">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE5">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH5">
         <v>5.6</v>
@@ -2188,7 +2188,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -2241,166 +2241,166 @@
         <v>180</v>
       </c>
       <c r="F6">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
         <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
         <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
         <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S6">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC6">
+        <v>11</v>
+      </c>
+      <c r="AD6">
+        <v>26</v>
+      </c>
+      <c r="AE6">
+        <v>110</v>
+      </c>
+      <c r="AF6">
+        <v>10</v>
+      </c>
+      <c r="AG6">
+        <v>10.5</v>
+      </c>
+      <c r="AH6">
         <v>22</v>
       </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>16.5</v>
-      </c>
-      <c r="AG6">
-        <v>18</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AK6">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP6">
-        <v>1.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6">
-        <v>1.6</v>
+        <v>21</v>
       </c>
       <c r="AR6">
-        <v>1.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS6">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT6">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU6">
+        <v>9.6</v>
+      </c>
+      <c r="AV6">
         <v>7.6</v>
       </c>
-      <c r="AV6">
-        <v>1.6</v>
-      </c>
       <c r="AW6">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="AX6">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AY6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>1.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="BB6">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC6">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BD6">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="BF6">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="BH6">
         <v>4.5</v>
@@ -2409,7 +2409,7 @@
         <v>3.25</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BK6">
         <v>7.4</v>
@@ -2483,22 +2483,22 @@
         <v>181</v>
       </c>
       <c r="F7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G7">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="H7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="I7">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2531,7 +2531,7 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W7">
         <v>1.21</v>
@@ -2725,22 +2725,22 @@
         <v>182</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>1.53</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
-        <v>890</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2749,22 +2749,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q8">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>2.52</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2773,10 +2773,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2881,7 +2881,7 @@
         <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
@@ -2908,7 +2908,7 @@
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP8">
         <v>1000</v>
@@ -2976,7 +2976,7 @@
         <v>3.3</v>
       </c>
       <c r="I9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J9">
         <v>2.4</v>
@@ -2991,10 +2991,10 @@
         <v>1.18</v>
       </c>
       <c r="N9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P9">
         <v>1.31</v>
@@ -3003,10 +3003,10 @@
         <v>3.2</v>
       </c>
       <c r="R9">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
         <v>2.26</v>
@@ -3087,7 +3087,7 @@
         <v>1.84</v>
       </c>
       <c r="AT9">
-        <v>1.59</v>
+        <v>6</v>
       </c>
       <c r="AU9">
         <v>1.46</v>
@@ -3132,7 +3132,7 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3209,226 +3209,226 @@
         <v>184</v>
       </c>
       <c r="F10">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="G10">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="H10">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="I10">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="J10">
         <v>3.8</v>
       </c>
       <c r="K10">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P10">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>221</v>
@@ -3451,34 +3451,34 @@
         <v>185</v>
       </c>
       <c r="F11">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="G11">
         <v>1.86</v>
       </c>
       <c r="H11">
+        <v>4.5</v>
+      </c>
+      <c r="I11">
+        <v>6.2</v>
+      </c>
+      <c r="J11">
         <v>3.2</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>6.6</v>
       </c>
-      <c r="J11">
-        <v>2.16</v>
-      </c>
-      <c r="K11">
-        <v>8</v>
-      </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P11">
         <v>2</v>
@@ -3487,190 +3487,190 @@
         <v>1.79</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>221</v>
@@ -3696,223 +3696,223 @@
         <v>1.04</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>1.23</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="K12">
         <v>900</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P12">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
         <v>221</v>
@@ -3935,226 +3935,226 @@
         <v>187</v>
       </c>
       <c r="F13">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H13">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I13">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J13">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K13">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
         <v>1.69</v>
       </c>
       <c r="Q13">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>221</v>
@@ -4177,10 +4177,10 @@
         <v>188</v>
       </c>
       <c r="F14">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H14">
         <v>1.96</v>
@@ -4189,214 +4189,214 @@
         <v>2.6</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P14">
         <v>1.68</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>221</v>
@@ -4419,226 +4419,226 @@
         <v>189</v>
       </c>
       <c r="F15">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="G15">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="H15">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J15">
         <v>3.35</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P15">
         <v>1.68</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>221</v>
@@ -4679,7 +4679,7 @@
         <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M16">
         <v>1.06</v>
@@ -4688,19 +4688,19 @@
         <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P16">
         <v>2.2</v>
       </c>
       <c r="Q16">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T16">
         <v>1.88</v>
@@ -4715,13 +4715,13 @@
         <v>1.17</v>
       </c>
       <c r="X16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y16">
         <v>9.199999999999999</v>
       </c>
       <c r="Z16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA16">
         <v>15</v>
@@ -4733,46 +4733,46 @@
         <v>9.6</v>
       </c>
       <c r="AD16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE16">
         <v>16.5</v>
       </c>
       <c r="AF16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH16">
         <v>21</v>
       </c>
       <c r="AI16">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO16">
+        <v>8.4</v>
+      </c>
+      <c r="AP16">
+        <v>15</v>
+      </c>
+      <c r="AQ16">
         <v>8.6</v>
-      </c>
-      <c r="AP16">
-        <v>14.5</v>
-      </c>
-      <c r="AQ16">
-        <v>8.199999999999999</v>
       </c>
       <c r="AR16">
         <v>9</v>
@@ -4781,28 +4781,28 @@
         <v>13.5</v>
       </c>
       <c r="AT16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16">
         <v>9</v>
       </c>
       <c r="AW16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX16">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AY16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA16">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BB16">
         <v>44</v>
@@ -4820,13 +4820,13 @@
         <v>38</v>
       </c>
       <c r="BG16">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH16">
         <v>4.3</v>
       </c>
       <c r="BI16">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ16">
         <v>12.5</v>
@@ -4838,7 +4838,7 @@
         <v>160</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BN16">
         <v>12</v>
@@ -4906,22 +4906,22 @@
         <v>1.24</v>
       </c>
       <c r="G17">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H17">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="J17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M17">
         <v>1.04</v>
@@ -4939,13 +4939,13 @@
         <v>1.69</v>
       </c>
       <c r="R17">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S17">
         <v>2.76</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U17">
         <v>1.61</v>
@@ -4954,19 +4954,19 @@
         <v>1.05</v>
       </c>
       <c r="W17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y17">
         <v>50</v>
       </c>
       <c r="Z17">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB17">
         <v>8.4</v>
@@ -4975,10 +4975,10 @@
         <v>16</v>
       </c>
       <c r="AD17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE17">
-        <v>470</v>
+        <v>390</v>
       </c>
       <c r="AF17">
         <v>7.2</v>
@@ -4987,52 +4987,52 @@
         <v>12</v>
       </c>
       <c r="AH17">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI17">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AJ17">
         <v>8.4</v>
       </c>
       <c r="AK17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL17">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM17">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AN17">
         <v>4.6</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AP17">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ17">
         <v>38</v>
       </c>
       <c r="AR17">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="AS17">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AT17">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU17">
         <v>14.5</v>
       </c>
       <c r="AV17">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="AW17">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AX17">
         <v>6.4</v>
@@ -5044,25 +5044,25 @@
         <v>36</v>
       </c>
       <c r="BA17">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BB17">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC17">
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BE17">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BF17">
         <v>4.2</v>
       </c>
       <c r="BG17">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="BH17">
         <v>4.3</v>
@@ -5080,16 +5080,16 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BN17">
         <v>3.85</v>
       </c>
       <c r="BO17">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BP17">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT17">
         <v>1000</v>
@@ -5110,13 +5110,13 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5148,163 +5148,163 @@
         <v>6.2</v>
       </c>
       <c r="G18">
+        <v>6.8</v>
+      </c>
+      <c r="H18">
+        <v>1.58</v>
+      </c>
+      <c r="I18">
+        <v>1.6</v>
+      </c>
+      <c r="J18">
+        <v>4.6</v>
+      </c>
+      <c r="K18">
+        <v>4.7</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1.05</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>2.18</v>
+      </c>
+      <c r="Q18">
+        <v>1.78</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1.87</v>
+      </c>
+      <c r="U18">
+        <v>2.04</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>19.5</v>
+      </c>
+      <c r="Y18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z18">
+        <v>10.5</v>
+      </c>
+      <c r="AA18">
+        <v>15.5</v>
+      </c>
+      <c r="AB18">
+        <v>24</v>
+      </c>
+      <c r="AC18">
+        <v>10.5</v>
+      </c>
+      <c r="AD18">
+        <v>10.5</v>
+      </c>
+      <c r="AE18">
+        <v>17.5</v>
+      </c>
+      <c r="AF18">
+        <v>65</v>
+      </c>
+      <c r="AG18">
+        <v>26</v>
+      </c>
+      <c r="AH18">
+        <v>22</v>
+      </c>
+      <c r="AI18">
+        <v>36</v>
+      </c>
+      <c r="AJ18">
+        <v>200</v>
+      </c>
+      <c r="AK18">
+        <v>100</v>
+      </c>
+      <c r="AL18">
+        <v>95</v>
+      </c>
+      <c r="AM18">
+        <v>130</v>
+      </c>
+      <c r="AN18">
+        <v>120</v>
+      </c>
+      <c r="AO18">
+        <v>8</v>
+      </c>
+      <c r="AP18">
+        <v>16.5</v>
+      </c>
+      <c r="AQ18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR18">
+        <v>9</v>
+      </c>
+      <c r="AS18">
+        <v>13</v>
+      </c>
+      <c r="AT18">
+        <v>19</v>
+      </c>
+      <c r="AU18">
+        <v>9</v>
+      </c>
+      <c r="AV18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW18">
+        <v>14</v>
+      </c>
+      <c r="AX18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY18">
+        <v>20</v>
+      </c>
+      <c r="AZ18">
+        <v>17.5</v>
+      </c>
+      <c r="BA18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB18">
+        <v>10</v>
+      </c>
+      <c r="BC18">
+        <v>9.6</v>
+      </c>
+      <c r="BD18">
+        <v>9.6</v>
+      </c>
+      <c r="BE18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG18">
         <v>7</v>
-      </c>
-      <c r="H18">
-        <v>1.56</v>
-      </c>
-      <c r="I18">
-        <v>1.59</v>
-      </c>
-      <c r="J18">
-        <v>4.7</v>
-      </c>
-      <c r="K18">
-        <v>4.8</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>1.04</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>2.02</v>
-      </c>
-      <c r="Q18">
-        <v>1.7</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>1.8</v>
-      </c>
-      <c r="U18">
-        <v>1.87</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>970</v>
-      </c>
-      <c r="Z18">
-        <v>970</v>
-      </c>
-      <c r="AA18">
-        <v>970</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>970</v>
-      </c>
-      <c r="AD18">
-        <v>970</v>
-      </c>
-      <c r="AE18">
-        <v>970</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>1000</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>970</v>
-      </c>
-      <c r="AP18">
-        <v>11</v>
-      </c>
-      <c r="AQ18">
-        <v>6.8</v>
-      </c>
-      <c r="AR18">
-        <v>7</v>
-      </c>
-      <c r="AS18">
-        <v>1.53</v>
-      </c>
-      <c r="AT18">
-        <v>1.58</v>
-      </c>
-      <c r="AU18">
-        <v>7</v>
-      </c>
-      <c r="AV18">
-        <v>7.2</v>
-      </c>
-      <c r="AW18">
-        <v>1.55</v>
-      </c>
-      <c r="AX18">
-        <v>1.58</v>
-      </c>
-      <c r="AY18">
-        <v>1.58</v>
-      </c>
-      <c r="AZ18">
-        <v>1.58</v>
-      </c>
-      <c r="BA18">
-        <v>1.58</v>
-      </c>
-      <c r="BB18">
-        <v>1.58</v>
-      </c>
-      <c r="BC18">
-        <v>1.58</v>
-      </c>
-      <c r="BD18">
-        <v>1.58</v>
-      </c>
-      <c r="BE18">
-        <v>1.58</v>
-      </c>
-      <c r="BF18">
-        <v>1.58</v>
-      </c>
-      <c r="BG18">
-        <v>6</v>
       </c>
       <c r="BH18">
         <v>0</v>
@@ -5390,19 +5390,19 @@
         <v>1.43</v>
       </c>
       <c r="G19">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="H19">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I19">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="J19">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q19">
         <v>1.67</v>
@@ -5429,10 +5429,10 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U19">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5632,19 +5632,19 @@
         <v>2.62</v>
       </c>
       <c r="G20">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="H20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I20">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K20">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5662,7 +5662,7 @@
         <v>1.91</v>
       </c>
       <c r="Q20">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5871,22 +5871,22 @@
         <v>195</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G21">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="H21">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="I21">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>1.94</v>
       </c>
       <c r="Q21">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6113,22 +6113,22 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="G22">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="I22">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="J22">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6143,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="Q22">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6355,22 +6355,22 @@
         <v>197</v>
       </c>
       <c r="F23">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G23">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="H23">
         <v>4.8</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K23">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q23">
         <v>1.63</v>
@@ -6597,22 +6597,22 @@
         <v>198</v>
       </c>
       <c r="F24">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G24">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I24">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J24">
         <v>3.15</v>
       </c>
       <c r="K24">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6630,7 +6630,7 @@
         <v>1.57</v>
       </c>
       <c r="Q24">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -7081,22 +7081,22 @@
         <v>200</v>
       </c>
       <c r="F26">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H26">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I26">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J26">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K26">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>2.06</v>
       </c>
       <c r="Q26">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7323,19 +7323,19 @@
         <v>201</v>
       </c>
       <c r="F27">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G27">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="H27">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="I27">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J27">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K27">
         <v>4.5</v>
@@ -7353,7 +7353,7 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q27">
         <v>1.57</v>
@@ -7565,22 +7565,22 @@
         <v>202</v>
       </c>
       <c r="F28">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>1.21</v>
       </c>
       <c r="H28">
-        <v>1.05</v>
+        <v>15.5</v>
       </c>
       <c r="I28">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J28">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7810,19 +7810,19 @@
         <v>3.35</v>
       </c>
       <c r="G29">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I29">
         <v>2.24</v>
       </c>
       <c r="J29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K29">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7837,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q29">
         <v>1.54</v>
@@ -8052,19 +8052,19 @@
         <v>2.66</v>
       </c>
       <c r="G30">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="H30">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I30">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J30">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8079,10 +8079,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8091,10 +8091,10 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="U30">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -8103,112 +8103,112 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Y30">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB30">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC30">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD30">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG30">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP30">
-        <v>1.42</v>
+        <v>8</v>
       </c>
       <c r="AQ30">
-        <v>1.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR30">
-        <v>1.58</v>
+        <v>16.5</v>
       </c>
       <c r="AS30">
-        <v>1.58</v>
+        <v>8</v>
       </c>
       <c r="AT30">
-        <v>1.41</v>
+        <v>7.4</v>
       </c>
       <c r="AU30">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV30">
-        <v>1.53</v>
+        <v>12</v>
       </c>
       <c r="AW30">
-        <v>1.58</v>
+        <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>1.58</v>
+        <v>14</v>
       </c>
       <c r="AY30">
-        <v>1.51</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
-        <v>1.58</v>
+        <v>16</v>
       </c>
       <c r="BA30">
-        <v>1.58</v>
+        <v>8</v>
       </c>
       <c r="BB30">
-        <v>1.58</v>
+        <v>7.8</v>
       </c>
       <c r="BC30">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="BD30">
-        <v>1.58</v>
+        <v>8</v>
       </c>
       <c r="BE30">
-        <v>1.58</v>
+        <v>8.6</v>
       </c>
       <c r="BF30">
-        <v>1.58</v>
+        <v>7.6</v>
       </c>
       <c r="BG30">
-        <v>1.58</v>
+        <v>8</v>
       </c>
       <c r="BH30">
         <v>0</v>
@@ -8291,22 +8291,22 @@
         <v>205</v>
       </c>
       <c r="F31">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G31">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H31">
+        <v>4.2</v>
+      </c>
+      <c r="I31">
+        <v>4.3</v>
+      </c>
+      <c r="J31">
+        <v>3.95</v>
+      </c>
+      <c r="K31">
         <v>4.1</v>
-      </c>
-      <c r="I31">
-        <v>4.5</v>
-      </c>
-      <c r="J31">
-        <v>3.65</v>
-      </c>
-      <c r="K31">
-        <v>4.8</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8324,7 +8324,7 @@
         <v>2.46</v>
       </c>
       <c r="Q31">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8539,7 +8539,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I32">
         <v>1.86</v>
@@ -8548,7 +8548,7 @@
         <v>3.9</v>
       </c>
       <c r="K32">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -9017,22 +9017,22 @@
         <v>208</v>
       </c>
       <c r="F34">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="G34">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H34">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I34">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J34">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K34">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q34">
         <v>1.76</v>
@@ -9259,16 +9259,16 @@
         <v>209</v>
       </c>
       <c r="F35">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G35">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H35">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="I35">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J35">
         <v>3.25</v>
@@ -9289,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q35">
         <v>1.57</v>
@@ -9504,19 +9504,19 @@
         <v>1.23</v>
       </c>
       <c r="G36">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="H36">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="I36">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="J36">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="K36">
-        <v>880</v>
+        <v>8</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9531,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="Q36">
         <v>1.58</v>
@@ -9746,19 +9746,19 @@
         <v>2.96</v>
       </c>
       <c r="G37">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="H37">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I37">
         <v>2.82</v>
       </c>
       <c r="J37">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K37">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9785,10 +9785,10 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U37">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -9797,112 +9797,112 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="Y37">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z37">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="AA37">
         <v>140</v>
       </c>
       <c r="AB37">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AC37">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD37">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE37">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG37">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AH37">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AI37">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK37">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL37">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM37">
         <v>1000</v>
       </c>
       <c r="AN37">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO37">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ37">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR37">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AS37">
-        <v>1.73</v>
+        <v>5.6</v>
       </c>
       <c r="AT37">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU37">
+        <v>6.8</v>
+      </c>
+      <c r="AV37">
+        <v>10.5</v>
+      </c>
+      <c r="AW37">
+        <v>5.6</v>
+      </c>
+      <c r="AX37">
+        <v>16.5</v>
+      </c>
+      <c r="AY37">
+        <v>11</v>
+      </c>
+      <c r="AZ37">
+        <v>4.8</v>
+      </c>
+      <c r="BA37">
+        <v>5.9</v>
+      </c>
+      <c r="BB37">
+        <v>5.9</v>
+      </c>
+      <c r="BC37">
+        <v>5.6</v>
+      </c>
+      <c r="BD37">
+        <v>5.9</v>
+      </c>
+      <c r="BE37">
+        <v>6.4</v>
+      </c>
+      <c r="BF37">
+        <v>5.6</v>
+      </c>
+      <c r="BG37">
         <v>5.5</v>
-      </c>
-      <c r="AV37">
-        <v>8.6</v>
-      </c>
-      <c r="AW37">
-        <v>1.75</v>
-      </c>
-      <c r="AX37">
-        <v>11</v>
-      </c>
-      <c r="AY37">
-        <v>9</v>
-      </c>
-      <c r="AZ37">
-        <v>1.63</v>
-      </c>
-      <c r="BA37">
-        <v>1.75</v>
-      </c>
-      <c r="BB37">
-        <v>1.75</v>
-      </c>
-      <c r="BC37">
-        <v>1.75</v>
-      </c>
-      <c r="BD37">
-        <v>1.75</v>
-      </c>
-      <c r="BE37">
-        <v>1.75</v>
-      </c>
-      <c r="BF37">
-        <v>1.75</v>
-      </c>
-      <c r="BG37">
-        <v>1.75</v>
       </c>
       <c r="BH37">
         <v>0</v>
@@ -9994,7 +9994,7 @@
         <v>2.74</v>
       </c>
       <c r="I38">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J38">
         <v>4</v>
@@ -10018,7 +10018,7 @@
         <v>2.72</v>
       </c>
       <c r="Q38">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10260,7 +10260,7 @@
         <v>3.05</v>
       </c>
       <c r="Q39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10469,7 +10469,7 @@
         <v>214</v>
       </c>
       <c r="F40">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="G40">
         <v>1.55</v>
@@ -10478,10 +10478,10 @@
         <v>5.9</v>
       </c>
       <c r="I40">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="J40">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K40">
         <v>6.6</v>
@@ -10502,7 +10502,7 @@
         <v>2.06</v>
       </c>
       <c r="Q40">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10711,7 +10711,7 @@
         <v>215</v>
       </c>
       <c r="F41">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="G41">
         <v>2.64</v>
@@ -10720,14 +10720,14 @@
         <v>2.9</v>
       </c>
       <c r="I41">
+        <v>3.3</v>
+      </c>
+      <c r="J41">
+        <v>3.35</v>
+      </c>
+      <c r="K41">
         <v>3.8</v>
       </c>
-      <c r="J41">
-        <v>3.4</v>
-      </c>
-      <c r="K41">
-        <v>3.65</v>
-      </c>
       <c r="L41">
         <v>0</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q41">
         <v>1.81</v>
@@ -10965,7 +10965,7 @@
         <v>15</v>
       </c>
       <c r="J42">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K42">
         <v>7</v>
@@ -10986,13 +10986,13 @@
         <v>2.66</v>
       </c>
       <c r="Q42">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R42">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S42">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T42">
         <v>2.12</v>
@@ -11043,7 +11043,7 @@
         <v>1000</v>
       </c>
       <c r="AJ42">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK42">
         <v>14.5</v>
@@ -11067,10 +11067,10 @@
         <v>38</v>
       </c>
       <c r="AR42">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="AS42">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="AT42">
         <v>9.4</v>
@@ -11082,7 +11082,7 @@
         <v>27</v>
       </c>
       <c r="AW42">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="AX42">
         <v>7.6</v>
@@ -11094,7 +11094,7 @@
         <v>21</v>
       </c>
       <c r="BA42">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="BB42">
         <v>8.800000000000001</v>
@@ -11106,13 +11106,13 @@
         <v>32</v>
       </c>
       <c r="BE42">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="BF42">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG42">
-        <v>13.5</v>
+        <v>95</v>
       </c>
       <c r="BH42">
         <v>4.8</v>
@@ -11222,7 +11222,7 @@
         <v>4.3</v>
       </c>
       <c r="O43">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P43">
         <v>2.12</v>
@@ -11240,7 +11240,7 @@
         <v>1.69</v>
       </c>
       <c r="U43">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11300,7 +11300,7 @@
         <v>17.5</v>
       </c>
       <c r="AO43">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP43">
         <v>15</v>
@@ -11336,19 +11336,19 @@
         <v>14.5</v>
       </c>
       <c r="BA43">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB43">
         <v>30</v>
       </c>
       <c r="BC43">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD43">
         <v>30</v>
       </c>
       <c r="BE43">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF43">
         <v>16</v>
@@ -11357,64 +11357,64 @@
         <v>25</v>
       </c>
       <c r="BH43">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI43">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BJ43">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK43">
+        <v>8</v>
+      </c>
+      <c r="BL43">
+        <v>120</v>
+      </c>
+      <c r="BM43">
+        <v>1.01</v>
+      </c>
+      <c r="BN43">
+        <v>5.4</v>
+      </c>
+      <c r="BO43">
+        <v>5</v>
+      </c>
+      <c r="BP43">
+        <v>18</v>
+      </c>
+      <c r="BQ43">
+        <v>15</v>
+      </c>
+      <c r="BR43">
+        <v>34</v>
+      </c>
+      <c r="BS43">
+        <v>21</v>
+      </c>
+      <c r="BT43">
         <v>6.4</v>
       </c>
-      <c r="BL43">
-        <v>1000</v>
-      </c>
-      <c r="BM43">
-        <v>1.01</v>
-      </c>
-      <c r="BN43">
-        <v>6.8</v>
-      </c>
-      <c r="BO43">
-        <v>4.4</v>
-      </c>
-      <c r="BP43">
-        <v>1000</v>
-      </c>
-      <c r="BQ43">
-        <v>10.5</v>
-      </c>
-      <c r="BR43">
-        <v>1000</v>
-      </c>
-      <c r="BS43">
-        <v>1.01</v>
-      </c>
-      <c r="BT43">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BU43">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV43">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW43">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BX43">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY43">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ43">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA43">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="CB43" t="s">
         <v>221</v>
@@ -11437,7 +11437,7 @@
         <v>218</v>
       </c>
       <c r="F44">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G44">
         <v>1.99</v>
@@ -11461,7 +11461,7 @@
         <v>1.04</v>
       </c>
       <c r="N44">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O44">
         <v>1.2</v>
@@ -11470,16 +11470,16 @@
         <v>2.52</v>
       </c>
       <c r="Q44">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R44">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S44">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T44">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U44">
         <v>2.62</v>
@@ -11494,7 +11494,7 @@
         <v>25</v>
       </c>
       <c r="Y44">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z44">
         <v>34</v>
@@ -11503,19 +11503,19 @@
         <v>85</v>
       </c>
       <c r="AB44">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC44">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD44">
         <v>17</v>
       </c>
       <c r="AE44">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF44">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG44">
         <v>10.5</v>
@@ -11530,16 +11530,16 @@
         <v>24</v>
       </c>
       <c r="AK44">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL44">
         <v>28</v>
       </c>
       <c r="AM44">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN44">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AO44">
         <v>30</v>
@@ -11554,10 +11554,10 @@
         <v>20</v>
       </c>
       <c r="AS44">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AT44">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU44">
         <v>8.6</v>
@@ -11572,10 +11572,10 @@
         <v>13</v>
       </c>
       <c r="AY44">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ44">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA44">
         <v>24</v>
@@ -11679,19 +11679,19 @@
         <v>219</v>
       </c>
       <c r="F45">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="G45">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="H45">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I45">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="J45">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K45">
         <v>3.35</v>
@@ -11712,7 +11712,7 @@
         <v>1.25</v>
       </c>
       <c r="Q45">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -11924,25 +11924,25 @@
         <v>1.45</v>
       </c>
       <c r="G46">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H46">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I46">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J46">
         <v>4.7</v>
       </c>
       <c r="K46">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -11963,10 +11963,10 @@
         <v>0</v>
       </c>
       <c r="T46">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="U46">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V46">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -706,7 +706,7 @@
     <t>Estoril Praia</t>
   </si>
   <si>
-    <t>2026-09-12 16:25:50</t>
+    <t>2026-09-12 19:01:10</t>
   </si>
 </sst>
 </file>
@@ -1300,10 +1300,10 @@
         <v>181</v>
       </c>
       <c r="F2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H2">
         <v>3.5</v>
@@ -1312,22 +1312,22 @@
         <v>3.85</v>
       </c>
       <c r="J2">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
         <v>1.77</v>
@@ -1336,130 +1336,130 @@
         <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T2">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="X2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB2">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AG2">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
+        <v>11</v>
+      </c>
+      <c r="AR2">
+        <v>18</v>
+      </c>
+      <c r="AS2">
+        <v>48</v>
+      </c>
+      <c r="AT2">
+        <v>8</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>13</v>
+      </c>
+      <c r="AW2">
+        <v>32</v>
+      </c>
+      <c r="AX2">
+        <v>12.5</v>
+      </c>
+      <c r="AY2">
         <v>9.6</v>
       </c>
-      <c r="AR2">
-        <v>1.01</v>
-      </c>
-      <c r="AS2">
-        <v>1.01</v>
-      </c>
-      <c r="AT2">
-        <v>7.8</v>
-      </c>
-      <c r="AU2">
-        <v>5.3</v>
-      </c>
-      <c r="AV2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW2">
-        <v>1.01</v>
-      </c>
-      <c r="AX2">
-        <v>9.6</v>
-      </c>
-      <c r="AY2">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1548,16 +1548,16 @@
         <v>2.84</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
         <v>3.4</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
         <v>1.64</v>
@@ -1569,25 +1569,25 @@
         <v>2.4</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
         <v>1.15</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V3">
         <v>1.42</v>
@@ -1596,7 +1596,7 @@
         <v>1.54</v>
       </c>
       <c r="X3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y3">
         <v>8.4</v>
@@ -1605,7 +1605,7 @@
         <v>20</v>
       </c>
       <c r="AA3">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AB3">
         <v>7.4</v>
@@ -1617,43 +1617,43 @@
         <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AF3">
         <v>16</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
         <v>32</v>
       </c>
       <c r="AI3">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="AJ3">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AK3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL3">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="AM3">
-        <v>890</v>
+        <v>770</v>
       </c>
       <c r="AN3">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AO3">
-        <v>920</v>
+        <v>880</v>
       </c>
       <c r="AP3">
         <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
         <v>17.5</v>
@@ -1680,7 +1680,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA3">
         <v>38</v>
@@ -1692,10 +1692,10 @@
         <v>25</v>
       </c>
       <c r="BD3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BF3">
         <v>28</v>
@@ -1713,7 +1713,7 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>3.8</v>
       </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
         <v>4.2</v>
@@ -1814,13 +1814,13 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
         <v>1.65</v>
       </c>
       <c r="R4">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
         <v>2.62</v>
@@ -1841,7 +1841,7 @@
         <v>23</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>32</v>
@@ -1856,7 +1856,7 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE4">
         <v>46</v>
@@ -1892,16 +1892,16 @@
         <v>34</v>
       </c>
       <c r="AP4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4">
         <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT4">
         <v>11</v>
@@ -1913,7 +1913,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX4">
         <v>13.5</v>
@@ -1925,19 +1925,19 @@
         <v>14</v>
       </c>
       <c r="BA4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC4">
         <v>17</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF4">
         <v>9.800000000000001</v>
@@ -2029,19 +2029,19 @@
         <v>2.76</v>
       </c>
       <c r="G5">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I5">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J5">
         <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.27</v>
@@ -2062,22 +2062,22 @@
         <v>1.53</v>
       </c>
       <c r="R5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T5">
         <v>1.5</v>
       </c>
       <c r="U5">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X5">
         <v>30</v>
@@ -2086,7 +2086,7 @@
         <v>18.5</v>
       </c>
       <c r="Z5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA5">
         <v>42</v>
@@ -2110,13 +2110,13 @@
         <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI5">
         <v>29</v>
       </c>
       <c r="AJ5">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AK5">
         <v>27</v>
@@ -2134,7 +2134,7 @@
         <v>12.5</v>
       </c>
       <c r="AP5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
         <v>15.5</v>
@@ -2143,7 +2143,7 @@
         <v>18</v>
       </c>
       <c r="AS5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AT5">
         <v>16.5</v>
@@ -2158,7 +2158,7 @@
         <v>19.5</v>
       </c>
       <c r="AX5">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AY5">
         <v>12</v>
@@ -2167,7 +2167,7 @@
         <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BB5">
         <v>25</v>
@@ -2268,13 +2268,13 @@
         <v>185</v>
       </c>
       <c r="F6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G6">
         <v>1.59</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -2292,16 +2292,16 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
         <v>1.24</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R6">
         <v>1.5</v>
@@ -2325,7 +2325,7 @@
         <v>21</v>
       </c>
       <c r="Y6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z6">
         <v>70</v>
@@ -2382,10 +2382,10 @@
         <v>21</v>
       </c>
       <c r="AR6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>8.6</v>
@@ -2397,7 +2397,7 @@
         <v>7.8</v>
       </c>
       <c r="AW6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX6">
         <v>9</v>
@@ -2418,16 +2418,16 @@
         <v>14</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
         <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
         <v>4.5</v>
@@ -2516,16 +2516,16 @@
         <v>5.6</v>
       </c>
       <c r="H7">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I7">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>3.1</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2546,7 +2546,7 @@
         <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S7">
         <v>3.5</v>
@@ -2752,7 +2752,7 @@
         <v>187</v>
       </c>
       <c r="F8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G8">
         <v>1.54</v>
@@ -2761,19 +2761,19 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
         <v>2.42</v>
@@ -2791,7 +2791,7 @@
         <v>1.37</v>
       </c>
       <c r="S8">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2800,7 +2800,7 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W8">
         <v>2.84</v>
@@ -2809,52 +2809,52 @@
         <v>1000</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE8">
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI8">
         <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO8">
         <v>1000</v>
@@ -2884,7 +2884,7 @@
         <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY8">
         <v>1.01</v>
@@ -2896,10 +2896,10 @@
         <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BD8">
         <v>1.01</v>
@@ -3018,10 +3018,10 @@
         <v>1.18</v>
       </c>
       <c r="N9">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="O9">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
         <v>1.31</v>
@@ -3260,13 +3260,13 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
         <v>1.3</v>
       </c>
       <c r="P10">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="Q10">
         <v>1.92</v>
@@ -3287,10 +3287,10 @@
         <v>1.19</v>
       </c>
       <c r="W10">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="X10">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Y10">
         <v>1000</v>
@@ -3362,7 +3362,7 @@
         <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
         <v>1.01</v>
@@ -3392,7 +3392,7 @@
         <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG10">
         <v>1.01</v>
@@ -3478,13 +3478,13 @@
         <v>190</v>
       </c>
       <c r="F11">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G11">
         <v>1.86</v>
       </c>
       <c r="H11">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I11">
         <v>6.2</v>
@@ -3493,7 +3493,7 @@
         <v>3.9</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3502,7 +3502,7 @@
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O11">
         <v>1.26</v>
@@ -3511,10 +3511,10 @@
         <v>2</v>
       </c>
       <c r="Q11">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
         <v>2.52</v>
@@ -3586,52 +3586,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3723,7 +3723,7 @@
         <v>1.1</v>
       </c>
       <c r="G12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="H12">
         <v>1.04</v>
@@ -3977,7 +3977,7 @@
         <v>2.92</v>
       </c>
       <c r="K13">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="L13">
         <v>1.33</v>
@@ -3986,22 +3986,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q13">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R13">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S13">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4458,7 +4458,7 @@
         <v>5.5</v>
       </c>
       <c r="J15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
         <v>3.8</v>
@@ -4467,16 +4467,16 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N15">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O15">
         <v>1.4</v>
       </c>
       <c r="P15">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q15">
         <v>2.14</v>
@@ -4485,16 +4485,16 @@
         <v>1.24</v>
       </c>
       <c r="S15">
-        <v>2.44</v>
+        <v>4</v>
       </c>
       <c r="T15">
         <v>1.96</v>
       </c>
       <c r="U15">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W15">
         <v>2</v>
@@ -4512,7 +4512,7 @@
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC15">
         <v>1000</v>
@@ -4521,7 +4521,7 @@
         <v>1000</v>
       </c>
       <c r="AE15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
         <v>1000</v>
@@ -4563,7 +4563,7 @@
         <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
         <v>5.7</v>
@@ -4599,7 +4599,7 @@
         <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>10</v>
@@ -4688,61 +4688,61 @@
         <v>195</v>
       </c>
       <c r="F16">
+        <v>6.2</v>
+      </c>
+      <c r="G16">
         <v>6.4</v>
       </c>
-      <c r="G16">
-        <v>6.6</v>
-      </c>
       <c r="H16">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I16">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J16">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M16">
         <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
         <v>1.27</v>
       </c>
       <c r="P16">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q16">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R16">
         <v>1.44</v>
       </c>
       <c r="S16">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T16">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U16">
         <v>2.04</v>
       </c>
       <c r="V16">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y16">
         <v>9.199999999999999</v>
@@ -4757,7 +4757,7 @@
         <v>23</v>
       </c>
       <c r="AC16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16">
         <v>10</v>
@@ -4835,7 +4835,7 @@
         <v>44</v>
       </c>
       <c r="BC16">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BD16">
         <v>36</v>
@@ -4930,16 +4930,16 @@
         <v>196</v>
       </c>
       <c r="F17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H17">
         <v>17</v>
       </c>
       <c r="I17">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -4954,7 +4954,7 @@
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>1.23</v>
@@ -4969,19 +4969,19 @@
         <v>1.53</v>
       </c>
       <c r="S17">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T17">
         <v>2.5</v>
       </c>
       <c r="U17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="X17">
         <v>22</v>
@@ -4999,16 +4999,16 @@
         <v>8.4</v>
       </c>
       <c r="AC17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD17">
         <v>65</v>
       </c>
       <c r="AE17">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AF17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG17">
         <v>12</v>
@@ -5017,10 +5017,10 @@
         <v>44</v>
       </c>
       <c r="AI17">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AJ17">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK17">
         <v>15</v>
@@ -5032,10 +5032,10 @@
         <v>310</v>
       </c>
       <c r="AN17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO17">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AP17">
         <v>19.5</v>
@@ -5047,7 +5047,7 @@
         <v>46</v>
       </c>
       <c r="AS17">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AT17">
         <v>7.8</v>
@@ -5059,7 +5059,7 @@
         <v>55</v>
       </c>
       <c r="AW17">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AX17">
         <v>6.6</v>
@@ -5071,7 +5071,7 @@
         <v>36</v>
       </c>
       <c r="BA17">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BB17">
         <v>7.8</v>
@@ -5086,19 +5086,19 @@
         <v>50</v>
       </c>
       <c r="BF17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG17">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BH17">
         <v>4</v>
       </c>
       <c r="BI17">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ17">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BK17">
         <v>1.01</v>
@@ -5110,10 +5110,10 @@
         <v>21</v>
       </c>
       <c r="BN17">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BO17">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP17">
         <v>7</v>
@@ -5122,13 +5122,13 @@
         <v>5.9</v>
       </c>
       <c r="BR17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BS17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BT17">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BU17">
         <v>1.01</v>
@@ -5137,13 +5137,13 @@
         <v>210</v>
       </c>
       <c r="BW17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BX17">
         <v>160</v>
       </c>
       <c r="BY17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5181,10 +5181,10 @@
         <v>1.58</v>
       </c>
       <c r="I18">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J18">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="K18">
         <v>4.7</v>
@@ -5199,19 +5199,19 @@
         <v>4.4</v>
       </c>
       <c r="O18">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P18">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q18">
         <v>1.78</v>
       </c>
       <c r="R18">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="T18">
         <v>1.87</v>
@@ -5220,7 +5220,7 @@
         <v>2.04</v>
       </c>
       <c r="V18">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="W18">
         <v>1.17</v>
@@ -5232,7 +5232,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA18">
         <v>15.5</v>
@@ -5423,10 +5423,10 @@
         <v>7.2</v>
       </c>
       <c r="I19">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K19">
         <v>5.1</v>
@@ -5435,31 +5435,31 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>2.64</v>
+        <v>4.2</v>
       </c>
       <c r="O19">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P19">
         <v>2.14</v>
       </c>
       <c r="Q19">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
         <v>1.44</v>
       </c>
       <c r="S19">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="T19">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U19">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="V19">
         <v>1.13</v>
@@ -5468,64 +5468,64 @@
         <v>2.84</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG19">
+        <v>12</v>
+      </c>
+      <c r="AH19">
+        <v>27</v>
+      </c>
+      <c r="AI19">
+        <v>110</v>
+      </c>
+      <c r="AJ19">
+        <v>15.5</v>
+      </c>
+      <c r="AK19">
+        <v>16.5</v>
+      </c>
+      <c r="AL19">
+        <v>40</v>
+      </c>
+      <c r="AM19">
+        <v>140</v>
+      </c>
+      <c r="AN19">
+        <v>7.4</v>
+      </c>
+      <c r="AO19">
+        <v>150</v>
+      </c>
+      <c r="AP19">
+        <v>15.5</v>
+      </c>
+      <c r="AQ19">
         <v>19.5</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>9</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.03</v>
-      </c>
-      <c r="AQ19">
-        <v>1.03</v>
       </c>
       <c r="AR19">
         <v>1.03</v>
@@ -5534,10 +5534,10 @@
         <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV19">
         <v>1.03</v>
@@ -5546,22 +5546,22 @@
         <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA19">
         <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD19">
         <v>1.03</v>
@@ -5570,10 +5570,10 @@
         <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5656,22 +5656,22 @@
         <v>199</v>
       </c>
       <c r="F20">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="G20">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H20">
         <v>2.32</v>
       </c>
       <c r="I20">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5686,13 +5686,13 @@
         <v>1.24</v>
       </c>
       <c r="P20">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Q20">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R20">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
         <v>2.42</v>
@@ -5704,10 +5704,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W20">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5901,7 +5901,7 @@
         <v>2.3</v>
       </c>
       <c r="G21">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H21">
         <v>2.92</v>
@@ -5910,16 +5910,16 @@
         <v>3.3</v>
       </c>
       <c r="J21">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N21">
         <v>4.3</v>
@@ -5928,22 +5928,22 @@
         <v>1.26</v>
       </c>
       <c r="P21">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q21">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R21">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S21">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="T21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U21">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
         <v>1.43</v>
@@ -5952,112 +5952,112 @@
         <v>1.64</v>
       </c>
       <c r="X21">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y21">
+        <v>15</v>
+      </c>
+      <c r="Z21">
+        <v>24</v>
+      </c>
+      <c r="AA21">
+        <v>55</v>
+      </c>
+      <c r="AB21">
+        <v>13</v>
+      </c>
+      <c r="AC21">
+        <v>9</v>
+      </c>
+      <c r="AD21">
+        <v>14.5</v>
+      </c>
+      <c r="AE21">
+        <v>34</v>
+      </c>
+      <c r="AF21">
         <v>18</v>
       </c>
-      <c r="Z21">
-        <v>30</v>
-      </c>
-      <c r="AA21">
-        <v>70</v>
-      </c>
-      <c r="AB21">
+      <c r="AG21">
+        <v>12</v>
+      </c>
+      <c r="AH21">
+        <v>16.5</v>
+      </c>
+      <c r="AI21">
+        <v>40</v>
+      </c>
+      <c r="AJ21">
+        <v>34</v>
+      </c>
+      <c r="AK21">
+        <v>25</v>
+      </c>
+      <c r="AL21">
+        <v>36</v>
+      </c>
+      <c r="AM21">
+        <v>75</v>
+      </c>
+      <c r="AN21">
+        <v>17</v>
+      </c>
+      <c r="AO21">
+        <v>26</v>
+      </c>
+      <c r="AP21">
         <v>15.5</v>
       </c>
-      <c r="AC21">
+      <c r="AQ21">
+        <v>12.5</v>
+      </c>
+      <c r="AR21">
+        <v>19.5</v>
+      </c>
+      <c r="AS21">
+        <v>42</v>
+      </c>
+      <c r="AT21">
         <v>10.5</v>
       </c>
-      <c r="AD21">
-        <v>17.5</v>
-      </c>
-      <c r="AE21">
-        <v>46</v>
-      </c>
-      <c r="AF21">
+      <c r="AU21">
+        <v>7.4</v>
+      </c>
+      <c r="AV21">
+        <v>11.5</v>
+      </c>
+      <c r="AW21">
+        <v>27</v>
+      </c>
+      <c r="AX21">
+        <v>14.5</v>
+      </c>
+      <c r="AY21">
+        <v>10</v>
+      </c>
+      <c r="AZ21">
+        <v>13.5</v>
+      </c>
+      <c r="BA21">
+        <v>32</v>
+      </c>
+      <c r="BB21">
+        <v>27</v>
+      </c>
+      <c r="BC21">
+        <v>20</v>
+      </c>
+      <c r="BD21">
+        <v>28</v>
+      </c>
+      <c r="BE21">
+        <v>60</v>
+      </c>
+      <c r="BF21">
+        <v>13.5</v>
+      </c>
+      <c r="BG21">
         <v>21</v>
-      </c>
-      <c r="AG21">
-        <v>14.5</v>
-      </c>
-      <c r="AH21">
-        <v>20</v>
-      </c>
-      <c r="AI21">
-        <v>55</v>
-      </c>
-      <c r="AJ21">
-        <v>46</v>
-      </c>
-      <c r="AK21">
-        <v>32</v>
-      </c>
-      <c r="AL21">
-        <v>48</v>
-      </c>
-      <c r="AM21">
-        <v>100</v>
-      </c>
-      <c r="AN21">
-        <v>20</v>
-      </c>
-      <c r="AO21">
-        <v>34</v>
-      </c>
-      <c r="AP21">
-        <v>13</v>
-      </c>
-      <c r="AQ21">
-        <v>10.5</v>
-      </c>
-      <c r="AR21">
-        <v>14.5</v>
-      </c>
-      <c r="AS21">
-        <v>30</v>
-      </c>
-      <c r="AT21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU21">
-        <v>6.2</v>
-      </c>
-      <c r="AV21">
-        <v>10</v>
-      </c>
-      <c r="AW21">
-        <v>20</v>
-      </c>
-      <c r="AX21">
-        <v>12</v>
-      </c>
-      <c r="AY21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21">
-        <v>12</v>
-      </c>
-      <c r="BA21">
-        <v>24</v>
-      </c>
-      <c r="BB21">
-        <v>20</v>
-      </c>
-      <c r="BC21">
-        <v>15.5</v>
-      </c>
-      <c r="BD21">
-        <v>21</v>
-      </c>
-      <c r="BE21">
-        <v>42</v>
-      </c>
-      <c r="BF21">
-        <v>11.5</v>
-      </c>
-      <c r="BG21">
-        <v>16</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6161,7 +6161,7 @@
         <v>1.26</v>
       </c>
       <c r="M22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
         <v>4.8</v>
@@ -6170,7 +6170,7 @@
         <v>1.19</v>
       </c>
       <c r="P22">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
         <v>1.54</v>
@@ -6242,46 +6242,46 @@
         <v>1000</v>
       </c>
       <c r="AN22">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO22">
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AQ22">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AR22">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AS22">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT22">
         <v>9.199999999999999</v>
       </c>
       <c r="AU22">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV22">
         <v>18.5</v>
       </c>
       <c r="AW22">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AX22">
         <v>8</v>
       </c>
       <c r="AY22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA22">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB22">
         <v>9.800000000000001</v>
@@ -6290,16 +6290,16 @@
         <v>11</v>
       </c>
       <c r="BD22">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BE22">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BF22">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG22">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH22">
         <v>5.7</v>
@@ -6382,226 +6382,226 @@
         <v>202</v>
       </c>
       <c r="F23">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G23">
         <v>1.68</v>
       </c>
       <c r="H23">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I23">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>4.3</v>
       </c>
       <c r="K23">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L23">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M23">
         <v>1.04</v>
       </c>
       <c r="N23">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P23">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q23">
         <v>1.64</v>
       </c>
       <c r="R23">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S23">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="T23">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="U23">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="V23">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W23">
         <v>2.46</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB23">
+        <v>11.5</v>
+      </c>
+      <c r="AC23">
+        <v>10.5</v>
+      </c>
+      <c r="AD23">
+        <v>23</v>
+      </c>
+      <c r="AE23">
+        <v>75</v>
+      </c>
+      <c r="AF23">
+        <v>11.5</v>
+      </c>
+      <c r="AG23">
+        <v>10.5</v>
+      </c>
+      <c r="AH23">
         <v>20</v>
       </c>
-      <c r="AC23">
-        <v>17.5</v>
-      </c>
-      <c r="AD23">
-        <v>1000</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
-        <v>21</v>
-      </c>
-      <c r="AG23">
-        <v>17.5</v>
-      </c>
-      <c r="AH23">
-        <v>1000</v>
-      </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK23">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN23">
+        <v>7.4</v>
+      </c>
+      <c r="AO23">
+        <v>75</v>
+      </c>
+      <c r="AP23">
+        <v>19</v>
+      </c>
+      <c r="AQ23">
+        <v>20</v>
+      </c>
+      <c r="AR23">
+        <v>8.4</v>
+      </c>
+      <c r="AS23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT23">
         <v>9.800000000000001</v>
       </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>1.49</v>
-      </c>
-      <c r="AQ23">
-        <v>1.49</v>
-      </c>
-      <c r="AR23">
-        <v>1.49</v>
-      </c>
-      <c r="AS23">
-        <v>1.49</v>
-      </c>
-      <c r="AT23">
+      <c r="AU23">
+        <v>9.4</v>
+      </c>
+      <c r="AV23">
+        <v>18.5</v>
+      </c>
+      <c r="AW23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX23">
+        <v>10</v>
+      </c>
+      <c r="AY23">
+        <v>9</v>
+      </c>
+      <c r="AZ23">
+        <v>16</v>
+      </c>
+      <c r="BA23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB23">
+        <v>14</v>
+      </c>
+      <c r="BC23">
+        <v>13.5</v>
+      </c>
+      <c r="BD23">
         <v>7.6</v>
       </c>
-      <c r="AU23">
-        <v>7.2</v>
-      </c>
-      <c r="AV23">
-        <v>1.49</v>
-      </c>
-      <c r="AW23">
-        <v>1.49</v>
-      </c>
-      <c r="AX23">
-        <v>7.6</v>
-      </c>
-      <c r="AY23">
-        <v>7.2</v>
-      </c>
-      <c r="AZ23">
-        <v>11</v>
-      </c>
-      <c r="BA23">
-        <v>1.49</v>
-      </c>
-      <c r="BB23">
-        <v>10.5</v>
-      </c>
-      <c r="BC23">
+      <c r="BE23">
+        <v>9</v>
+      </c>
+      <c r="BF23">
+        <v>6.4</v>
+      </c>
+      <c r="BG23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH23">
+        <v>4.2</v>
+      </c>
+      <c r="BI23">
+        <v>3.75</v>
+      </c>
+      <c r="BJ23">
         <v>9.800000000000001</v>
       </c>
-      <c r="BD23">
-        <v>1.49</v>
-      </c>
-      <c r="BE23">
-        <v>1.49</v>
-      </c>
-      <c r="BF23">
-        <v>5.5</v>
-      </c>
-      <c r="BG23">
-        <v>1.49</v>
-      </c>
-      <c r="BH23">
-        <v>4.6</v>
-      </c>
-      <c r="BI23">
-        <v>3.45</v>
-      </c>
-      <c r="BJ23">
-        <v>11.5</v>
-      </c>
       <c r="BK23">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM23">
         <v>21</v>
       </c>
       <c r="BN23">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO23">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BP23">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ23">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR23">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BS23">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BT23">
+        <v>9.4</v>
+      </c>
+      <c r="BU23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BV23">
+        <v>46</v>
+      </c>
+      <c r="BW23">
+        <v>32</v>
+      </c>
+      <c r="BX23">
+        <v>48</v>
+      </c>
+      <c r="BY23">
+        <v>32</v>
+      </c>
+      <c r="BZ23">
+        <v>17</v>
+      </c>
+      <c r="CA23">
         <v>11</v>
-      </c>
-      <c r="BU23">
-        <v>7</v>
-      </c>
-      <c r="BV23">
-        <v>60</v>
-      </c>
-      <c r="BW23">
-        <v>21</v>
-      </c>
-      <c r="BX23">
-        <v>65</v>
-      </c>
-      <c r="BY23">
-        <v>21</v>
-      </c>
-      <c r="BZ23">
-        <v>20</v>
-      </c>
-      <c r="CA23">
-        <v>9.199999999999999</v>
       </c>
       <c r="CB23" t="s">
         <v>230</v>
@@ -6633,7 +6633,7 @@
         <v>2.02</v>
       </c>
       <c r="I24">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="J24">
         <v>1.01</v>
@@ -6642,7 +6642,7 @@
         <v>5.5</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M24">
         <v>1.01</v>
@@ -6672,7 +6672,7 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="W24">
         <v>1.27</v>
@@ -6884,7 +6884,7 @@
         <v>3.65</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M25">
         <v>1.01</v>
@@ -7132,7 +7132,7 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O26">
         <v>1.2</v>
@@ -7150,10 +7150,10 @@
         <v>2.46</v>
       </c>
       <c r="T26">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V26">
         <v>1.46</v>
@@ -7219,34 +7219,34 @@
         <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
         <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
         <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
         <v>1.01</v>
@@ -7264,10 +7264,10 @@
         <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7353,124 +7353,124 @@
         <v>2.38</v>
       </c>
       <c r="G27">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H27">
         <v>2.8</v>
       </c>
       <c r="I27">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J27">
         <v>3.55</v>
       </c>
       <c r="K27">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N27">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O27">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P27">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q27">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R27">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S27">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T27">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="U27">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V27">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X27">
         <v>1000</v>
       </c>
       <c r="Y27">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB27">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="AC27">
         <v>14.5</v>
       </c>
       <c r="AD27">
+        <v>16</v>
+      </c>
+      <c r="AE27">
+        <v>40</v>
+      </c>
+      <c r="AF27">
+        <v>23</v>
+      </c>
+      <c r="AG27">
+        <v>16</v>
+      </c>
+      <c r="AH27">
+        <v>19</v>
+      </c>
+      <c r="AI27">
+        <v>50</v>
+      </c>
+      <c r="AJ27">
+        <v>46</v>
+      </c>
+      <c r="AK27">
+        <v>34</v>
+      </c>
+      <c r="AL27">
+        <v>44</v>
+      </c>
+      <c r="AM27">
+        <v>95</v>
+      </c>
+      <c r="AN27">
+        <v>22</v>
+      </c>
+      <c r="AO27">
         <v>29</v>
       </c>
-      <c r="AE27">
-        <v>1000</v>
-      </c>
-      <c r="AF27">
-        <v>1000</v>
-      </c>
-      <c r="AG27">
-        <v>22</v>
-      </c>
-      <c r="AH27">
-        <v>55</v>
-      </c>
-      <c r="AI27">
-        <v>1000</v>
-      </c>
-      <c r="AJ27">
-        <v>1000</v>
-      </c>
-      <c r="AK27">
-        <v>1000</v>
-      </c>
-      <c r="AL27">
-        <v>1000</v>
-      </c>
-      <c r="AM27">
-        <v>1000</v>
-      </c>
-      <c r="AN27">
-        <v>55</v>
-      </c>
-      <c r="AO27">
-        <v>1000</v>
-      </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AT27">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU27">
         <v>6</v>
@@ -7479,10 +7479,10 @@
         <v>7.2</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX27">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AY27">
         <v>6.6</v>
@@ -7491,31 +7491,31 @@
         <v>8</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF27">
         <v>8</v>
       </c>
       <c r="BG27">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BH27">
         <v>4.6</v>
       </c>
       <c r="BI27">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
@@ -7533,7 +7533,7 @@
         <v>8</v>
       </c>
       <c r="BO27">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
         <v>1000</v>
@@ -7551,7 +7551,7 @@
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
         <v>1000</v>
@@ -7595,7 +7595,7 @@
         <v>1.19</v>
       </c>
       <c r="G28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H28">
         <v>15</v>
@@ -7616,10 +7616,10 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O28">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P28">
         <v>4</v>
@@ -7628,130 +7628,130 @@
         <v>1.3</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="T28">
         <v>1.86</v>
       </c>
       <c r="U28">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V28">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W28">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA28">
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF28">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AG28">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ28">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AK28">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN28">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP28">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="AQ28">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="AR28">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="AS28">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="AT28">
-        <v>2.02</v>
+        <v>14.5</v>
       </c>
       <c r="AU28">
-        <v>2.02</v>
+        <v>19.5</v>
       </c>
       <c r="AV28">
-        <v>2.02</v>
+        <v>7.4</v>
       </c>
       <c r="AW28">
-        <v>2.02</v>
+        <v>7.4</v>
       </c>
       <c r="AX28">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY28">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="BA28">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="BB28">
-        <v>1.84</v>
+        <v>9.4</v>
       </c>
       <c r="BC28">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="BD28">
-        <v>2.02</v>
+        <v>6.8</v>
       </c>
       <c r="BE28">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="BF28">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BG28">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7834,58 +7834,58 @@
         <v>208</v>
       </c>
       <c r="F29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H29">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I29">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="J29">
         <v>3.6</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L29">
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29">
         <v>2.42</v>
       </c>
       <c r="O29">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P29">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q29">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R29">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="S29">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="T29">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U29">
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="W29">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7942,37 +7942,37 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ29">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS29">
         <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU29">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV29">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX29">
         <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ29">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA29">
         <v>1.01</v>
@@ -7993,7 +7993,7 @@
         <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8079,19 +8079,19 @@
         <v>2.66</v>
       </c>
       <c r="G30">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="H30">
         <v>3</v>
       </c>
       <c r="I30">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J30">
         <v>3</v>
       </c>
       <c r="K30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8115,7 +8115,7 @@
         <v>1.22</v>
       </c>
       <c r="S30">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T30">
         <v>2</v>
@@ -8127,7 +8127,7 @@
         <v>1.43</v>
       </c>
       <c r="W30">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X30">
         <v>9.6</v>
@@ -8154,7 +8154,7 @@
         <v>55</v>
       </c>
       <c r="AF30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG30">
         <v>13.5</v>
@@ -8175,13 +8175,13 @@
         <v>70</v>
       </c>
       <c r="AM30">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN30">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO30">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP30">
         <v>8</v>
@@ -8193,7 +8193,7 @@
         <v>16.5</v>
       </c>
       <c r="AS30">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT30">
         <v>7.6</v>
@@ -8205,7 +8205,7 @@
         <v>12</v>
       </c>
       <c r="AW30">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AX30">
         <v>14.5</v>
@@ -8217,25 +8217,25 @@
         <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB30">
         <v>36</v>
       </c>
       <c r="BC30">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD30">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE30">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF30">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BG30">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8244,58 +8244,58 @@
         <v>2.4</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB30" t="s">
         <v>230</v>
@@ -8318,16 +8318,16 @@
         <v>210</v>
       </c>
       <c r="F31">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G31">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H31">
         <v>4.2</v>
       </c>
       <c r="I31">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J31">
         <v>3.95</v>
@@ -8342,7 +8342,7 @@
         <v>1.04</v>
       </c>
       <c r="N31">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O31">
         <v>1.2</v>
@@ -8351,31 +8351,31 @@
         <v>2.46</v>
       </c>
       <c r="Q31">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="R31">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="S31">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="T31">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W31">
         <v>2.02</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y31">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Z31">
         <v>48</v>
@@ -8384,100 +8384,100 @@
         <v>100</v>
       </c>
       <c r="AB31">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC31">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD31">
+        <v>17.5</v>
+      </c>
+      <c r="AE31">
+        <v>50</v>
+      </c>
+      <c r="AF31">
+        <v>14.5</v>
+      </c>
+      <c r="AG31">
+        <v>11</v>
+      </c>
+      <c r="AH31">
+        <v>16</v>
+      </c>
+      <c r="AI31">
+        <v>55</v>
+      </c>
+      <c r="AJ31">
         <v>24</v>
       </c>
-      <c r="AE31">
-        <v>60</v>
-      </c>
-      <c r="AF31">
-        <v>19</v>
-      </c>
-      <c r="AG31">
-        <v>13</v>
-      </c>
-      <c r="AH31">
-        <v>21</v>
-      </c>
-      <c r="AI31">
-        <v>65</v>
-      </c>
-      <c r="AJ31">
+      <c r="AK31">
+        <v>18.5</v>
+      </c>
+      <c r="AL31">
         <v>30</v>
-      </c>
-      <c r="AK31">
-        <v>24</v>
-      </c>
-      <c r="AL31">
-        <v>36</v>
       </c>
       <c r="AM31">
         <v>90</v>
       </c>
       <c r="AN31">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO31">
         <v>48</v>
       </c>
       <c r="AP31">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AQ31">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AR31">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS31">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AT31">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU31">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV31">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW31">
-        <v>3.35</v>
+        <v>9.4</v>
       </c>
       <c r="AX31">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY31">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ31">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA31">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB31">
         <v>14</v>
       </c>
       <c r="BC31">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD31">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="BF31">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG31">
-        <v>3.3</v>
+        <v>21</v>
       </c>
       <c r="BH31">
         <v>4.8</v>
@@ -8859,7 +8859,7 @@
         <v>24</v>
       </c>
       <c r="Y33">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z33">
         <v>24</v>
@@ -8868,10 +8868,10 @@
         <v>1000</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC33">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD33">
         <v>21</v>
@@ -8910,25 +8910,25 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS33">
         <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
         <v>1.01</v>
@@ -8937,10 +8937,10 @@
         <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
         <v>1.01</v>
@@ -8961,13 +8961,13 @@
         <v>1.01</v>
       </c>
       <c r="BG33">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
@@ -9003,7 +9003,7 @@
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV33">
         <v>1000</v>
@@ -9053,7 +9053,7 @@
         <v>4.2</v>
       </c>
       <c r="I34">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J34">
         <v>3.6</v>
@@ -9065,13 +9065,13 @@
         <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O34">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P34">
         <v>1.94</v>
@@ -9080,130 +9080,130 @@
         <v>1.92</v>
       </c>
       <c r="R34">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S34">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T34">
         <v>1.8</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V34">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W34">
         <v>1.96</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y34">
+        <v>16</v>
+      </c>
+      <c r="Z34">
+        <v>34</v>
+      </c>
+      <c r="AA34">
+        <v>120</v>
+      </c>
+      <c r="AB34">
+        <v>9.4</v>
+      </c>
+      <c r="AC34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD34">
+        <v>18</v>
+      </c>
+      <c r="AE34">
+        <v>70</v>
+      </c>
+      <c r="AF34">
+        <v>12.5</v>
+      </c>
+      <c r="AG34">
+        <v>11</v>
+      </c>
+      <c r="AH34">
+        <v>19</v>
+      </c>
+      <c r="AI34">
+        <v>75</v>
+      </c>
+      <c r="AJ34">
+        <v>24</v>
+      </c>
+      <c r="AK34">
         <v>22</v>
       </c>
-      <c r="Z34">
-        <v>48</v>
-      </c>
-      <c r="AA34">
-        <v>1000</v>
-      </c>
-      <c r="AB34">
+      <c r="AL34">
+        <v>38</v>
+      </c>
+      <c r="AM34">
+        <v>120</v>
+      </c>
+      <c r="AN34">
+        <v>17</v>
+      </c>
+      <c r="AO34">
+        <v>75</v>
+      </c>
+      <c r="AP34">
         <v>13</v>
       </c>
-      <c r="AC34">
-        <v>10</v>
-      </c>
-      <c r="AD34">
-        <v>25</v>
-      </c>
-      <c r="AE34">
+      <c r="AQ34">
+        <v>13.5</v>
+      </c>
+      <c r="AR34">
+        <v>28</v>
+      </c>
+      <c r="AS34">
+        <v>80</v>
+      </c>
+      <c r="AT34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU34">
+        <v>7.4</v>
+      </c>
+      <c r="AV34">
+        <v>15</v>
+      </c>
+      <c r="AW34">
+        <v>46</v>
+      </c>
+      <c r="AX34">
+        <v>10.5</v>
+      </c>
+      <c r="AY34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ34">
+        <v>16</v>
+      </c>
+      <c r="BA34">
+        <v>50</v>
+      </c>
+      <c r="BB34">
+        <v>20</v>
+      </c>
+      <c r="BC34">
+        <v>18</v>
+      </c>
+      <c r="BD34">
+        <v>30</v>
+      </c>
+      <c r="BE34">
         <v>85</v>
       </c>
-      <c r="AF34">
-        <v>17.5</v>
-      </c>
-      <c r="AG34">
-        <v>15</v>
-      </c>
-      <c r="AH34">
-        <v>26</v>
-      </c>
-      <c r="AI34">
-        <v>90</v>
-      </c>
-      <c r="AJ34">
-        <v>32</v>
-      </c>
-      <c r="AK34">
-        <v>30</v>
-      </c>
-      <c r="AL34">
+      <c r="BF34">
+        <v>12</v>
+      </c>
+      <c r="BG34">
         <v>50</v>
-      </c>
-      <c r="AM34">
-        <v>1000</v>
-      </c>
-      <c r="AN34">
-        <v>20</v>
-      </c>
-      <c r="AO34">
-        <v>90</v>
-      </c>
-      <c r="AP34">
-        <v>9.4</v>
-      </c>
-      <c r="AQ34">
-        <v>11.5</v>
-      </c>
-      <c r="AR34">
-        <v>19</v>
-      </c>
-      <c r="AS34">
-        <v>55</v>
-      </c>
-      <c r="AT34">
-        <v>7.2</v>
-      </c>
-      <c r="AU34">
-        <v>6.2</v>
-      </c>
-      <c r="AV34">
-        <v>12.5</v>
-      </c>
-      <c r="AW34">
-        <v>32</v>
-      </c>
-      <c r="AX34">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY34">
-        <v>8</v>
-      </c>
-      <c r="AZ34">
-        <v>13.5</v>
-      </c>
-      <c r="BA34">
-        <v>36</v>
-      </c>
-      <c r="BB34">
-        <v>16.5</v>
-      </c>
-      <c r="BC34">
-        <v>12.5</v>
-      </c>
-      <c r="BD34">
-        <v>22</v>
-      </c>
-      <c r="BE34">
-        <v>60</v>
-      </c>
-      <c r="BF34">
-        <v>10</v>
-      </c>
-      <c r="BG34">
-        <v>36</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9289,13 +9289,13 @@
         <v>1.23</v>
       </c>
       <c r="G35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H35">
         <v>17</v>
       </c>
       <c r="I35">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J35">
         <v>6.8</v>
@@ -9310,22 +9310,22 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O35">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P35">
         <v>2.42</v>
       </c>
       <c r="Q35">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R35">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S35">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T35">
         <v>2.38</v>
@@ -9334,67 +9334,67 @@
         <v>1.62</v>
       </c>
       <c r="V35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="X35">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y35">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z35">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA35">
         <v>1000</v>
       </c>
       <c r="AB35">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC35">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AD35">
         <v>85</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AF35">
         <v>7.8</v>
       </c>
       <c r="AG35">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH35">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI35">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ35">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK35">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL35">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM35">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN35">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AO35">
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ35">
         <v>36</v>
@@ -9409,10 +9409,10 @@
         <v>7.8</v>
       </c>
       <c r="AU35">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AV35">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AW35">
         <v>95</v>
@@ -9421,19 +9421,19 @@
         <v>6.4</v>
       </c>
       <c r="AY35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ35">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BA35">
         <v>95</v>
       </c>
       <c r="BB35">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC35">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BD35">
         <v>36</v>
@@ -9442,7 +9442,7 @@
         <v>95</v>
       </c>
       <c r="BF35">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BG35">
         <v>95</v>
@@ -9528,172 +9528,172 @@
         <v>215</v>
       </c>
       <c r="F36">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G36">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="H36">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I36">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="J36">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K36">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L36">
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N36">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="O36">
         <v>1.23</v>
       </c>
       <c r="P36">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q36">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R36">
+        <v>1.43</v>
+      </c>
+      <c r="S36">
+        <v>2.62</v>
+      </c>
+      <c r="T36">
+        <v>1.59</v>
+      </c>
+      <c r="U36">
+        <v>2.38</v>
+      </c>
+      <c r="V36">
         <v>1.44</v>
       </c>
-      <c r="S36">
-        <v>2.58</v>
-      </c>
-      <c r="T36">
-        <v>1.57</v>
-      </c>
-      <c r="U36">
-        <v>2.34</v>
-      </c>
-      <c r="V36">
-        <v>1.38</v>
-      </c>
       <c r="W36">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC36">
+        <v>10</v>
+      </c>
+      <c r="AD36">
+        <v>16.5</v>
+      </c>
+      <c r="AE36">
+        <v>38</v>
+      </c>
+      <c r="AF36">
+        <v>18.5</v>
+      </c>
+      <c r="AG36">
+        <v>14.5</v>
+      </c>
+      <c r="AH36">
+        <v>18.5</v>
+      </c>
+      <c r="AI36">
+        <v>50</v>
+      </c>
+      <c r="AJ36">
+        <v>48</v>
+      </c>
+      <c r="AK36">
+        <v>25</v>
+      </c>
+      <c r="AL36">
+        <v>38</v>
+      </c>
+      <c r="AM36">
+        <v>80</v>
+      </c>
+      <c r="AN36">
+        <v>17.5</v>
+      </c>
+      <c r="AO36">
+        <v>26</v>
+      </c>
+      <c r="AP36">
+        <v>17.5</v>
+      </c>
+      <c r="AQ36">
         <v>13</v>
       </c>
-      <c r="AD36">
-        <v>1000</v>
-      </c>
-      <c r="AE36">
-        <v>1000</v>
-      </c>
-      <c r="AF36">
-        <v>1000</v>
-      </c>
-      <c r="AG36">
-        <v>1000</v>
-      </c>
-      <c r="AH36">
-        <v>1000</v>
-      </c>
-      <c r="AI36">
-        <v>1000</v>
-      </c>
-      <c r="AJ36">
-        <v>1000</v>
-      </c>
-      <c r="AK36">
-        <v>1000</v>
-      </c>
-      <c r="AL36">
-        <v>1000</v>
-      </c>
-      <c r="AM36">
-        <v>1000</v>
-      </c>
-      <c r="AN36">
-        <v>1000</v>
-      </c>
-      <c r="AO36">
-        <v>1000</v>
-      </c>
-      <c r="AP36">
+      <c r="AR36">
+        <v>16.5</v>
+      </c>
+      <c r="AS36">
+        <v>34</v>
+      </c>
+      <c r="AT36">
+        <v>11.5</v>
+      </c>
+      <c r="AU36">
+        <v>7.8</v>
+      </c>
+      <c r="AV36">
+        <v>11.5</v>
+      </c>
+      <c r="AW36">
+        <v>22</v>
+      </c>
+      <c r="AX36">
+        <v>15</v>
+      </c>
+      <c r="AY36">
         <v>10</v>
       </c>
-      <c r="AQ36">
-        <v>10</v>
-      </c>
-      <c r="AR36">
-        <v>1.01</v>
-      </c>
-      <c r="AS36">
-        <v>1.01</v>
-      </c>
-      <c r="AT36">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU36">
-        <v>6.2</v>
-      </c>
-      <c r="AV36">
-        <v>9.4</v>
-      </c>
-      <c r="AW36">
-        <v>1.01</v>
-      </c>
-      <c r="AX36">
-        <v>11</v>
-      </c>
-      <c r="AY36">
-        <v>8.4</v>
-      </c>
       <c r="AZ36">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA36">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC36">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF36">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH36">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ36">
         <v>1000</v>
@@ -9770,19 +9770,19 @@
         <v>216</v>
       </c>
       <c r="F37">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="G37">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H37">
         <v>2.66</v>
       </c>
       <c r="I37">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J37">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K37">
         <v>3.4</v>
@@ -9794,7 +9794,7 @@
         <v>1.09</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O37">
         <v>1.38</v>
@@ -9806,22 +9806,22 @@
         <v>2.16</v>
       </c>
       <c r="R37">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S37">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T37">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="U37">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="V37">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W37">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X37">
         <v>12.5</v>
@@ -9830,7 +9830,7 @@
         <v>10.5</v>
       </c>
       <c r="Z37">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA37">
         <v>140</v>
@@ -9845,7 +9845,7 @@
         <v>12.5</v>
       </c>
       <c r="AE37">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF37">
         <v>21</v>
@@ -9854,7 +9854,7 @@
         <v>14</v>
       </c>
       <c r="AH37">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI37">
         <v>50</v>
@@ -9863,7 +9863,7 @@
         <v>55</v>
       </c>
       <c r="AK37">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL37">
         <v>55</v>
@@ -9875,7 +9875,7 @@
         <v>40</v>
       </c>
       <c r="AO37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP37">
         <v>10</v>
@@ -9887,7 +9887,7 @@
         <v>14.5</v>
       </c>
       <c r="AS37">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT37">
         <v>9.6</v>
@@ -9896,10 +9896,10 @@
         <v>6.8</v>
       </c>
       <c r="AV37">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW37">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX37">
         <v>16.5</v>
@@ -9911,37 +9911,37 @@
         <v>16</v>
       </c>
       <c r="BA37">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB37">
+        <v>8.6</v>
+      </c>
+      <c r="BC37">
         <v>8</v>
       </c>
-      <c r="BC37">
+      <c r="BD37">
+        <v>8.6</v>
+      </c>
+      <c r="BE37">
+        <v>9.4</v>
+      </c>
+      <c r="BF37">
+        <v>8</v>
+      </c>
+      <c r="BG37">
         <v>7.6</v>
       </c>
-      <c r="BD37">
-        <v>8</v>
-      </c>
-      <c r="BE37">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF37">
-        <v>7.6</v>
-      </c>
-      <c r="BG37">
-        <v>7.2</v>
-      </c>
       <c r="BH37">
-        <v>3.4</v>
+        <v>970</v>
       </c>
       <c r="BI37">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37">
         <v>1000</v>
       </c>
       <c r="BK37">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL37">
         <v>1000</v>
@@ -9950,10 +9950,10 @@
         <v>1.01</v>
       </c>
       <c r="BN37">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="BO37">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP37">
         <v>1000</v>
@@ -9968,10 +9968,10 @@
         <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="BU37">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV37">
         <v>1000</v>
@@ -10021,13 +10021,13 @@
         <v>8.4</v>
       </c>
       <c r="I38">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>4.9</v>
       </c>
       <c r="K38">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -10039,19 +10039,19 @@
         <v>4.4</v>
       </c>
       <c r="O38">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P38">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q38">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R38">
         <v>1.45</v>
       </c>
       <c r="S38">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T38">
         <v>1.81</v>
@@ -10060,7 +10060,7 @@
         <v>1.89</v>
       </c>
       <c r="V38">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W38">
         <v>3.1</v>
@@ -10069,7 +10069,7 @@
         <v>1000</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z38">
         <v>1000</v>
@@ -10078,7 +10078,7 @@
         <v>1000</v>
       </c>
       <c r="AB38">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AC38">
         <v>23</v>
@@ -10090,88 +10090,88 @@
         <v>1000</v>
       </c>
       <c r="AF38">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG38">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH38">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI38">
         <v>1000</v>
       </c>
       <c r="AJ38">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AK38">
         <v>48</v>
       </c>
       <c r="AL38">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM38">
         <v>1000</v>
       </c>
       <c r="AN38">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO38">
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="AQ38">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AR38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="AS38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="AT38">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="AU38">
-        <v>1.63</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="AW38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="AX38">
-        <v>1.56</v>
+        <v>7.2</v>
       </c>
       <c r="AY38">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AZ38">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="BA38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="BB38">
-        <v>1.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC38">
-        <v>1.7</v>
+        <v>11.5</v>
       </c>
       <c r="BD38">
-        <v>1.76</v>
+        <v>2.32</v>
       </c>
       <c r="BE38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="BF38">
         <v>4.7</v>
       </c>
       <c r="BG38">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10195,7 +10195,7 @@
         <v>1000</v>
       </c>
       <c r="BO38">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP38">
         <v>1000</v>
@@ -10299,7 +10299,7 @@
         <v>1.39</v>
       </c>
       <c r="U39">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="V39">
         <v>1.44</v>
@@ -10365,7 +10365,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR39">
         <v>1.01</v>
@@ -10496,22 +10496,22 @@
         <v>219</v>
       </c>
       <c r="F40">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G40">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="H40">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="I40">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J40">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K40">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10544,10 +10544,10 @@
         <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W40">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10738,16 +10738,16 @@
         <v>220</v>
       </c>
       <c r="F41">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G41">
         <v>2.58</v>
       </c>
       <c r="H41">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I41">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="J41">
         <v>3.35</v>
@@ -10759,19 +10759,19 @@
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N41">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O41">
         <v>1.31</v>
       </c>
       <c r="P41">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q41">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R41">
         <v>1.31</v>
@@ -10783,16 +10783,16 @@
         <v>1.72</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
         <v>1.63</v>
       </c>
       <c r="X41">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y41">
         <v>27</v>
@@ -10894,7 +10894,7 @@
         <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG41">
         <v>1.01</v>
@@ -10983,7 +10983,7 @@
         <v>1.77</v>
       </c>
       <c r="G42">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H42">
         <v>4.3</v>
@@ -10992,7 +10992,7 @@
         <v>5.9</v>
       </c>
       <c r="J42">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K42">
         <v>4.4</v>
@@ -11010,10 +11010,10 @@
         <v>1.29</v>
       </c>
       <c r="P42">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q42">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="R42">
         <v>1.31</v>
@@ -11028,10 +11028,10 @@
         <v>1.89</v>
       </c>
       <c r="V42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W42">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="X42">
         <v>34</v>
@@ -11049,7 +11049,7 @@
         <v>13.5</v>
       </c>
       <c r="AC42">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AD42">
         <v>1000</v>
@@ -11058,10 +11058,10 @@
         <v>1000</v>
       </c>
       <c r="AF42">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG42">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH42">
         <v>1000</v>
@@ -11091,7 +11091,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ42">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR42">
         <v>1.01</v>
@@ -11112,10 +11112,10 @@
         <v>1.01</v>
       </c>
       <c r="AX42">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY42">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ42">
         <v>1.01</v>
@@ -11136,7 +11136,7 @@
         <v>1.01</v>
       </c>
       <c r="BF42">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BG42">
         <v>1.01</v>
@@ -11464,22 +11464,22 @@
         <v>223</v>
       </c>
       <c r="F44">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="G44">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="H44">
         <v>2</v>
       </c>
       <c r="I44">
-        <v>110</v>
+        <v>5.1</v>
       </c>
       <c r="J44">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K44">
-        <v>920</v>
+        <v>4</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11488,22 +11488,22 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="O44">
         <v>1.01</v>
       </c>
       <c r="P44">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q44">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="R44">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="S44">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="T44">
         <v>1.01</v>
@@ -11512,10 +11512,10 @@
         <v>1.01</v>
       </c>
       <c r="V44">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -11715,22 +11715,22 @@
         <v>2.3</v>
       </c>
       <c r="I45">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="J45">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K45">
         <v>3.9</v>
       </c>
       <c r="L45">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M45">
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O45">
         <v>1.2</v>
@@ -11754,7 +11754,7 @@
         <v>1.01</v>
       </c>
       <c r="V45">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W45">
         <v>1.45</v>
@@ -11951,10 +11951,10 @@
         <v>1.27</v>
       </c>
       <c r="G46">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H46">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="I46">
         <v>15</v>
@@ -11966,22 +11966,22 @@
         <v>7</v>
       </c>
       <c r="L46">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M46">
         <v>1.04</v>
       </c>
       <c r="N46">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O46">
         <v>1.18</v>
       </c>
       <c r="P46">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q46">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R46">
         <v>1.69</v>
@@ -11990,7 +11990,7 @@
         <v>2.36</v>
       </c>
       <c r="T46">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U46">
         <v>1.83</v>
@@ -11999,7 +11999,7 @@
         <v>1.07</v>
       </c>
       <c r="W46">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="X46">
         <v>28</v>
@@ -12011,7 +12011,7 @@
         <v>1000</v>
       </c>
       <c r="AA46">
-        <v>740</v>
+        <v>710</v>
       </c>
       <c r="AB46">
         <v>10.5</v>
@@ -12032,10 +12032,10 @@
         <v>11.5</v>
       </c>
       <c r="AH46">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI46">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ46">
         <v>9.6</v>
@@ -12047,13 +12047,13 @@
         <v>38</v>
       </c>
       <c r="AM46">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN46">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO46">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AP46">
         <v>23</v>
@@ -12065,28 +12065,28 @@
         <v>42</v>
       </c>
       <c r="AS46">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AT46">
         <v>9.6</v>
       </c>
       <c r="AU46">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV46">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AW46">
         <v>48</v>
       </c>
       <c r="AX46">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY46">
         <v>10.5</v>
       </c>
       <c r="AZ46">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA46">
         <v>44</v>
@@ -12107,61 +12107,61 @@
         <v>3.8</v>
       </c>
       <c r="BG46">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="BH46">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI46">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BJ46">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK46">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BL46">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM46">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN46">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BO46">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP46">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BQ46">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR46">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS46">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BT46">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU46">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BV46">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW46">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BX46">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY46">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ46">
         <v>0</v>
@@ -12190,16 +12190,16 @@
         <v>226</v>
       </c>
       <c r="F47">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G47">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H47">
+        <v>3.1</v>
+      </c>
+      <c r="I47">
         <v>3.15</v>
-      </c>
-      <c r="I47">
-        <v>3.2</v>
       </c>
       <c r="J47">
         <v>3.65</v>
@@ -12208,7 +12208,7 @@
         <v>3.7</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M47">
         <v>1.06</v>
@@ -12238,16 +12238,16 @@
         <v>2.36</v>
       </c>
       <c r="V47">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W47">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X47">
         <v>16</v>
       </c>
       <c r="Y47">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z47">
         <v>22</v>
@@ -12259,7 +12259,7 @@
         <v>11.5</v>
       </c>
       <c r="AC47">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD47">
         <v>13</v>
@@ -12280,10 +12280,10 @@
         <v>40</v>
       </c>
       <c r="AJ47">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL47">
         <v>32</v>
@@ -12328,10 +12328,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ47">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA47">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB47">
         <v>30</v>
@@ -12352,64 +12352,64 @@
         <v>26</v>
       </c>
       <c r="BH47">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI47">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ47">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BK47">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL47">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM47">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN47">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO47">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BP47">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ47">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BR47">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS47">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT47">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU47">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV47">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW47">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX47">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY47">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ47">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA47">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="CB47" t="s">
         <v>230</v>
@@ -12450,7 +12450,7 @@
         <v>4.2</v>
       </c>
       <c r="L48">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M48">
         <v>1.04</v>
@@ -12462,10 +12462,10 @@
         <v>1.2</v>
       </c>
       <c r="P48">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q48">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R48">
         <v>1.61</v>
@@ -12492,13 +12492,13 @@
         <v>21</v>
       </c>
       <c r="Z48">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA48">
         <v>75</v>
       </c>
       <c r="AB48">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC48">
         <v>9.6</v>
@@ -12507,7 +12507,7 @@
         <v>16</v>
       </c>
       <c r="AE48">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF48">
         <v>15</v>
@@ -12525,7 +12525,7 @@
         <v>24</v>
       </c>
       <c r="AK48">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL48">
         <v>27</v>
@@ -12534,7 +12534,7 @@
         <v>65</v>
       </c>
       <c r="AN48">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO48">
         <v>29</v>
@@ -12543,16 +12543,16 @@
         <v>21</v>
       </c>
       <c r="AQ48">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR48">
         <v>28</v>
       </c>
       <c r="AS48">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AT48">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU48">
         <v>8.800000000000001</v>
@@ -12564,13 +12564,13 @@
         <v>34</v>
       </c>
       <c r="AX48">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY48">
         <v>9.6</v>
       </c>
       <c r="AZ48">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA48">
         <v>36</v>
@@ -12585,7 +12585,7 @@
         <v>23</v>
       </c>
       <c r="BE48">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF48">
         <v>8.6</v>
@@ -12603,7 +12603,7 @@
         <v>13</v>
       </c>
       <c r="BK48">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL48">
         <v>1000</v>
@@ -12618,10 +12618,10 @@
         <v>4</v>
       </c>
       <c r="BP48">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ48">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR48">
         <v>1000</v>
@@ -12633,7 +12633,7 @@
         <v>10.5</v>
       </c>
       <c r="BU48">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV48">
         <v>1000</v>
@@ -12674,226 +12674,226 @@
         <v>228</v>
       </c>
       <c r="F49">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G49">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H49">
         <v>3.25</v>
       </c>
       <c r="I49">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J49">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K49">
         <v>3.35</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P49">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q49">
         <v>2.32</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH49">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI49">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL49">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN49">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO49">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP49">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU49">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV49">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW49">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AX49">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY49">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ49">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BD49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE49">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BG49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BJ49">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BK49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN49">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT49">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ49">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB49" t="s">
         <v>230</v>
@@ -12919,7 +12919,7 @@
         <v>1.47</v>
       </c>
       <c r="G50">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H50">
         <v>7.6</v>
@@ -12934,46 +12934,46 @@
         <v>5.1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M50">
         <v>1.05</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P50">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q50">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T50">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U50">
         <v>1.93</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X50">
         <v>23</v>
       </c>
       <c r="Y50">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z50">
         <v>90</v>
@@ -13012,28 +13012,28 @@
         <v>16.5</v>
       </c>
       <c r="AL50">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM50">
         <v>150</v>
       </c>
       <c r="AN50">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AO50">
         <v>180</v>
       </c>
       <c r="AP50">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ50">
         <v>20</v>
       </c>
       <c r="AR50">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AS50">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT50">
         <v>7.8</v>
@@ -13042,10 +13042,10 @@
         <v>9.6</v>
       </c>
       <c r="AV50">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AW50">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX50">
         <v>7.8</v>
@@ -13057,7 +13057,7 @@
         <v>20</v>
       </c>
       <c r="BA50">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB50">
         <v>11.5</v>
@@ -13066,76 +13066,76 @@
         <v>13</v>
       </c>
       <c r="BD50">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE50">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF50">
         <v>6.2</v>
       </c>
       <c r="BG50">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH50">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI50">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN50">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO50">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BP50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="s">
         <v>230</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -844,7 +844,7 @@
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>2026-09-13 02:25:56</t>
+    <t>2026-09-13 04:49:35</t>
   </si>
 </sst>
 </file>
@@ -1438,151 +1438,151 @@
         <v>212</v>
       </c>
       <c r="F2">
+        <v>5.2</v>
+      </c>
+      <c r="G2">
+        <v>6.4</v>
+      </c>
+      <c r="H2">
+        <v>1.55</v>
+      </c>
+      <c r="I2">
+        <v>1.61</v>
+      </c>
+      <c r="J2">
+        <v>4.7</v>
+      </c>
+      <c r="K2">
         <v>5.8</v>
       </c>
-      <c r="G2">
-        <v>7.6</v>
-      </c>
-      <c r="H2">
-        <v>1.49</v>
-      </c>
-      <c r="I2">
-        <v>1.53</v>
-      </c>
-      <c r="J2">
-        <v>4.9</v>
-      </c>
-      <c r="K2">
-        <v>6.2</v>
-      </c>
       <c r="L2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q2">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R2">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="S2">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="W2">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AP2">
         <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
         <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX2">
         <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
         <v>1.01</v>
@@ -1591,13 +1591,13 @@
         <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
         <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1695,7 +1695,7 @@
         <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
         <v>1.44</v>
@@ -1773,7 +1773,7 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL3">
         <v>50</v>
@@ -1845,7 +1845,7 @@
         <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ3">
         <v>12</v>
@@ -1949,13 +1949,13 @@
         <v>2.38</v>
       </c>
       <c r="O4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P4">
         <v>1.45</v>
       </c>
       <c r="Q4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
         <v>1.15</v>
@@ -1964,7 +1964,7 @@
         <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U4">
         <v>1.69</v>
@@ -2009,7 +2009,7 @@
         <v>32</v>
       </c>
       <c r="AI4">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="AJ4">
         <v>120</v>
@@ -2018,16 +2018,16 @@
         <v>130</v>
       </c>
       <c r="AL4">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="AM4">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="AN4">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="AO4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP4">
         <v>6.4</v>
@@ -2078,25 +2078,25 @@
         <v>90</v>
       </c>
       <c r="BF4">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BG4">
         <v>34</v>
       </c>
       <c r="BH4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BI4">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BK4">
         <v>10</v>
       </c>
       <c r="BL4">
-        <v>980</v>
+        <v>890</v>
       </c>
       <c r="BM4">
         <v>22</v>
@@ -2108,16 +2108,16 @@
         <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
         <v>20</v>
       </c>
       <c r="BR4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BT4">
         <v>7</v>
@@ -2126,10 +2126,10 @@
         <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BX4">
         <v>75</v>
@@ -2138,10 +2138,10 @@
         <v>46</v>
       </c>
       <c r="BZ4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="CA4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="CB4" t="s">
         <v>276</v>
@@ -2173,43 +2173,43 @@
         <v>3.55</v>
       </c>
       <c r="I5">
+        <v>3.75</v>
+      </c>
+      <c r="J5">
         <v>3.8</v>
-      </c>
-      <c r="J5">
-        <v>3.85</v>
       </c>
       <c r="K5">
         <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
         <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U5">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V5">
         <v>1.3</v>
@@ -2221,7 +2221,7 @@
         <v>23</v>
       </c>
       <c r="Y5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z5">
         <v>32</v>
@@ -2242,13 +2242,13 @@
         <v>48</v>
       </c>
       <c r="AF5">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
         <v>46</v>
@@ -2269,7 +2269,7 @@
         <v>12</v>
       </c>
       <c r="AO5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AP5">
         <v>17</v>
@@ -2317,7 +2317,7 @@
         <v>23</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF5">
         <v>10.5</v>
@@ -2326,22 +2326,22 @@
         <v>20</v>
       </c>
       <c r="BH5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="BN5">
         <v>5.1</v>
@@ -2356,7 +2356,7 @@
         <v>12</v>
       </c>
       <c r="BR5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS5">
         <v>17.5</v>
@@ -2368,22 +2368,22 @@
         <v>6.4</v>
       </c>
       <c r="BV5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BX5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY5">
+        <v>24</v>
+      </c>
+      <c r="BZ5">
         <v>23</v>
       </c>
-      <c r="BZ5">
-        <v>22</v>
-      </c>
       <c r="CA5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>276</v>
@@ -2406,19 +2406,19 @@
         <v>216</v>
       </c>
       <c r="F6">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G6">
         <v>2.9</v>
       </c>
       <c r="H6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I6">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
         <v>4.1</v>
@@ -2454,7 +2454,7 @@
         <v>2.92</v>
       </c>
       <c r="V6">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W6">
         <v>1.53</v>
@@ -2469,7 +2469,7 @@
         <v>21</v>
       </c>
       <c r="AA6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB6">
         <v>19.5</v>
@@ -2496,7 +2496,7 @@
         <v>28</v>
       </c>
       <c r="AJ6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK6">
         <v>26</v>
@@ -2514,7 +2514,7 @@
         <v>12</v>
       </c>
       <c r="AP6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
         <v>16</v>
@@ -2538,7 +2538,7 @@
         <v>20</v>
       </c>
       <c r="AX6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY6">
         <v>12</v>
@@ -2562,22 +2562,22 @@
         <v>40</v>
       </c>
       <c r="BF6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG6">
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI6">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2589,13 +2589,13 @@
         <v>8.4</v>
       </c>
       <c r="BO6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU6">
         <v>4.7</v>
@@ -2613,7 +2613,7 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2648,76 +2648,76 @@
         <v>217</v>
       </c>
       <c r="F7">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S7">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V7">
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="X7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y7">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z7">
         <v>65</v>
       </c>
       <c r="AA7">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
         <v>24</v>
@@ -2726,19 +2726,19 @@
         <v>100</v>
       </c>
       <c r="AF7">
+        <v>10.5</v>
+      </c>
+      <c r="AG7">
         <v>10</v>
-      </c>
-      <c r="AG7">
-        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK7">
         <v>15.5</v>
@@ -2747,13 +2747,13 @@
         <v>38</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP7">
         <v>18.5</v>
@@ -2762,25 +2762,25 @@
         <v>20</v>
       </c>
       <c r="AR7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV7">
         <v>20</v>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY7">
         <v>9</v>
@@ -2789,31 +2789,31 @@
         <v>18</v>
       </c>
       <c r="BA7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB7">
         <v>13</v>
       </c>
       <c r="BC7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD7">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF7">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH7">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BI7">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BJ7">
         <v>18</v>
@@ -2893,10 +2893,10 @@
         <v>4.7</v>
       </c>
       <c r="G8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I8">
         <v>1.95</v>
@@ -2905,7 +2905,7 @@
         <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.44</v>
@@ -2944,7 +2944,7 @@
         <v>1.25</v>
       </c>
       <c r="X8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y8">
         <v>8.4</v>
@@ -2953,7 +2953,7 @@
         <v>11.5</v>
       </c>
       <c r="AA8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB8">
         <v>17.5</v>
@@ -3022,31 +3022,31 @@
         <v>16.5</v>
       </c>
       <c r="AX8">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY8">
         <v>16.5</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
+        <v>7.2</v>
+      </c>
+      <c r="BC8">
         <v>6.8</v>
       </c>
-      <c r="BC8">
-        <v>6.4</v>
-      </c>
       <c r="BD8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG8">
         <v>13</v>
@@ -3132,22 +3132,22 @@
         <v>219</v>
       </c>
       <c r="F9">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="G9">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>7.8</v>
+        <v>890</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3162,10 +3162,10 @@
         <v>1.21</v>
       </c>
       <c r="P9">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="Q9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R9">
         <v>1.46</v>
@@ -3180,10 +3180,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W9">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3288,7 +3288,7 @@
         <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG9">
         <v>1.01</v>
@@ -3380,7 +3380,7 @@
         <v>3.4</v>
       </c>
       <c r="H10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I10">
         <v>3.95</v>
@@ -3389,7 +3389,7 @@
         <v>2.4</v>
       </c>
       <c r="K10">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3398,25 +3398,25 @@
         <v>1.18</v>
       </c>
       <c r="N10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Q10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
         <v>1.13</v>
       </c>
       <c r="S10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T10">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U10">
         <v>1.6</v>
@@ -3485,13 +3485,13 @@
         <v>4.5</v>
       </c>
       <c r="AQ10">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AR10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AS10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AT10">
         <v>6</v>
@@ -3500,40 +3500,40 @@
         <v>4.5</v>
       </c>
       <c r="AV10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AW10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AX10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AY10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AZ10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BA10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BB10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BC10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BD10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BE10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BF10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BG10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BH10">
         <v>970</v>
@@ -3625,13 +3625,13 @@
         <v>1.22</v>
       </c>
       <c r="I11">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J11">
         <v>4.8</v>
       </c>
       <c r="K11">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3640,7 +3640,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
         <v>1.16</v>
@@ -3664,7 +3664,7 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="W11">
         <v>1.01</v>
@@ -3858,22 +3858,22 @@
         <v>222</v>
       </c>
       <c r="F12">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G12">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="H12">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K12">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.33</v>
@@ -3882,202 +3882,202 @@
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="O12">
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R12">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S12">
         <v>2.92</v>
       </c>
       <c r="T12">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U12">
         <v>1.99</v>
       </c>
       <c r="V12">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W12">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X12">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Y12">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="Z12">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD12">
         <v>30</v>
       </c>
       <c r="AE12">
-        <v>920</v>
+        <v>820</v>
       </c>
       <c r="AF12">
         <v>13.5</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH12">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AI12">
+        <v>920</v>
+      </c>
+      <c r="AJ12">
+        <v>75</v>
+      </c>
+      <c r="AK12">
+        <v>75</v>
+      </c>
+      <c r="AL12">
+        <v>110</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>17</v>
+      </c>
+      <c r="AO12">
         <v>930</v>
-      </c>
-      <c r="AJ12">
-        <v>26</v>
-      </c>
-      <c r="AK12">
-        <v>28</v>
-      </c>
-      <c r="AL12">
-        <v>910</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>12</v>
-      </c>
-      <c r="AO12">
-        <v>940</v>
       </c>
       <c r="AP12">
         <v>11.5</v>
       </c>
       <c r="AQ12">
+        <v>13</v>
+      </c>
+      <c r="AR12">
+        <v>8</v>
+      </c>
+      <c r="AS12">
+        <v>2.48</v>
+      </c>
+      <c r="AT12">
+        <v>6.4</v>
+      </c>
+      <c r="AU12">
+        <v>6.8</v>
+      </c>
+      <c r="AV12">
         <v>14.5</v>
       </c>
-      <c r="AR12">
-        <v>11</v>
-      </c>
-      <c r="AS12">
-        <v>3.7</v>
-      </c>
-      <c r="AT12">
-        <v>6.8</v>
-      </c>
-      <c r="AU12">
-        <v>7.2</v>
-      </c>
-      <c r="AV12">
-        <v>15.5</v>
-      </c>
       <c r="AW12">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AX12">
         <v>7.8</v>
       </c>
       <c r="AY12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ12">
         <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BB12">
         <v>13</v>
       </c>
       <c r="BC12">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD12">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE12">
-        <v>3.7</v>
+        <v>24</v>
       </c>
       <c r="BF12">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG12">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="BH12">
-        <v>3.95</v>
+        <v>970</v>
       </c>
       <c r="BI12">
         <v>2.88</v>
       </c>
       <c r="BJ12">
-        <v>920</v>
+        <v>970</v>
       </c>
       <c r="BK12">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BN12">
-        <v>4.9</v>
+        <v>970</v>
       </c>
       <c r="BO12">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="BQ12">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BT12">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="BU12">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="CB12" t="s">
         <v>276</v>
@@ -4390,10 +4390,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4626,10 +4626,10 @@
         <v>3.5</v>
       </c>
       <c r="T15">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="U15">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V15">
         <v>1.46</v>
@@ -4671,7 +4671,7 @@
         <v>21</v>
       </c>
       <c r="AI15">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ15">
         <v>55</v>
@@ -4844,7 +4844,7 @@
         <v>3.55</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M16">
         <v>1.01</v>
@@ -4853,10 +4853,10 @@
         <v>2.66</v>
       </c>
       <c r="O16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P16">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q16">
         <v>2.28</v>
@@ -5310,10 +5310,10 @@
         <v>228</v>
       </c>
       <c r="F18">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="G18">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H18">
         <v>3.55</v>
@@ -5325,7 +5325,7 @@
         <v>3.15</v>
       </c>
       <c r="K18">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5343,13 +5343,13 @@
         <v>1.73</v>
       </c>
       <c r="Q18">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <v>1.23</v>
       </c>
       <c r="S18">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5361,7 +5361,7 @@
         <v>1.26</v>
       </c>
       <c r="W18">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5555,19 +5555,19 @@
         <v>1.21</v>
       </c>
       <c r="G19">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="H19">
-        <v>2.08</v>
+        <v>5.7</v>
       </c>
       <c r="I19">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
         <v>1.23</v>
@@ -5585,10 +5585,10 @@
         <v>2.12</v>
       </c>
       <c r="Q19">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="R19">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S19">
         <v>2.66</v>
@@ -5603,7 +5603,7 @@
         <v>1.01</v>
       </c>
       <c r="W19">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5797,13 +5797,13 @@
         <v>1.85</v>
       </c>
       <c r="G20">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I20">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J20">
         <v>3.35</v>
@@ -5818,7 +5818,7 @@
         <v>1.09</v>
       </c>
       <c r="N20">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
         <v>1.38</v>
@@ -5830,37 +5830,37 @@
         <v>2.16</v>
       </c>
       <c r="R20">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S20">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="T20">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U20">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="V20">
         <v>1.23</v>
       </c>
       <c r="W20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X20">
         <v>14.5</v>
       </c>
       <c r="Y20">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z20">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA20">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>9.6</v>
@@ -5869,10 +5869,10 @@
         <v>24</v>
       </c>
       <c r="AE20">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG20">
         <v>13</v>
@@ -5893,7 +5893,7 @@
         <v>55</v>
       </c>
       <c r="AM20">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN20">
         <v>20</v>
@@ -5908,22 +5908,22 @@
         <v>12.5</v>
       </c>
       <c r="AR20">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
         <v>6.6</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV20">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW20">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
         <v>9.4</v>
@@ -5935,7 +5935,7 @@
         <v>15.5</v>
       </c>
       <c r="BA20">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
         <v>18.5</v>
@@ -5944,16 +5944,16 @@
         <v>16.5</v>
       </c>
       <c r="BD20">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>14</v>
       </c>
       <c r="BG20">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6036,22 +6036,22 @@
         <v>231</v>
       </c>
       <c r="F21">
+        <v>4.3</v>
+      </c>
+      <c r="G21">
+        <v>6.8</v>
+      </c>
+      <c r="H21">
+        <v>1.6</v>
+      </c>
+      <c r="I21">
+        <v>1.8</v>
+      </c>
+      <c r="J21">
         <v>4.2</v>
       </c>
-      <c r="G21">
-        <v>7.4</v>
-      </c>
-      <c r="H21">
-        <v>1.57</v>
-      </c>
-      <c r="I21">
-        <v>1.77</v>
-      </c>
-      <c r="J21">
-        <v>3.35</v>
-      </c>
       <c r="K21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -6060,10 +6060,10 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P21">
         <v>2.48</v>
@@ -6075,7 +6075,7 @@
         <v>1.6</v>
       </c>
       <c r="S21">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -6084,10 +6084,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6284,7 +6284,7 @@
         <v>6.4</v>
       </c>
       <c r="H22">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I22">
         <v>1.63</v>
@@ -6299,7 +6299,7 @@
         <v>1.38</v>
       </c>
       <c r="M22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
         <v>4.4</v>
@@ -6311,7 +6311,7 @@
         <v>2.18</v>
       </c>
       <c r="Q22">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R22">
         <v>1.44</v>
@@ -6386,7 +6386,7 @@
         <v>8.4</v>
       </c>
       <c r="AP22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ22">
         <v>8.6</v>
@@ -6398,10 +6398,10 @@
         <v>13.5</v>
       </c>
       <c r="AT22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV22">
         <v>9</v>
@@ -6434,7 +6434,7 @@
         <v>40</v>
       </c>
       <c r="BF22">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BG22">
         <v>7.8</v>
@@ -6449,49 +6449,49 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6526,7 +6526,7 @@
         <v>1.26</v>
       </c>
       <c r="H23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23">
         <v>18.5</v>
@@ -6535,7 +6535,7 @@
         <v>6.8</v>
       </c>
       <c r="K23">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>1.34</v>
@@ -6568,10 +6568,10 @@
         <v>1.62</v>
       </c>
       <c r="V23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X23">
         <v>22</v>
@@ -6607,7 +6607,7 @@
         <v>44</v>
       </c>
       <c r="AI23">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AJ23">
         <v>8.199999999999999</v>
@@ -6664,13 +6664,13 @@
         <v>90</v>
       </c>
       <c r="BB23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC23">
         <v>14</v>
       </c>
       <c r="BD23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE23">
         <v>50</v>
@@ -6682,55 +6682,55 @@
         <v>90</v>
       </c>
       <c r="BH23">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BI23">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ23">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BK23">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM23">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BN23">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BO23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP23">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BQ23">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR23">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BS23">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BU23">
         <v>13.5</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BW23">
         <v>27</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BY23">
         <v>27</v>
@@ -6765,10 +6765,10 @@
         <v>6.4</v>
       </c>
       <c r="G24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="I24">
         <v>1.61</v>
@@ -6777,7 +6777,7 @@
         <v>4.5</v>
       </c>
       <c r="K24">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>1.35</v>
@@ -6789,31 +6789,31 @@
         <v>4.3</v>
       </c>
       <c r="O24">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P24">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q24">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R24">
         <v>1.45</v>
       </c>
       <c r="S24">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T24">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U24">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V24">
         <v>2.64</v>
       </c>
       <c r="W24">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X24">
         <v>19.5</v>
@@ -6903,7 +6903,7 @@
         <v>17.5</v>
       </c>
       <c r="BA24">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BB24">
         <v>10</v>
@@ -7007,7 +7007,7 @@
         <v>1.5</v>
       </c>
       <c r="G25">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="H25">
         <v>7.2</v>
@@ -7028,34 +7028,34 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P25">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q25">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R25">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S25">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="T25">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="U25">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="V25">
         <v>1.13</v>
       </c>
       <c r="W25">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="X25">
         <v>22</v>
@@ -7172,7 +7172,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK25">
         <v>1.01</v>
@@ -7184,43 +7184,43 @@
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ25">
         <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS25">
         <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU25">
         <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW25">
         <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
@@ -7249,13 +7249,13 @@
         <v>2.84</v>
       </c>
       <c r="G26">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H26">
         <v>2.32</v>
       </c>
       <c r="I26">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J26">
         <v>3.5</v>
@@ -7279,7 +7279,7 @@
         <v>2.06</v>
       </c>
       <c r="Q26">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R26">
         <v>1.42</v>
@@ -7288,16 +7288,16 @@
         <v>2.94</v>
       </c>
       <c r="T26">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="U26">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W26">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X26">
         <v>21</v>
@@ -7488,22 +7488,22 @@
         <v>237</v>
       </c>
       <c r="F27">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H27">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="I27">
         <v>3.5</v>
       </c>
       <c r="J27">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7518,16 +7518,16 @@
         <v>1.24</v>
       </c>
       <c r="P27">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q27">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R27">
         <v>1.41</v>
       </c>
       <c r="S27">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="T27">
         <v>1.57</v>
@@ -7536,7 +7536,7 @@
         <v>2.22</v>
       </c>
       <c r="V27">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
         <v>1.64</v>
@@ -7566,7 +7566,7 @@
         <v>34</v>
       </c>
       <c r="AF27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG27">
         <v>12</v>
@@ -7754,19 +7754,19 @@
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O28">
         <v>1.2</v>
       </c>
       <c r="P28">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q28">
         <v>1.6</v>
       </c>
       <c r="R28">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S28">
         <v>2.5</v>
@@ -7787,7 +7787,7 @@
         <v>27</v>
       </c>
       <c r="Y28">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z28">
         <v>85</v>
@@ -7823,10 +7823,10 @@
         <v>13</v>
       </c>
       <c r="AK28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL28">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM28">
         <v>120</v>
@@ -7844,7 +7844,7 @@
         <v>13.5</v>
       </c>
       <c r="AR28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS28">
         <v>13</v>
@@ -7856,10 +7856,10 @@
         <v>10.5</v>
       </c>
       <c r="AV28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX28">
         <v>9</v>
@@ -7877,19 +7877,19 @@
         <v>11.5</v>
       </c>
       <c r="BC28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD28">
         <v>9.800000000000001</v>
       </c>
       <c r="BE28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF28">
         <v>5</v>
       </c>
       <c r="BG28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH28">
         <v>4.3</v>
@@ -7901,13 +7901,13 @@
         <v>12</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL28">
         <v>130</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28">
         <v>4.1</v>
@@ -7925,31 +7925,31 @@
         <v>24</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT28">
         <v>11.5</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV28">
         <v>70</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX28">
         <v>65</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ28">
         <v>14</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB28" t="s">
         <v>276</v>
@@ -7984,13 +7984,13 @@
         <v>6</v>
       </c>
       <c r="J29">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K29">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L29">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M29">
         <v>1.04</v>
@@ -8083,16 +8083,16 @@
         <v>19</v>
       </c>
       <c r="AQ29">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS29">
         <v>9.199999999999999</v>
       </c>
       <c r="AT29">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU29">
         <v>9</v>
@@ -8101,7 +8101,7 @@
         <v>18.5</v>
       </c>
       <c r="AW29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX29">
         <v>9.800000000000001</v>
@@ -8134,64 +8134,64 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH29">
-        <v>970</v>
+        <v>4.2</v>
       </c>
       <c r="BI29">
-        <v>1.45</v>
+        <v>3.75</v>
       </c>
       <c r="BJ29">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK29">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM29">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="BN29">
-        <v>970</v>
+        <v>4.5</v>
       </c>
       <c r="BO29">
-        <v>1.52</v>
+        <v>4</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ29">
-        <v>2.16</v>
+        <v>5.8</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS29">
-        <v>1.13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT29">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="BU29">
-        <v>1.93</v>
+        <v>5.4</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW29">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY29">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA29">
-        <v>1.13</v>
+        <v>7</v>
       </c>
       <c r="CB29" t="s">
         <v>276</v>
@@ -8456,58 +8456,58 @@
         <v>241</v>
       </c>
       <c r="F31">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G31">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H31">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="I31">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J31">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K31">
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
         <v>1.37</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N31">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="O31">
         <v>1.39</v>
       </c>
       <c r="P31">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q31">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R31">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="S31">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V31">
         <v>1.68</v>
       </c>
       <c r="W31">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X31">
         <v>12</v>
@@ -8567,7 +8567,7 @@
         <v>3.9</v>
       </c>
       <c r="AQ31">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR31">
         <v>4.1</v>
@@ -8591,16 +8591,16 @@
         <v>4.9</v>
       </c>
       <c r="AY31">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ31">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA31">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB31">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC31">
         <v>5.3</v>
@@ -8609,10 +8609,10 @@
         <v>5.4</v>
       </c>
       <c r="BE31">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF31">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG31">
         <v>4.8</v>
@@ -8704,16 +8704,16 @@
         <v>2.76</v>
       </c>
       <c r="H32">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I32">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K32">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8722,7 +8722,7 @@
         <v>1.04</v>
       </c>
       <c r="N32">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O32">
         <v>1.2</v>
@@ -8743,10 +8743,10 @@
         <v>1.52</v>
       </c>
       <c r="U32">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
         <v>1.57</v>
@@ -8755,7 +8755,7 @@
         <v>1000</v>
       </c>
       <c r="Y32">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z32">
         <v>30</v>
@@ -8803,19 +8803,19 @@
         <v>19</v>
       </c>
       <c r="AO32">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP32">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="AQ32">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AR32">
         <v>15</v>
       </c>
       <c r="AS32">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AT32">
         <v>10</v>
@@ -8824,7 +8824,7 @@
         <v>7.2</v>
       </c>
       <c r="AV32">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="AW32">
         <v>17.5</v>
@@ -8833,25 +8833,25 @@
         <v>13.5</v>
       </c>
       <c r="AY32">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="AZ32">
         <v>12</v>
       </c>
       <c r="BA32">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BB32">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BC32">
         <v>15.5</v>
       </c>
       <c r="BD32">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BE32">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="BF32">
         <v>11</v>
@@ -8866,58 +8866,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL32">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB32" t="s">
         <v>276</v>
@@ -8946,7 +8946,7 @@
         <v>5.4</v>
       </c>
       <c r="H33">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I33">
         <v>2.08</v>
@@ -8958,10 +8958,10 @@
         <v>3.75</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N33">
         <v>3.25</v>
@@ -8979,7 +8979,7 @@
         <v>1.25</v>
       </c>
       <c r="S33">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T33">
         <v>1.84</v>
@@ -9051,7 +9051,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR33">
         <v>1.01</v>
@@ -9063,7 +9063,7 @@
         <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV33">
         <v>1.01</v>
@@ -9102,7 +9102,7 @@
         <v>1.01</v>
       </c>
       <c r="BH33">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI33">
         <v>1.01</v>
@@ -9123,7 +9123,7 @@
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BP33">
         <v>1000</v>
@@ -9138,7 +9138,7 @@
         <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU33">
         <v>1.01</v>
@@ -9185,7 +9185,7 @@
         <v>2.38</v>
       </c>
       <c r="G34">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H34">
         <v>2.82</v>
@@ -9197,7 +9197,7 @@
         <v>3.65</v>
       </c>
       <c r="K34">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L34">
         <v>1.27</v>
@@ -9209,16 +9209,16 @@
         <v>4.7</v>
       </c>
       <c r="O34">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P34">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q34">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R34">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S34">
         <v>2.74</v>
@@ -9233,7 +9233,7 @@
         <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X34">
         <v>23</v>
@@ -9341,7 +9341,7 @@
         <v>13.5</v>
       </c>
       <c r="BG34">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH34">
         <v>4.6</v>
@@ -9350,58 +9350,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN34">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BO34">
         <v>1.01</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR34">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU34">
         <v>1.01</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA34">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB34" t="s">
         <v>276</v>
@@ -9430,13 +9430,13 @@
         <v>1.21</v>
       </c>
       <c r="H35">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I35">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J35">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K35">
         <v>10.5</v>
@@ -9448,40 +9448,40 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P35">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R35">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S35">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="T35">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="U35">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V35">
         <v>1.06</v>
       </c>
       <c r="W35">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X35">
         <v>1000</v>
       </c>
       <c r="Y35">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="Z35">
         <v>1000</v>
@@ -9490,43 +9490,43 @@
         <v>1000</v>
       </c>
       <c r="AB35">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AC35">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AD35">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AE35">
         <v>1000</v>
       </c>
       <c r="AF35">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG35">
         <v>14</v>
       </c>
       <c r="AH35">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AI35">
         <v>1000</v>
       </c>
       <c r="AJ35">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK35">
         <v>13.5</v>
       </c>
       <c r="AL35">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AM35">
         <v>1000</v>
       </c>
       <c r="AN35">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AO35">
         <v>1000</v>
@@ -9538,49 +9538,49 @@
         <v>42</v>
       </c>
       <c r="AR35">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AS35">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AT35">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU35">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AV35">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW35">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AX35">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY35">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ35">
         <v>24</v>
       </c>
       <c r="BA35">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BB35">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC35">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD35">
         <v>23</v>
       </c>
       <c r="BE35">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF35">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BG35">
         <v>44</v>
@@ -9610,7 +9610,7 @@
         <v>3.4</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ35">
         <v>4.8</v>
@@ -9666,10 +9666,10 @@
         <v>246</v>
       </c>
       <c r="F36">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G36">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H36">
         <v>1.86</v>
@@ -9678,10 +9678,10 @@
         <v>2.12</v>
       </c>
       <c r="J36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K36">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9690,7 +9690,7 @@
         <v>1.02</v>
       </c>
       <c r="N36">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="O36">
         <v>1.23</v>
@@ -9699,25 +9699,25 @@
         <v>2.18</v>
       </c>
       <c r="Q36">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R36">
         <v>1.47</v>
       </c>
       <c r="S36">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T36">
         <v>1.59</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V36">
         <v>1.9</v>
       </c>
       <c r="W36">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9735,7 +9735,7 @@
         <v>1000</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD36">
         <v>1000</v>
@@ -9771,40 +9771,40 @@
         <v>1000</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP36">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR36">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS36">
         <v>1.01</v>
       </c>
       <c r="AT36">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU36">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV36">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW36">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX36">
         <v>1.01</v>
       </c>
       <c r="AY36">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA36">
         <v>1.01</v>
@@ -9825,7 +9825,7 @@
         <v>1.01</v>
       </c>
       <c r="BG36">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9911,7 +9911,7 @@
         <v>2.68</v>
       </c>
       <c r="G37">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H37">
         <v>3</v>
@@ -9926,10 +9926,10 @@
         <v>3.25</v>
       </c>
       <c r="L37">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M37">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N37">
         <v>2.78</v>
@@ -9938,16 +9938,16 @@
         <v>1.5</v>
       </c>
       <c r="P37">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q37">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R37">
         <v>1.22</v>
       </c>
       <c r="S37">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T37">
         <v>2</v>
@@ -9959,7 +9959,7 @@
         <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X37">
         <v>9.4</v>
@@ -9977,7 +9977,7 @@
         <v>9</v>
       </c>
       <c r="AC37">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD37">
         <v>15</v>
@@ -10025,7 +10025,7 @@
         <v>17</v>
       </c>
       <c r="AS37">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT37">
         <v>7.8</v>
@@ -10034,100 +10034,100 @@
         <v>6.2</v>
       </c>
       <c r="AV37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW37">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="AX37">
         <v>14</v>
       </c>
       <c r="AY37">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ37">
         <v>17.5</v>
       </c>
       <c r="BA37">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB37">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC37">
         <v>8</v>
       </c>
       <c r="BD37">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE37">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF37">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BG37">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH37">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="BI37">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK37">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BN37">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO37">
         <v>3.9</v>
       </c>
       <c r="BP37">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BR37">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS37">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="BT37">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU37">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="BV37">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW37">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BX37">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY37">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="BZ37">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA37">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="CB37" t="s">
         <v>276</v>
@@ -10150,10 +10150,10 @@
         <v>248</v>
       </c>
       <c r="F38">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G38">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H38">
         <v>4.2</v>
@@ -10162,10 +10162,10 @@
         <v>4.5</v>
       </c>
       <c r="J38">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K38">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L38">
         <v>1.27</v>
@@ -10183,13 +10183,13 @@
         <v>2.46</v>
       </c>
       <c r="Q38">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R38">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S38">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T38">
         <v>1.53</v>
@@ -10198,118 +10198,118 @@
         <v>2.34</v>
       </c>
       <c r="V38">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W38">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X38">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Y38">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Z38">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AA38">
         <v>100</v>
       </c>
       <c r="AB38">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AC38">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD38">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF38">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH38">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI38">
         <v>55</v>
       </c>
       <c r="AJ38">
+        <v>30</v>
+      </c>
+      <c r="AK38">
         <v>23</v>
-      </c>
-      <c r="AK38">
-        <v>18</v>
       </c>
       <c r="AL38">
         <v>36</v>
       </c>
       <c r="AM38">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO38">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP38">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AQ38">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AR38">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AS38">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AT38">
+        <v>10</v>
+      </c>
+      <c r="AU38">
+        <v>8</v>
+      </c>
+      <c r="AV38">
+        <v>13.5</v>
+      </c>
+      <c r="AW38">
+        <v>4.3</v>
+      </c>
+      <c r="AX38">
         <v>11.5</v>
       </c>
-      <c r="AU38">
-        <v>8.6</v>
-      </c>
-      <c r="AV38">
-        <v>15</v>
-      </c>
-      <c r="AW38">
-        <v>22</v>
-      </c>
-      <c r="AX38">
+      <c r="AY38">
+        <v>8.4</v>
+      </c>
+      <c r="AZ38">
         <v>12.5</v>
       </c>
-      <c r="AY38">
-        <v>9.6</v>
-      </c>
-      <c r="AZ38">
-        <v>13.5</v>
-      </c>
       <c r="BA38">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="BB38">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC38">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD38">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE38">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF38">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG38">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="BH38">
         <v>970</v>
@@ -10318,7 +10318,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ38">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="BK38">
         <v>1.01</v>
@@ -10416,7 +10416,7 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O39">
         <v>1.22</v>
@@ -10446,112 +10446,112 @@
         <v>1.2</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP39">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ39">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR39">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AS39">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AT39">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AU39">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV39">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW39">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AX39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY39">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AZ39">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA39">
         <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF39">
         <v>1.01</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10637,7 +10637,7 @@
         <v>1.94</v>
       </c>
       <c r="G40">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H40">
         <v>4.2</v>
@@ -10658,19 +10658,19 @@
         <v>1.07</v>
       </c>
       <c r="N40">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O40">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P40">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q40">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R40">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S40">
         <v>3.35</v>
@@ -10685,7 +10685,7 @@
         <v>1.28</v>
       </c>
       <c r="W40">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X40">
         <v>15</v>
@@ -10799,61 +10799,61 @@
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BJ40">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK40">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BN40">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO40">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP40">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ40">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BR40">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS40">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BT40">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU40">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV40">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW40">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BX40">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY40">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ40">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA40">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="CB40" t="s">
         <v>276</v>
@@ -10876,22 +10876,22 @@
         <v>251</v>
       </c>
       <c r="F41">
-        <v>1.02</v>
+        <v>2.22</v>
       </c>
       <c r="G41">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H41">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="I41">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J41">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K41">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10900,22 +10900,22 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O41">
         <v>1.01</v>
       </c>
       <c r="P41">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q41">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R41">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>2.98</v>
       </c>
       <c r="T41">
         <v>1.01</v>
@@ -10924,10 +10924,10 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W41">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -11118,10 +11118,10 @@
         <v>252</v>
       </c>
       <c r="F42">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G42">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H42">
         <v>17</v>
@@ -11130,10 +11130,10 @@
         <v>23</v>
       </c>
       <c r="J42">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K42">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -11142,22 +11142,22 @@
         <v>1.04</v>
       </c>
       <c r="N42">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O42">
         <v>1.2</v>
       </c>
       <c r="P42">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q42">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R42">
         <v>1.57</v>
       </c>
       <c r="S42">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T42">
         <v>2.38</v>
@@ -11169,10 +11169,10 @@
         <v>1.05</v>
       </c>
       <c r="W42">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="X42">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y42">
         <v>60</v>
@@ -11187,10 +11187,10 @@
         <v>9</v>
       </c>
       <c r="AC42">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AD42">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AE42">
         <v>430</v>
@@ -11229,7 +11229,7 @@
         <v>19</v>
       </c>
       <c r="AQ42">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AR42">
         <v>1.01</v>
@@ -11250,7 +11250,7 @@
         <v>1.01</v>
       </c>
       <c r="AX42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY42">
         <v>10.5</v>
@@ -11262,19 +11262,19 @@
         <v>1.01</v>
       </c>
       <c r="BB42">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC42">
         <v>13</v>
       </c>
       <c r="BD42">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE42">
         <v>1.01</v>
       </c>
       <c r="BF42">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG42">
         <v>1.01</v>
@@ -11363,19 +11363,19 @@
         <v>2.3</v>
       </c>
       <c r="G43">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="H43">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I43">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J43">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="K43">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11384,7 +11384,7 @@
         <v>1.05</v>
       </c>
       <c r="N43">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O43">
         <v>1.24</v>
@@ -11393,25 +11393,25 @@
         <v>2.18</v>
       </c>
       <c r="Q43">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S43">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="T43">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="U43">
         <v>2.28</v>
       </c>
       <c r="V43">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11429,7 +11429,7 @@
         <v>1000</v>
       </c>
       <c r="AC43">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD43">
         <v>1000</v>
@@ -11441,7 +11441,7 @@
         <v>1000</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH43">
         <v>1000</v>
@@ -11468,10 +11468,10 @@
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR43">
         <v>1.01</v>
@@ -11480,25 +11480,25 @@
         <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU43">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV43">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW43">
         <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY43">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA43">
         <v>1.01</v>
@@ -11516,7 +11516,7 @@
         <v>1.01</v>
       </c>
       <c r="BF43">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG43">
         <v>1.01</v>
@@ -11525,7 +11525,7 @@
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
@@ -11602,10 +11602,10 @@
         <v>254</v>
       </c>
       <c r="F44">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="G44">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H44">
         <v>2.66</v>
@@ -11614,10 +11614,10 @@
         <v>2.82</v>
       </c>
       <c r="J44">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K44">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L44">
         <v>1.42</v>
@@ -11632,10 +11632,10 @@
         <v>1.3</v>
       </c>
       <c r="P44">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q44">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R44">
         <v>1.33</v>
@@ -11644,16 +11644,16 @@
         <v>3.15</v>
       </c>
       <c r="T44">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U44">
         <v>2.08</v>
       </c>
       <c r="V44">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W44">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X44">
         <v>970</v>
@@ -11671,10 +11671,10 @@
         <v>970</v>
       </c>
       <c r="AC44">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD44">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE44">
         <v>1000</v>
@@ -11710,58 +11710,58 @@
         <v>1000</v>
       </c>
       <c r="AP44">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ44">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS44">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AT44">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU44">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV44">
         <v>8.4</v>
       </c>
       <c r="AW44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AX44">
         <v>11.5</v>
       </c>
       <c r="AY44">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ44">
         <v>10.5</v>
       </c>
       <c r="BA44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BB44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BC44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BD44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BE44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BF44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BG44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BH44">
         <v>970</v>
@@ -11874,10 +11874,10 @@
         <v>1.13</v>
       </c>
       <c r="P45">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q45">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R45">
         <v>1.74</v>
@@ -11916,7 +11916,7 @@
         <v>22</v>
       </c>
       <c r="AD45">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE45">
         <v>1000</v>
@@ -11925,7 +11925,7 @@
         <v>1000</v>
       </c>
       <c r="AG45">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH45">
         <v>1000</v>
@@ -12086,22 +12086,22 @@
         <v>256</v>
       </c>
       <c r="F46">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G46">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H46">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="I46">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="J46">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K46">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12134,10 +12134,10 @@
         <v>1.01</v>
       </c>
       <c r="V46">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="W46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12328,7 +12328,7 @@
         <v>257</v>
       </c>
       <c r="F47">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G47">
         <v>1.51</v>
@@ -12343,7 +12343,7 @@
         <v>4.7</v>
       </c>
       <c r="K47">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12352,19 +12352,19 @@
         <v>1.04</v>
       </c>
       <c r="N47">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O47">
         <v>1.22</v>
       </c>
       <c r="P47">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q47">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R47">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S47">
         <v>2.68</v>
@@ -12373,7 +12373,7 @@
         <v>1.92</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V47">
         <v>1.11</v>
@@ -12406,7 +12406,7 @@
         <v>150</v>
       </c>
       <c r="AF47">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG47">
         <v>12.5</v>
@@ -12451,7 +12451,7 @@
         <v>7.8</v>
       </c>
       <c r="AU47">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV47">
         <v>6</v>
@@ -12463,7 +12463,7 @@
         <v>7.8</v>
       </c>
       <c r="AY47">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ47">
         <v>20</v>
@@ -12472,7 +12472,7 @@
         <v>7</v>
       </c>
       <c r="BB47">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC47">
         <v>13</v>
@@ -12493,7 +12493,7 @@
         <v>1000</v>
       </c>
       <c r="BI47">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ47">
         <v>1000</v>
@@ -12508,7 +12508,7 @@
         <v>1.01</v>
       </c>
       <c r="BN47">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO47">
         <v>1.01</v>
@@ -12570,25 +12570,25 @@
         <v>258</v>
       </c>
       <c r="F48">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H48">
         <v>13.5</v>
       </c>
       <c r="I48">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J48">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="K48">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L48">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M48">
         <v>1.04</v>
@@ -12597,10 +12597,10 @@
         <v>6</v>
       </c>
       <c r="O48">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P48">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q48">
         <v>1.56</v>
@@ -12615,13 +12615,13 @@
         <v>2.12</v>
       </c>
       <c r="U48">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V48">
         <v>1.07</v>
       </c>
       <c r="W48">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="X48">
         <v>27</v>
@@ -12633,7 +12633,7 @@
         <v>1000</v>
       </c>
       <c r="AA48">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="AB48">
         <v>10.5</v>
@@ -12672,7 +12672,7 @@
         <v>1000</v>
       </c>
       <c r="AN48">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AO48">
         <v>240</v>
@@ -12696,19 +12696,19 @@
         <v>13.5</v>
       </c>
       <c r="AV48">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AW48">
         <v>48</v>
       </c>
       <c r="AX48">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY48">
         <v>10.5</v>
       </c>
       <c r="AZ48">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA48">
         <v>44</v>
@@ -12732,22 +12732,22 @@
         <v>50</v>
       </c>
       <c r="BH48">
-        <v>5.1</v>
+        <v>970</v>
       </c>
       <c r="BI48">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ48">
         <v>34</v>
       </c>
       <c r="BK48">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BN48">
         <v>4.3</v>
@@ -12756,34 +12756,34 @@
         <v>3.15</v>
       </c>
       <c r="BP48">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="BQ48">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR48">
         <v>1000</v>
       </c>
       <c r="BS48">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT48">
         <v>1000</v>
       </c>
       <c r="BU48">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV48">
         <v>1000</v>
       </c>
       <c r="BW48">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BX48">
         <v>1000</v>
       </c>
       <c r="BY48">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ48">
         <v>0</v>
@@ -12812,22 +12812,22 @@
         <v>259</v>
       </c>
       <c r="F49">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G49">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H49">
         <v>2.44</v>
       </c>
       <c r="I49">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J49">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K49">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L49">
         <v>1.31</v>
@@ -12842,115 +12842,115 @@
         <v>1.23</v>
       </c>
       <c r="P49">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q49">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="R49">
         <v>1.42</v>
       </c>
       <c r="S49">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T49">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="U49">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W49">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X49">
         <v>1000</v>
       </c>
       <c r="Y49">
+        <v>16</v>
+      </c>
+      <c r="Z49">
+        <v>26</v>
+      </c>
+      <c r="AA49">
+        <v>55</v>
+      </c>
+      <c r="AB49">
+        <v>17</v>
+      </c>
+      <c r="AC49">
+        <v>10</v>
+      </c>
+      <c r="AD49">
+        <v>15.5</v>
+      </c>
+      <c r="AE49">
+        <v>38</v>
+      </c>
+      <c r="AF49">
+        <v>26</v>
+      </c>
+      <c r="AG49">
+        <v>16</v>
+      </c>
+      <c r="AH49">
+        <v>20</v>
+      </c>
+      <c r="AI49">
+        <v>46</v>
+      </c>
+      <c r="AJ49">
+        <v>60</v>
+      </c>
+      <c r="AK49">
+        <v>46</v>
+      </c>
+      <c r="AL49">
+        <v>48</v>
+      </c>
+      <c r="AM49">
+        <v>100</v>
+      </c>
+      <c r="AN49">
         <v>32</v>
       </c>
-      <c r="Z49">
-        <v>1000</v>
-      </c>
-      <c r="AA49">
-        <v>1000</v>
-      </c>
-      <c r="AB49">
-        <v>32</v>
-      </c>
-      <c r="AC49">
+      <c r="AO49">
+        <v>28</v>
+      </c>
+      <c r="AP49">
+        <v>1.01</v>
+      </c>
+      <c r="AQ49">
+        <v>9.6</v>
+      </c>
+      <c r="AR49">
         <v>13</v>
       </c>
-      <c r="AD49">
-        <v>30</v>
-      </c>
-      <c r="AE49">
-        <v>1000</v>
-      </c>
-      <c r="AF49">
-        <v>1000</v>
-      </c>
-      <c r="AG49">
-        <v>46</v>
-      </c>
-      <c r="AH49">
-        <v>1000</v>
-      </c>
-      <c r="AI49">
-        <v>1000</v>
-      </c>
-      <c r="AJ49">
-        <v>1000</v>
-      </c>
-      <c r="AK49">
-        <v>1000</v>
-      </c>
-      <c r="AL49">
-        <v>1000</v>
-      </c>
-      <c r="AM49">
-        <v>1000</v>
-      </c>
-      <c r="AN49">
-        <v>1000</v>
-      </c>
-      <c r="AO49">
-        <v>1000</v>
-      </c>
-      <c r="AP49">
-        <v>10</v>
-      </c>
-      <c r="AQ49">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR49">
-        <v>10.5</v>
-      </c>
       <c r="AS49">
         <v>1.01</v>
       </c>
       <c r="AT49">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU49">
         <v>6.2</v>
       </c>
       <c r="AV49">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW49">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX49">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY49">
         <v>9</v>
       </c>
       <c r="AZ49">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA49">
         <v>1.01</v>
@@ -12959,7 +12959,7 @@
         <v>1.01</v>
       </c>
       <c r="BC49">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD49">
         <v>1.01</v>
@@ -12968,22 +12968,22 @@
         <v>1.01</v>
       </c>
       <c r="BF49">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG49">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BH49">
-        <v>4.2</v>
+        <v>970</v>
       </c>
       <c r="BI49">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ49">
         <v>1000</v>
       </c>
       <c r="BK49">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL49">
         <v>1000</v>
@@ -12992,10 +12992,10 @@
         <v>1.01</v>
       </c>
       <c r="BN49">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO49">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP49">
         <v>1000</v>
@@ -13013,7 +13013,7 @@
         <v>1000</v>
       </c>
       <c r="BU49">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV49">
         <v>1000</v>
@@ -13054,79 +13054,79 @@
         <v>260</v>
       </c>
       <c r="F50">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="H50">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="J50">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K50">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L50">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N50">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="O50">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="P50">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="Q50">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="R50">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="S50">
-        <v>1.72</v>
+        <v>2.98</v>
       </c>
       <c r="T50">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U50">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X50">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y50">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z50">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA50">
         <v>1000</v>
       </c>
       <c r="AB50">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AC50">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD50">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE50">
         <v>1000</v>
@@ -13135,7 +13135,7 @@
         <v>1000</v>
       </c>
       <c r="AG50">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH50">
         <v>1000</v>
@@ -13177,7 +13177,7 @@
         <v>1.01</v>
       </c>
       <c r="AU50">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV50">
         <v>1.01</v>
@@ -13216,7 +13216,7 @@
         <v>1.01</v>
       </c>
       <c r="BH50">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI50">
         <v>1.01</v>
@@ -13252,7 +13252,7 @@
         <v>1.01</v>
       </c>
       <c r="BT50">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU50">
         <v>1.01</v>
@@ -13296,22 +13296,22 @@
         <v>261</v>
       </c>
       <c r="F51">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="G51">
         <v>2.58</v>
       </c>
       <c r="H51">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="I51">
         <v>3.25</v>
       </c>
       <c r="J51">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K51">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L51">
         <v>1.37</v>
@@ -13320,7 +13320,7 @@
         <v>1.07</v>
       </c>
       <c r="N51">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O51">
         <v>1.31</v>
@@ -13329,7 +13329,7 @@
         <v>1.84</v>
       </c>
       <c r="Q51">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R51">
         <v>1.32</v>
@@ -13350,22 +13350,22 @@
         <v>1.64</v>
       </c>
       <c r="X51">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y51">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Z51">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA51">
         <v>1000</v>
       </c>
       <c r="AB51">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC51">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AD51">
         <v>44</v>
@@ -13377,10 +13377,10 @@
         <v>65</v>
       </c>
       <c r="AG51">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AH51">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AI51">
         <v>1000</v>
@@ -13404,61 +13404,61 @@
         <v>1000</v>
       </c>
       <c r="AP51">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="AQ51">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR51">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AS51">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AT51">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU51">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV51">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW51">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX51">
         <v>8.4</v>
       </c>
       <c r="AY51">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="AZ51">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BA51">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BB51">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC51">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD51">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BE51">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BF51">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BG51">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BH51">
-        <v>3.7</v>
+        <v>970</v>
       </c>
       <c r="BI51">
         <v>1.01</v>
@@ -13476,7 +13476,7 @@
         <v>1.01</v>
       </c>
       <c r="BN51">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="BO51">
         <v>1.01</v>
@@ -13494,7 +13494,7 @@
         <v>1.01</v>
       </c>
       <c r="BT51">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU51">
         <v>1.01</v>
@@ -13538,19 +13538,19 @@
         <v>262</v>
       </c>
       <c r="F52">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="G52">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H52">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I52">
         <v>5.3</v>
       </c>
       <c r="J52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K52">
         <v>4.6</v>
@@ -13565,7 +13565,7 @@
         <v>3.4</v>
       </c>
       <c r="O52">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P52">
         <v>1.84</v>
@@ -13577,7 +13577,7 @@
         <v>1.32</v>
       </c>
       <c r="S52">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T52">
         <v>1.82</v>
@@ -13589,7 +13589,7 @@
         <v>1.24</v>
       </c>
       <c r="W52">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X52">
         <v>34</v>
@@ -13604,10 +13604,10 @@
         <v>1000</v>
       </c>
       <c r="AB52">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC52">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD52">
         <v>1000</v>
@@ -13670,13 +13670,13 @@
         <v>1.01</v>
       </c>
       <c r="AX52">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY52">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ52">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA52">
         <v>1.01</v>
@@ -13694,22 +13694,22 @@
         <v>1.01</v>
       </c>
       <c r="BF52">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG52">
         <v>1.01</v>
       </c>
       <c r="BH52">
-        <v>3.75</v>
+        <v>970</v>
       </c>
       <c r="BI52">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ52">
         <v>1000</v>
       </c>
       <c r="BK52">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL52">
         <v>1000</v>
@@ -13718,10 +13718,10 @@
         <v>1.01</v>
       </c>
       <c r="BN52">
-        <v>5.2</v>
+        <v>970</v>
       </c>
       <c r="BO52">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP52">
         <v>1000</v>
@@ -13739,7 +13739,7 @@
         <v>1000</v>
       </c>
       <c r="BU52">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV52">
         <v>1000</v>
@@ -13780,22 +13780,22 @@
         <v>263</v>
       </c>
       <c r="F53">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H53">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I53">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J53">
         <v>3.65</v>
       </c>
       <c r="K53">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="L53">
         <v>1.28</v>
@@ -13810,10 +13810,10 @@
         <v>1.23</v>
       </c>
       <c r="P53">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q53">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R53">
         <v>1.39</v>
@@ -13828,7 +13828,7 @@
         <v>1.01</v>
       </c>
       <c r="V53">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W53">
         <v>1.37</v>
@@ -13945,7 +13945,7 @@
         <v>1000</v>
       </c>
       <c r="BI53">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ53">
         <v>1000</v>
@@ -14022,16 +14022,16 @@
         <v>264</v>
       </c>
       <c r="F54">
+        <v>2.4</v>
+      </c>
+      <c r="G54">
         <v>2.44</v>
       </c>
-      <c r="G54">
-        <v>2.46</v>
-      </c>
       <c r="H54">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I54">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J54">
         <v>3.65</v>
@@ -14067,13 +14067,13 @@
         <v>1.69</v>
       </c>
       <c r="U54">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V54">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W54">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X54">
         <v>16</v>
@@ -14094,7 +14094,7 @@
         <v>7.8</v>
       </c>
       <c r="AD54">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE54">
         <v>34</v>
@@ -14199,7 +14199,7 @@
         <v>1000</v>
       </c>
       <c r="BM54">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BN54">
         <v>6.2</v>
@@ -14217,7 +14217,7 @@
         <v>1000</v>
       </c>
       <c r="BS54">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT54">
         <v>970</v>
@@ -14229,19 +14229,19 @@
         <v>1000</v>
       </c>
       <c r="BW54">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX54">
         <v>1000</v>
       </c>
       <c r="BY54">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ54">
         <v>1000</v>
       </c>
       <c r="CA54">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB54" t="s">
         <v>276</v>
@@ -14264,13 +14264,13 @@
         <v>265</v>
       </c>
       <c r="F55">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G55">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H55">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I55">
         <v>4</v>
@@ -14300,7 +14300,7 @@
         <v>1.64</v>
       </c>
       <c r="R55">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S55">
         <v>2.56</v>
@@ -14315,7 +14315,7 @@
         <v>1.33</v>
       </c>
       <c r="W55">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X55">
         <v>24</v>
@@ -14384,7 +14384,7 @@
         <v>60</v>
       </c>
       <c r="AT55">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU55">
         <v>8.800000000000001</v>
@@ -14396,7 +14396,7 @@
         <v>34</v>
       </c>
       <c r="AX55">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY55">
         <v>9.6</v>
@@ -14441,7 +14441,7 @@
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN55">
         <v>5.9</v>
@@ -14459,7 +14459,7 @@
         <v>1000</v>
       </c>
       <c r="BS55">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT55">
         <v>970</v>
@@ -14471,19 +14471,19 @@
         <v>1000</v>
       </c>
       <c r="BW55">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX55">
         <v>1000</v>
       </c>
       <c r="BY55">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BZ55">
         <v>1000</v>
       </c>
       <c r="CA55">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB55" t="s">
         <v>276</v>
@@ -14506,13 +14506,13 @@
         <v>266</v>
       </c>
       <c r="F56">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G56">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H56">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I56">
         <v>3.4</v>
@@ -14539,13 +14539,13 @@
         <v>1.58</v>
       </c>
       <c r="Q56">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R56">
         <v>1.2</v>
       </c>
       <c r="S56">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T56">
         <v>1.86</v>
@@ -14554,10 +14554,10 @@
         <v>1.83</v>
       </c>
       <c r="V56">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W56">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="X56">
         <v>10.5</v>
@@ -14748,19 +14748,19 @@
         <v>267</v>
       </c>
       <c r="F57">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G57">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H57">
         <v>8</v>
       </c>
       <c r="I57">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J57">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K57">
         <v>5</v>
@@ -14781,7 +14781,7 @@
         <v>2.18</v>
       </c>
       <c r="Q57">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R57">
         <v>1.45</v>
@@ -14799,7 +14799,7 @@
         <v>1.13</v>
       </c>
       <c r="W57">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X57">
         <v>22</v>
@@ -14844,7 +14844,7 @@
         <v>16.5</v>
       </c>
       <c r="AL57">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM57">
         <v>150</v>
@@ -14919,13 +14919,13 @@
         <v>15</v>
       </c>
       <c r="BK57">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BL57">
         <v>1000</v>
       </c>
       <c r="BM57">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="BN57">
         <v>5.2</v>
@@ -14937,37 +14937,37 @@
         <v>12</v>
       </c>
       <c r="BQ57">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BR57">
         <v>34</v>
       </c>
       <c r="BS57">
-        <v>15</v>
+        <v>3.2</v>
       </c>
       <c r="BT57">
         <v>15.5</v>
       </c>
       <c r="BU57">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV57">
         <v>95</v>
       </c>
       <c r="BW57">
-        <v>21</v>
+        <v>3.4</v>
       </c>
       <c r="BX57">
         <v>90</v>
       </c>
       <c r="BY57">
-        <v>21</v>
+        <v>3.4</v>
       </c>
       <c r="BZ57">
         <v>21</v>
       </c>
       <c r="CA57">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="CB57" t="s">
         <v>276</v>
@@ -14990,19 +14990,19 @@
         <v>268</v>
       </c>
       <c r="F58">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G58">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H58">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I58">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J58">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K58">
         <v>3.45</v>
@@ -15032,7 +15032,7 @@
         <v>5.7</v>
       </c>
       <c r="T58">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U58">
         <v>1.59</v>
@@ -15041,25 +15041,25 @@
         <v>1.34</v>
       </c>
       <c r="W58">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X58">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y58">
+        <v>13.5</v>
+      </c>
+      <c r="Z58">
+        <v>26</v>
+      </c>
+      <c r="AA58">
+        <v>100</v>
+      </c>
+      <c r="AB58">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z58">
-        <v>30</v>
-      </c>
-      <c r="AA58">
-        <v>110</v>
-      </c>
-      <c r="AB58">
-        <v>7</v>
-      </c>
       <c r="AC58">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AD58">
         <v>18.5</v>
@@ -15068,16 +15068,16 @@
         <v>85</v>
       </c>
       <c r="AF58">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AG58">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AH58">
         <v>34</v>
       </c>
       <c r="AI58">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ58">
         <v>50</v>
@@ -15086,70 +15086,70 @@
         <v>50</v>
       </c>
       <c r="AL58">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM58">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AN58">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO58">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP58">
+        <v>5.5</v>
+      </c>
+      <c r="AQ58">
         <v>6.4</v>
       </c>
-      <c r="AQ58">
-        <v>8</v>
-      </c>
       <c r="AR58">
-        <v>20</v>
+        <v>2.38</v>
       </c>
       <c r="AS58">
-        <v>8.4</v>
+        <v>2.32</v>
       </c>
       <c r="AT58">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AU58">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV58">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AW58">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="AX58">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY58">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AZ58">
-        <v>7.4</v>
+        <v>2.22</v>
       </c>
       <c r="BA58">
-        <v>8.6</v>
+        <v>2.32</v>
       </c>
       <c r="BB58">
-        <v>8.199999999999999</v>
+        <v>2.26</v>
       </c>
       <c r="BC58">
-        <v>8.199999999999999</v>
+        <v>2.26</v>
       </c>
       <c r="BD58">
-        <v>8.4</v>
+        <v>2.32</v>
       </c>
       <c r="BE58">
-        <v>9</v>
+        <v>2.36</v>
       </c>
       <c r="BF58">
-        <v>8</v>
+        <v>2.28</v>
       </c>
       <c r="BG58">
-        <v>8.6</v>
+        <v>2.32</v>
       </c>
       <c r="BH58">
         <v>2.6</v>
@@ -15235,37 +15235,37 @@
         <v>3.25</v>
       </c>
       <c r="G59">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H59">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I59">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J59">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K59">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="L59">
         <v>1.71</v>
       </c>
       <c r="M59">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N59">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O59">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="P59">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Q59">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="R59">
         <v>1.12</v>
@@ -15277,16 +15277,16 @@
         <v>2.42</v>
       </c>
       <c r="U59">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V59">
         <v>1.51</v>
       </c>
       <c r="W59">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X59">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y59">
         <v>9.800000000000001</v>
@@ -15298,10 +15298,10 @@
         <v>1000</v>
       </c>
       <c r="AB59">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC59">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD59">
         <v>1000</v>
@@ -15316,16 +15316,16 @@
         <v>1000</v>
       </c>
       <c r="AH59">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AI59">
         <v>1000</v>
       </c>
       <c r="AJ59">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK59">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL59">
         <v>1000</v>
@@ -15337,61 +15337,61 @@
         <v>1000</v>
       </c>
       <c r="AO59">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP59">
         <v>4.9</v>
       </c>
       <c r="AQ59">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR59">
-        <v>9.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="AS59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AT59">
         <v>5.8</v>
       </c>
       <c r="AU59">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AV59">
         <v>10</v>
       </c>
       <c r="AW59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AX59">
-        <v>1.84</v>
+        <v>17.5</v>
       </c>
       <c r="AY59">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AZ59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BA59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BB59">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="BC59">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="BD59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BE59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BF59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BG59">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="BH59">
         <v>2.42</v>
@@ -15474,22 +15474,22 @@
         <v>270</v>
       </c>
       <c r="F60">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G60">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H60">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I60">
         <v>2.44</v>
       </c>
       <c r="J60">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K60">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L60">
         <v>1.4</v>
@@ -15501,34 +15501,34 @@
         <v>3.15</v>
       </c>
       <c r="O60">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P60">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q60">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R60">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S60">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T60">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U60">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V60">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W60">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X60">
-        <v>890</v>
+        <v>800</v>
       </c>
       <c r="Y60">
         <v>14.5</v>
@@ -15725,7 +15725,7 @@
         <v>3</v>
       </c>
       <c r="I61">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J61">
         <v>2.62</v>
@@ -15764,7 +15764,7 @@
         <v>1.01</v>
       </c>
       <c r="V61">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W61">
         <v>1.53</v>
@@ -15964,10 +15964,10 @@
         <v>2.6</v>
       </c>
       <c r="H62">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I62">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J62">
         <v>2.76</v>
@@ -15991,13 +15991,13 @@
         <v>1.48</v>
       </c>
       <c r="Q62">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R62">
         <v>1.18</v>
       </c>
       <c r="S62">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T62">
         <v>2.06</v>
@@ -16006,10 +16006,10 @@
         <v>1.68</v>
       </c>
       <c r="V62">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W62">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X62">
         <v>11</v>
@@ -16200,7 +16200,7 @@
         <v>273</v>
       </c>
       <c r="F63">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G63">
         <v>1.87</v>
@@ -16215,7 +16215,7 @@
         <v>3.45</v>
       </c>
       <c r="K63">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L63">
         <v>1.01</v>
@@ -16233,13 +16233,13 @@
         <v>1.63</v>
       </c>
       <c r="Q63">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R63">
         <v>1.19</v>
       </c>
       <c r="S63">
-        <v>3.3</v>
+        <v>2.46</v>
       </c>
       <c r="T63">
         <v>1.01</v>
@@ -16445,16 +16445,16 @@
         <v>1.45</v>
       </c>
       <c r="G64">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="H64">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I64">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="J64">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="K64">
         <v>5.2</v>
@@ -16466,7 +16466,7 @@
         <v>1.04</v>
       </c>
       <c r="N64">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O64">
         <v>1.24</v>
@@ -16484,7 +16484,7 @@
         <v>2.6</v>
       </c>
       <c r="T64">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U64">
         <v>1.89</v>
@@ -16684,16 +16684,16 @@
         <v>275</v>
       </c>
       <c r="F65">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G65">
         <v>2.64</v>
       </c>
       <c r="H65">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I65">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J65">
         <v>3.5</v>
@@ -16708,22 +16708,22 @@
         <v>1.06</v>
       </c>
       <c r="N65">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O65">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P65">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="Q65">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R65">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S65">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="T65">
         <v>1.6</v>
@@ -16732,118 +16732,118 @@
         <v>2.18</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W65">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X65">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y65">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="Z65">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA65">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB65">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="AC65">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD65">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="AE65">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF65">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG65">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AH65">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI65">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ65">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK65">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL65">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM65">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN65">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO65">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP65">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ65">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR65">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS65">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT65">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU65">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AV65">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW65">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX65">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY65">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ65">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA65">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB65">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC65">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD65">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE65">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF65">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG65">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH65">
         <v>970</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-14.xlsx
@@ -844,7 +844,7 @@
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>2026-09-13 04:49:35</t>
+    <t>2026-09-13 07:13:58</t>
   </si>
 </sst>
 </file>
@@ -1438,148 +1438,148 @@
         <v>212</v>
       </c>
       <c r="F2">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="G2">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="H2">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="I2">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="J2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="Q2">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R2">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="S2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T2">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V2">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="W2">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB2">
         <v>36</v>
       </c>
       <c r="AC2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE2">
         <v>16.5</v>
       </c>
       <c r="AF2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
         <v>26</v>
       </c>
       <c r="AJ2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>70</v>
       </c>
       <c r="AN2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AQ2">
         <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS2">
         <v>12.5</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX2">
         <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB2">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
         <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>1.01</v>
@@ -1597,7 +1597,7 @@
         <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1680,7 +1680,7 @@
         <v>213</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G3">
         <v>2.42</v>
@@ -1695,13 +1695,13 @@
         <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.44</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
         <v>3.6</v>
@@ -1728,10 +1728,10 @@
         <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X3">
         <v>13</v>
@@ -1740,7 +1740,7 @@
         <v>16</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA3">
         <v>70</v>
@@ -1764,7 +1764,7 @@
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>70</v>
@@ -1842,64 +1842,64 @@
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>276</v>
@@ -1925,13 +1925,13 @@
         <v>2.74</v>
       </c>
       <c r="G4">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J4">
         <v>2.9</v>
@@ -1940,19 +1940,19 @@
         <v>2.98</v>
       </c>
       <c r="L4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M4">
         <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1970,7 +1970,7 @@
         <v>1.69</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
         <v>1.54</v>
@@ -2000,7 +2000,7 @@
         <v>60</v>
       </c>
       <c r="AF4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
@@ -2009,22 +2009,22 @@
         <v>32</v>
       </c>
       <c r="AI4">
-        <v>700</v>
+        <v>640</v>
       </c>
       <c r="AJ4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK4">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AL4">
-        <v>700</v>
+        <v>640</v>
       </c>
       <c r="AM4">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AN4">
-        <v>370</v>
+        <v>470</v>
       </c>
       <c r="AO4">
         <v>85</v>
@@ -2051,7 +2051,7 @@
         <v>14</v>
       </c>
       <c r="AW4">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AX4">
         <v>14</v>
@@ -2063,7 +2063,7 @@
         <v>23</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BB4">
         <v>40</v>
@@ -2075,7 +2075,7 @@
         <v>38</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="BF4">
         <v>29</v>
@@ -2090,19 +2090,19 @@
         <v>2.32</v>
       </c>
       <c r="BJ4">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
         <v>10</v>
       </c>
       <c r="BL4">
-        <v>890</v>
+        <v>810</v>
       </c>
       <c r="BM4">
         <v>22</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
         <v>4.9</v>
@@ -2111,7 +2111,7 @@
         <v>32</v>
       </c>
       <c r="BQ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR4">
         <v>65</v>
@@ -2123,13 +2123,13 @@
         <v>7</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
         <v>40</v>
       </c>
       <c r="BW4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BX4">
         <v>75</v>
@@ -2138,7 +2138,7 @@
         <v>46</v>
       </c>
       <c r="BZ4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="CA4">
         <v>48</v>
@@ -2167,16 +2167,16 @@
         <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
         <v>3.75</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
         <v>4.1</v>
@@ -2188,25 +2188,25 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S5">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U5">
         <v>2.42</v>
@@ -2230,7 +2230,7 @@
         <v>85</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
         <v>9</v>
@@ -2251,10 +2251,10 @@
         <v>16.5</v>
       </c>
       <c r="AI5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK5">
         <v>21</v>
@@ -2266,28 +2266,28 @@
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>42</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
         <v>15</v>
       </c>
       <c r="AR5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS5">
+        <v>9.4</v>
+      </c>
+      <c r="AT5">
         <v>10</v>
       </c>
-      <c r="AT5">
-        <v>10.5</v>
-      </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV5">
         <v>13.5</v>
@@ -2317,7 +2317,7 @@
         <v>23</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF5">
         <v>10.5</v>
@@ -2329,7 +2329,7 @@
         <v>3.9</v>
       </c>
       <c r="BI5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
         <v>11</v>
@@ -2338,16 +2338,16 @@
         <v>8</v>
       </c>
       <c r="BL5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM5">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="BN5">
         <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP5">
         <v>17</v>
@@ -2362,7 +2362,7 @@
         <v>17.5</v>
       </c>
       <c r="BT5">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
         <v>6.4</v>
@@ -2380,10 +2380,10 @@
         <v>24</v>
       </c>
       <c r="BZ5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB5" t="s">
         <v>276</v>
@@ -2415,10 +2415,10 @@
         <v>2.48</v>
       </c>
       <c r="I6">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
         <v>4.1</v>
@@ -2430,13 +2430,13 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O6">
         <v>1.17</v>
       </c>
       <c r="P6">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q6">
         <v>1.53</v>
@@ -2445,16 +2445,16 @@
         <v>1.72</v>
       </c>
       <c r="S6">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W6">
         <v>1.53</v>
@@ -2493,7 +2493,7 @@
         <v>14</v>
       </c>
       <c r="AI6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ6">
         <v>44</v>
@@ -2544,7 +2544,7 @@
         <v>12</v>
       </c>
       <c r="AZ6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA6">
         <v>24</v>
@@ -2559,7 +2559,7 @@
         <v>26</v>
       </c>
       <c r="BE6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF6">
         <v>13</v>
@@ -2568,64 +2568,64 @@
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI6">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK6">
+        <v>7.2</v>
+      </c>
+      <c r="BL6">
+        <v>80</v>
+      </c>
+      <c r="BM6">
+        <v>46</v>
+      </c>
+      <c r="BN6">
+        <v>6.4</v>
+      </c>
+      <c r="BO6">
+        <v>5.9</v>
+      </c>
+      <c r="BP6">
+        <v>23</v>
+      </c>
+      <c r="BQ6">
+        <v>15.5</v>
+      </c>
+      <c r="BR6">
+        <v>29</v>
+      </c>
+      <c r="BS6">
+        <v>17</v>
+      </c>
+      <c r="BT6">
         <v>6</v>
       </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.01</v>
-      </c>
-      <c r="BN6">
-        <v>8.4</v>
-      </c>
-      <c r="BO6">
-        <v>5</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>11</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.01</v>
-      </c>
-      <c r="BT6">
-        <v>7.6</v>
-      </c>
       <c r="BU6">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW6">
+        <v>14</v>
+      </c>
+      <c r="BX6">
+        <v>27</v>
+      </c>
+      <c r="BY6">
+        <v>16</v>
+      </c>
+      <c r="BZ6">
+        <v>17</v>
+      </c>
+      <c r="CA6">
         <v>10</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.01</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>276</v>
@@ -2648,10 +2648,10 @@
         <v>217</v>
       </c>
       <c r="F7">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H7">
         <v>6.4</v>
@@ -2663,7 +2663,7 @@
         <v>4.8</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
         <v>1.32</v>
@@ -2684,10 +2684,10 @@
         <v>1.68</v>
       </c>
       <c r="R7">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S7">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T7">
         <v>1.82</v>
@@ -2699,7 +2699,7 @@
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X7">
         <v>23</v>
@@ -2723,7 +2723,7 @@
         <v>24</v>
       </c>
       <c r="AE7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF7">
         <v>10.5</v>
@@ -2759,7 +2759,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ7">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="AR7">
         <v>10</v>
@@ -2780,13 +2780,13 @@
         <v>10</v>
       </c>
       <c r="AX7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7">
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA7">
         <v>10</v>
@@ -2899,7 +2899,7 @@
         <v>1.89</v>
       </c>
       <c r="I8">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J8">
         <v>3.55</v>
@@ -2914,31 +2914,31 @@
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
         <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
         <v>1.32</v>
       </c>
       <c r="S8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T8">
         <v>1.9</v>
       </c>
       <c r="U8">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W8">
         <v>1.25</v>
@@ -2947,7 +2947,7 @@
         <v>13</v>
       </c>
       <c r="Y8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z8">
         <v>11.5</v>
@@ -2977,7 +2977,7 @@
         <v>24</v>
       </c>
       <c r="AI8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ8">
         <v>140</v>
@@ -2986,22 +2986,22 @@
         <v>80</v>
       </c>
       <c r="AL8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM8">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP8">
         <v>11</v>
       </c>
       <c r="AQ8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR8">
         <v>9.800000000000001</v>
@@ -3022,7 +3022,7 @@
         <v>16.5</v>
       </c>
       <c r="AX8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY8">
         <v>16.5</v>
@@ -3031,82 +3031,82 @@
         <v>18</v>
       </c>
       <c r="BA8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG8">
         <v>13</v>
       </c>
       <c r="BH8">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
         <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
         <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
         <v>1.01</v>
@@ -3135,19 +3135,19 @@
         <v>1.38</v>
       </c>
       <c r="G9">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="K9">
-        <v>890</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3156,10 +3156,10 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
         <v>2.22</v>
@@ -3168,7 +3168,7 @@
         <v>1.53</v>
       </c>
       <c r="R9">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
         <v>2.48</v>
@@ -3180,10 +3180,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W9">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3288,7 +3288,7 @@
         <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
         <v>1.01</v>
@@ -3315,7 +3315,7 @@
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
@@ -3374,22 +3374,22 @@
         <v>220</v>
       </c>
       <c r="F10">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G10">
         <v>3.4</v>
       </c>
       <c r="H10">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J10">
         <v>2.4</v>
       </c>
       <c r="K10">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3398,13 +3398,13 @@
         <v>1.18</v>
       </c>
       <c r="N10">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P10">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Q10">
         <v>3.2</v>
@@ -3422,7 +3422,7 @@
         <v>1.6</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
         <v>1.42</v>
@@ -3646,16 +3646,16 @@
         <v>1.16</v>
       </c>
       <c r="P11">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R11">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S11">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3891,19 +3891,19 @@
         <v>1.92</v>
       </c>
       <c r="Q12">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R12">
         <v>1.36</v>
       </c>
       <c r="S12">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
         <v>1.77</v>
       </c>
       <c r="U12">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="V12">
         <v>1.19</v>
@@ -3912,10 +3912,10 @@
         <v>2.28</v>
       </c>
       <c r="X12">
+        <v>25</v>
+      </c>
+      <c r="Y12">
         <v>30</v>
-      </c>
-      <c r="Y12">
-        <v>75</v>
       </c>
       <c r="Z12">
         <v>120</v>
@@ -3924,37 +3924,37 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC12">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE12">
-        <v>820</v>
+        <v>730</v>
       </c>
       <c r="AF12">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG12">
         <v>16</v>
       </c>
       <c r="AH12">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AI12">
         <v>920</v>
       </c>
       <c r="AJ12">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AK12">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AL12">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM12">
         <v>1000</v>
@@ -3975,13 +3975,13 @@
         <v>8</v>
       </c>
       <c r="AS12">
-        <v>2.48</v>
+        <v>17</v>
       </c>
       <c r="AT12">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV12">
         <v>14.5</v>
@@ -4008,16 +4008,16 @@
         <v>11.5</v>
       </c>
       <c r="BD12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BF12">
         <v>7.2</v>
       </c>
       <c r="BG12">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="BH12">
         <v>970</v>
@@ -4044,7 +4044,7 @@
         <v>1.75</v>
       </c>
       <c r="BP12">
-        <v>940</v>
+        <v>850</v>
       </c>
       <c r="BQ12">
         <v>2.48</v>
@@ -4130,7 +4130,7 @@
         <v>1.26</v>
       </c>
       <c r="P13">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q13">
         <v>1.79</v>
@@ -4354,7 +4354,7 @@
         <v>1000</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K14">
         <v>900</v>
@@ -4363,7 +4363,7 @@
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
         <v>2.92</v>
@@ -4390,7 +4390,7 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
         <v>2.6</v>
@@ -4498,7 +4498,7 @@
         <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
         <v>1.01</v>
@@ -4525,7 +4525,7 @@
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
         <v>1000</v>
@@ -4620,7 +4620,7 @@
         <v>1.98</v>
       </c>
       <c r="R15">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S15">
         <v>3.5</v>
@@ -4701,7 +4701,7 @@
         <v>14</v>
       </c>
       <c r="AS15">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
         <v>8</v>
@@ -4713,7 +4713,7 @@
         <v>9.6</v>
       </c>
       <c r="AW15">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
         <v>13</v>
@@ -4725,25 +4725,25 @@
         <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
         <v>25</v>
       </c>
       <c r="BC15">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>19.5</v>
       </c>
       <c r="BG15">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4856,7 +4856,7 @@
         <v>1.02</v>
       </c>
       <c r="P16">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q16">
         <v>2.28</v>
@@ -5068,79 +5068,79 @@
         <v>227</v>
       </c>
       <c r="F17">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G17">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="I17">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J17">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.04</v>
+      </c>
+      <c r="N17">
+        <v>3.2</v>
+      </c>
+      <c r="O17">
+        <v>1.34</v>
+      </c>
+      <c r="P17">
+        <v>1.78</v>
+      </c>
+      <c r="Q17">
+        <v>2</v>
+      </c>
+      <c r="R17">
+        <v>1.28</v>
+      </c>
+      <c r="S17">
+        <v>3.35</v>
+      </c>
+      <c r="T17">
+        <v>1.78</v>
+      </c>
+      <c r="U17">
+        <v>1.93</v>
+      </c>
+      <c r="V17">
+        <v>1.71</v>
+      </c>
+      <c r="W17">
         <v>1.33</v>
       </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>3.35</v>
-      </c>
-      <c r="O17">
-        <v>1.33</v>
-      </c>
-      <c r="P17">
-        <v>1.7</v>
-      </c>
-      <c r="Q17">
-        <v>1.86</v>
-      </c>
-      <c r="R17">
-        <v>1.19</v>
-      </c>
-      <c r="S17">
-        <v>2.58</v>
-      </c>
-      <c r="T17">
-        <v>1.01</v>
-      </c>
-      <c r="U17">
-        <v>1.01</v>
-      </c>
-      <c r="V17">
-        <v>1.7</v>
-      </c>
-      <c r="W17">
-        <v>1.29</v>
-      </c>
       <c r="X17">
         <v>1000</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA17">
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE17">
         <v>1000</v>
@@ -5176,25 +5176,25 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS17">
         <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW17">
         <v>1.01</v>
@@ -5203,7 +5203,7 @@
         <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
         <v>1.01</v>
@@ -5227,7 +5227,7 @@
         <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>3.75</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M18">
         <v>1.01</v>
@@ -5340,10 +5340,10 @@
         <v>1.01</v>
       </c>
       <c r="P18">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R18">
         <v>1.23</v>
@@ -5555,16 +5555,16 @@
         <v>1.21</v>
       </c>
       <c r="G19">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="H19">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I19">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="K19">
         <v>110</v>
@@ -5576,7 +5576,7 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O19">
         <v>1.23</v>
@@ -5585,10 +5585,10 @@
         <v>2.12</v>
       </c>
       <c r="Q19">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="R19">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S19">
         <v>2.66</v>
@@ -5603,7 +5603,7 @@
         <v>1.01</v>
       </c>
       <c r="W19">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5797,7 +5797,7 @@
         <v>1.85</v>
       </c>
       <c r="G20">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>4.6</v>
@@ -5821,13 +5821,13 @@
         <v>3.1</v>
       </c>
       <c r="O20">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P20">
         <v>1.72</v>
       </c>
       <c r="Q20">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R20">
         <v>1.27</v>
@@ -5839,7 +5839,7 @@
         <v>1.95</v>
       </c>
       <c r="U20">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="V20">
         <v>1.23</v>
@@ -5860,7 +5860,7 @@
         <v>150</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20">
         <v>9.6</v>
@@ -5875,7 +5875,7 @@
         <v>13.5</v>
       </c>
       <c r="AG20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
         <v>26</v>
@@ -5908,10 +5908,10 @@
         <v>12.5</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT20">
         <v>6.6</v>
@@ -5923,7 +5923,7 @@
         <v>17</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX20">
         <v>9.4</v>
@@ -5935,25 +5935,25 @@
         <v>15.5</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB20">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BC20">
         <v>16.5</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6036,40 +6036,40 @@
         <v>231</v>
       </c>
       <c r="F21">
+        <v>4.2</v>
+      </c>
+      <c r="G21">
+        <v>6.4</v>
+      </c>
+      <c r="H21">
+        <v>1.62</v>
+      </c>
+      <c r="I21">
+        <v>1.82</v>
+      </c>
+      <c r="J21">
+        <v>3.4</v>
+      </c>
+      <c r="K21">
+        <v>6.8</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
         <v>4.3</v>
-      </c>
-      <c r="G21">
-        <v>6.8</v>
-      </c>
-      <c r="H21">
-        <v>1.6</v>
-      </c>
-      <c r="I21">
-        <v>1.8</v>
-      </c>
-      <c r="J21">
-        <v>4.2</v>
-      </c>
-      <c r="K21">
-        <v>7</v>
-      </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>5</v>
       </c>
       <c r="O21">
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q21">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
         <v>1.6</v>
@@ -6084,10 +6084,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6278,7 +6278,7 @@
         <v>232</v>
       </c>
       <c r="F22">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>6.4</v>
@@ -6329,7 +6329,7 @@
         <v>2.6</v>
       </c>
       <c r="W22">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X22">
         <v>18</v>
@@ -6344,7 +6344,7 @@
         <v>15</v>
       </c>
       <c r="AB22">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC22">
         <v>10.5</v>
@@ -6362,7 +6362,7 @@
         <v>23</v>
       </c>
       <c r="AH22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI22">
         <v>36</v>
@@ -6392,7 +6392,7 @@
         <v>8.6</v>
       </c>
       <c r="AR22">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS22">
         <v>13.5</v>
@@ -6425,7 +6425,7 @@
         <v>44</v>
       </c>
       <c r="BC22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD22">
         <v>65</v>
@@ -6526,7 +6526,7 @@
         <v>1.26</v>
       </c>
       <c r="H23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="I23">
         <v>18.5</v>
@@ -6589,7 +6589,7 @@
         <v>8.4</v>
       </c>
       <c r="AC23">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD23">
         <v>65</v>
@@ -6634,7 +6634,7 @@
         <v>40</v>
       </c>
       <c r="AR23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS23">
         <v>100</v>
@@ -6649,7 +6649,7 @@
         <v>55</v>
       </c>
       <c r="AW23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AX23">
         <v>6.6</v>
@@ -6685,7 +6685,7 @@
         <v>4</v>
       </c>
       <c r="BI23">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ23">
         <v>16</v>
@@ -6703,7 +6703,7 @@
         <v>3.5</v>
       </c>
       <c r="BO23">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP23">
         <v>6.8</v>
@@ -6718,7 +6718,7 @@
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BU23">
         <v>13.5</v>
@@ -6765,7 +6765,7 @@
         <v>6.4</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="H24">
         <v>1.56</v>
@@ -6783,7 +6783,7 @@
         <v>1.35</v>
       </c>
       <c r="M24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
         <v>4.3</v>
@@ -6792,22 +6792,22 @@
         <v>1.25</v>
       </c>
       <c r="P24">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q24">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R24">
         <v>1.45</v>
       </c>
       <c r="S24">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="T24">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U24">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V24">
         <v>2.64</v>
@@ -6822,10 +6822,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB24">
         <v>24</v>
@@ -6837,13 +6837,13 @@
         <v>10.5</v>
       </c>
       <c r="AE24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF24">
         <v>65</v>
       </c>
       <c r="AG24">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AH24">
         <v>22</v>
@@ -6867,7 +6867,7 @@
         <v>120</v>
       </c>
       <c r="AO24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP24">
         <v>16.5</v>
@@ -6879,7 +6879,7 @@
         <v>9</v>
       </c>
       <c r="AS24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT24">
         <v>19</v>
@@ -6906,19 +6906,19 @@
         <v>14</v>
       </c>
       <c r="BB24">
+        <v>10.5</v>
+      </c>
+      <c r="BC24">
         <v>10</v>
       </c>
-      <c r="BC24">
-        <v>9.6</v>
-      </c>
       <c r="BD24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE24">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF24">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG24">
         <v>7</v>
@@ -6966,7 +6966,7 @@
         <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW24">
         <v>1.01</v>
@@ -7007,7 +7007,7 @@
         <v>1.5</v>
       </c>
       <c r="G25">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H25">
         <v>7.2</v>
@@ -7028,22 +7028,22 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
         <v>1.26</v>
       </c>
       <c r="P25">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q25">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="R25">
         <v>1.46</v>
       </c>
       <c r="S25">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T25">
         <v>1.94</v>
@@ -7055,7 +7055,7 @@
         <v>1.13</v>
       </c>
       <c r="W25">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="X25">
         <v>22</v>
@@ -7196,7 +7196,7 @@
         <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS25">
         <v>1.01</v>
@@ -7261,13 +7261,13 @@
         <v>3.5</v>
       </c>
       <c r="K26">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L26">
         <v>1.24</v>
       </c>
       <c r="M26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N26">
         <v>4.1</v>
@@ -7279,7 +7279,7 @@
         <v>2.06</v>
       </c>
       <c r="Q26">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R26">
         <v>1.42</v>
@@ -7491,13 +7491,13 @@
         <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H27">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J27">
         <v>3.55</v>
@@ -7539,7 +7539,7 @@
         <v>1.42</v>
       </c>
       <c r="W27">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X27">
         <v>19</v>
@@ -7733,25 +7733,25 @@
         <v>1.45</v>
       </c>
       <c r="G28">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H28">
         <v>7.6</v>
       </c>
       <c r="I28">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K28">
         <v>5.4</v>
       </c>
       <c r="L28">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M28">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N28">
         <v>5.5</v>
@@ -7760,22 +7760,22 @@
         <v>1.2</v>
       </c>
       <c r="P28">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q28">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R28">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S28">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T28">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U28">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
         <v>1.13</v>
@@ -7787,16 +7787,16 @@
         <v>27</v>
       </c>
       <c r="Y28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z28">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA28">
         <v>260</v>
       </c>
       <c r="AB28">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC28">
         <v>12</v>
@@ -7808,13 +7808,13 @@
         <v>120</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG28">
         <v>10.5</v>
       </c>
       <c r="AH28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI28">
         <v>100</v>
@@ -7832,19 +7832,19 @@
         <v>120</v>
       </c>
       <c r="AN28">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO28">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP28">
         <v>21</v>
       </c>
       <c r="AQ28">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS28">
         <v>13</v>
@@ -7856,19 +7856,19 @@
         <v>10.5</v>
       </c>
       <c r="AV28">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW28">
         <v>12.5</v>
       </c>
       <c r="AX28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY28">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BA28">
         <v>12</v>
@@ -7880,7 +7880,7 @@
         <v>12.5</v>
       </c>
       <c r="BD28">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE28">
         <v>12.5</v>
@@ -7972,10 +7972,10 @@
         <v>239</v>
       </c>
       <c r="F29">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G29">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H29">
         <v>5.5</v>
@@ -7984,7 +7984,7 @@
         <v>6</v>
       </c>
       <c r="J29">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K29">
         <v>4.8</v>
@@ -8086,7 +8086,7 @@
         <v>20</v>
       </c>
       <c r="AR29">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS29">
         <v>9.199999999999999</v>
@@ -8125,7 +8125,7 @@
         <v>12</v>
       </c>
       <c r="BE29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF29">
         <v>6.4</v>
@@ -8456,7 +8456,7 @@
         <v>241</v>
       </c>
       <c r="F31">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G31">
         <v>4.1</v>
@@ -8468,43 +8468,43 @@
         <v>2.46</v>
       </c>
       <c r="J31">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L31">
         <v>1.37</v>
       </c>
       <c r="M31">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N31">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="O31">
         <v>1.39</v>
       </c>
       <c r="P31">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="Q31">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R31">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="S31">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="T31">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U31">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W31">
         <v>1.32</v>
@@ -8564,25 +8564,25 @@
         <v>29</v>
       </c>
       <c r="AP31">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ31">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="AR31">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AS31">
         <v>5</v>
       </c>
       <c r="AT31">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="AV31">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AW31">
         <v>4.9</v>
@@ -8591,16 +8591,16 @@
         <v>4.9</v>
       </c>
       <c r="AY31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AZ31">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BA31">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB31">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC31">
         <v>5.3</v>
@@ -8609,13 +8609,13 @@
         <v>5.4</v>
       </c>
       <c r="BE31">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF31">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG31">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8698,13 +8698,13 @@
         <v>242</v>
       </c>
       <c r="F32">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G32">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H32">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="I32">
         <v>3</v>
@@ -8713,7 +8713,7 @@
         <v>3.7</v>
       </c>
       <c r="K32">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8722,67 +8722,67 @@
         <v>1.04</v>
       </c>
       <c r="N32">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O32">
         <v>1.2</v>
       </c>
       <c r="P32">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q32">
         <v>1.63</v>
       </c>
       <c r="R32">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S32">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T32">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U32">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="V32">
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y32">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z32">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA32">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB32">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AC32">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD32">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE32">
         <v>38</v>
       </c>
       <c r="AF32">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AG32">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH32">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AI32">
         <v>48</v>
@@ -8794,88 +8794,88 @@
         <v>34</v>
       </c>
       <c r="AL32">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AM32">
         <v>90</v>
       </c>
       <c r="AN32">
+        <v>16</v>
+      </c>
+      <c r="AO32">
         <v>19</v>
       </c>
-      <c r="AO32">
+      <c r="AP32">
+        <v>16</v>
+      </c>
+      <c r="AQ32">
+        <v>13</v>
+      </c>
+      <c r="AR32">
+        <v>18</v>
+      </c>
+      <c r="AS32">
         <v>25</v>
       </c>
-      <c r="AP32">
-        <v>2.94</v>
-      </c>
-      <c r="AQ32">
-        <v>2.56</v>
-      </c>
-      <c r="AR32">
-        <v>15</v>
-      </c>
-      <c r="AS32">
-        <v>2.8</v>
-      </c>
       <c r="AT32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU32">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV32">
-        <v>2.48</v>
+        <v>11</v>
       </c>
       <c r="AW32">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX32">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY32">
-        <v>2.46</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32">
+        <v>13</v>
+      </c>
+      <c r="BA32">
+        <v>21</v>
+      </c>
+      <c r="BB32">
+        <v>22</v>
+      </c>
+      <c r="BC32">
+        <v>20</v>
+      </c>
+      <c r="BD32">
+        <v>7</v>
+      </c>
+      <c r="BE32">
+        <v>7.8</v>
+      </c>
+      <c r="BF32">
+        <v>13</v>
+      </c>
+      <c r="BG32">
+        <v>15.5</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.01</v>
+      </c>
+      <c r="BJ32">
         <v>12</v>
       </c>
-      <c r="BA32">
-        <v>2.78</v>
-      </c>
-      <c r="BB32">
-        <v>2.78</v>
-      </c>
-      <c r="BC32">
-        <v>15.5</v>
-      </c>
-      <c r="BD32">
-        <v>2.78</v>
-      </c>
-      <c r="BE32">
-        <v>2.86</v>
-      </c>
-      <c r="BF32">
-        <v>11</v>
-      </c>
-      <c r="BG32">
-        <v>13</v>
-      </c>
-      <c r="BH32">
-        <v>1000</v>
-      </c>
-      <c r="BI32">
-        <v>1.01</v>
-      </c>
-      <c r="BJ32">
-        <v>11.5</v>
-      </c>
       <c r="BK32">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
         <v>100</v>
       </c>
       <c r="BM32">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
         <v>8</v>
@@ -8887,16 +8887,16 @@
         <v>24</v>
       </c>
       <c r="BQ32">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
         <v>36</v>
       </c>
       <c r="BS32">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU32">
         <v>4.2</v>
@@ -8905,19 +8905,19 @@
         <v>28</v>
       </c>
       <c r="BW32">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
         <v>38</v>
       </c>
       <c r="BY32">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
         <v>25</v>
       </c>
       <c r="CA32">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
         <v>276</v>
@@ -8964,16 +8964,16 @@
         <v>1.06</v>
       </c>
       <c r="N33">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P33">
         <v>1.7</v>
       </c>
       <c r="Q33">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R33">
         <v>1.25</v>
@@ -9111,7 +9111,7 @@
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL33">
         <v>1000</v>
@@ -9191,7 +9191,7 @@
         <v>2.82</v>
       </c>
       <c r="I34">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J34">
         <v>3.65</v>
@@ -9200,7 +9200,7 @@
         <v>4.1</v>
       </c>
       <c r="L34">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M34">
         <v>1.05</v>
@@ -9209,7 +9209,7 @@
         <v>4.7</v>
       </c>
       <c r="O34">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P34">
         <v>2.24</v>
@@ -9299,7 +9299,7 @@
         <v>18.5</v>
       </c>
       <c r="AS34">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT34">
         <v>11.5</v>
@@ -9311,7 +9311,7 @@
         <v>11.5</v>
       </c>
       <c r="AW34">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX34">
         <v>15.5</v>
@@ -9335,7 +9335,7 @@
         <v>21</v>
       </c>
       <c r="BE34">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF34">
         <v>13.5</v>
@@ -9359,7 +9359,7 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN34">
         <v>7.6</v>
@@ -9371,13 +9371,13 @@
         <v>24</v>
       </c>
       <c r="BQ34">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR34">
         <v>36</v>
       </c>
       <c r="BS34">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT34">
         <v>8.199999999999999</v>
@@ -9389,19 +9389,19 @@
         <v>29</v>
       </c>
       <c r="BW34">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BX34">
         <v>40</v>
       </c>
       <c r="BY34">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34">
         <v>28</v>
       </c>
       <c r="CA34">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="s">
         <v>276</v>
@@ -9433,7 +9433,7 @@
         <v>15</v>
       </c>
       <c r="I35">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J35">
         <v>9.199999999999999</v>
@@ -9448,16 +9448,16 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="O35">
         <v>1.09</v>
       </c>
       <c r="P35">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R35">
         <v>2.22</v>
@@ -9469,19 +9469,19 @@
         <v>1.85</v>
       </c>
       <c r="U35">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V35">
         <v>1.06</v>
       </c>
       <c r="W35">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X35">
         <v>1000</v>
       </c>
       <c r="Y35">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="Z35">
         <v>1000</v>
@@ -9496,7 +9496,7 @@
         <v>26</v>
       </c>
       <c r="AD35">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AE35">
         <v>1000</v>
@@ -9505,10 +9505,10 @@
         <v>11.5</v>
       </c>
       <c r="AG35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH35">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AI35">
         <v>1000</v>
@@ -9517,7 +9517,7 @@
         <v>11</v>
       </c>
       <c r="AK35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL35">
         <v>34</v>
@@ -9532,25 +9532,25 @@
         <v>1000</v>
       </c>
       <c r="AP35">
+        <v>44</v>
+      </c>
+      <c r="AQ35">
         <v>40</v>
-      </c>
-      <c r="AQ35">
-        <v>42</v>
       </c>
       <c r="AR35">
         <v>44</v>
       </c>
       <c r="AS35">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AT35">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU35">
         <v>20</v>
       </c>
       <c r="AV35">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AW35">
         <v>46</v>
@@ -9562,7 +9562,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ35">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA35">
         <v>65</v>
@@ -9574,10 +9574,10 @@
         <v>11.5</v>
       </c>
       <c r="BD35">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BE35">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF35">
         <v>2.6</v>
@@ -9589,7 +9589,7 @@
         <v>1000</v>
       </c>
       <c r="BI35">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35">
         <v>1000</v>
@@ -9607,13 +9607,13 @@
         <v>4.7</v>
       </c>
       <c r="BO35">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP35">
         <v>8.6</v>
       </c>
       <c r="BQ35">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR35">
         <v>1000</v>
@@ -9669,7 +9669,7 @@
         <v>3.7</v>
       </c>
       <c r="G36">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H36">
         <v>1.86</v>
@@ -9690,7 +9690,7 @@
         <v>1.02</v>
       </c>
       <c r="N36">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O36">
         <v>1.23</v>
@@ -9711,13 +9711,13 @@
         <v>1.59</v>
       </c>
       <c r="U36">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V36">
         <v>1.9</v>
       </c>
       <c r="W36">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9917,13 +9917,13 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J37">
         <v>3</v>
       </c>
       <c r="K37">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L37">
         <v>1.51</v>
@@ -9938,7 +9938,7 @@
         <v>1.5</v>
       </c>
       <c r="P37">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q37">
         <v>2.46</v>
@@ -9977,10 +9977,10 @@
         <v>9</v>
       </c>
       <c r="AC37">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD37">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE37">
         <v>55</v>
@@ -10049,10 +10049,10 @@
         <v>17.5</v>
       </c>
       <c r="BA37">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB37">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC37">
         <v>8</v>
@@ -10061,73 +10061,73 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE37">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF37">
         <v>32</v>
       </c>
       <c r="BG37">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH37">
         <v>970</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK37">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO37">
         <v>3.9</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS37">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU37">
-        <v>1.5</v>
+        <v>2.76</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW37">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY37">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA37">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="CB37" t="s">
         <v>276</v>
@@ -10162,7 +10162,7 @@
         <v>4.5</v>
       </c>
       <c r="J38">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K38">
         <v>4.3</v>
@@ -10201,115 +10201,115 @@
         <v>1.29</v>
       </c>
       <c r="W38">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X38">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y38">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="Z38">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AA38">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB38">
         <v>16</v>
       </c>
       <c r="AC38">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD38">
         <v>23</v>
       </c>
       <c r="AE38">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AF38">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG38">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH38">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AI38">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ38">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AK38">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AL38">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AM38">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN38">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AO38">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP38">
-        <v>16.5</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR38">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AS38">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="AT38">
         <v>10</v>
       </c>
       <c r="AU38">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AV38">
         <v>13.5</v>
       </c>
       <c r="AW38">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AX38">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY38">
         <v>8.4</v>
       </c>
       <c r="AZ38">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA38">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BB38">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC38">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD38">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="BE38">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="BF38">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG38">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="BH38">
         <v>970</v>
@@ -10670,7 +10670,7 @@
         <v>1.94</v>
       </c>
       <c r="R40">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S40">
         <v>3.35</v>
@@ -10894,7 +10894,7 @@
         <v>5.5</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M41">
         <v>1.01</v>
@@ -11133,10 +11133,10 @@
         <v>7</v>
       </c>
       <c r="K42">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M42">
         <v>1.04</v>
@@ -11154,13 +11154,13 @@
         <v>1.52</v>
       </c>
       <c r="R42">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S42">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T42">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U42">
         <v>1.62</v>
@@ -11360,58 +11360,58 @@
         <v>253</v>
       </c>
       <c r="F43">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G43">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="H43">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J43">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K43">
+        <v>4.4</v>
+      </c>
+      <c r="L43">
+        <v>1.01</v>
+      </c>
+      <c r="M43">
+        <v>1.04</v>
+      </c>
+      <c r="N43">
         <v>4.5</v>
       </c>
-      <c r="L43">
-        <v>1.01</v>
-      </c>
-      <c r="M43">
-        <v>1.05</v>
-      </c>
-      <c r="N43">
-        <v>4</v>
-      </c>
       <c r="O43">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="P43">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q43">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="R43">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S43">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T43">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U43">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W43">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11441,7 +11441,7 @@
         <v>1000</v>
       </c>
       <c r="AG43">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH43">
         <v>1000</v>
@@ -11462,7 +11462,7 @@
         <v>1000</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO43">
         <v>1000</v>
@@ -11516,7 +11516,7 @@
         <v>1.01</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG43">
         <v>1.01</v>
@@ -11602,13 +11602,13 @@
         <v>254</v>
       </c>
       <c r="F44">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G44">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H44">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I44">
         <v>2.82</v>
@@ -11617,7 +11617,7 @@
         <v>3.4</v>
       </c>
       <c r="K44">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L44">
         <v>1.42</v>
@@ -11629,13 +11629,13 @@
         <v>3.45</v>
       </c>
       <c r="O44">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P44">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q44">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R44">
         <v>1.33</v>
@@ -11644,16 +11644,16 @@
         <v>3.15</v>
       </c>
       <c r="T44">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U44">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V44">
         <v>1.55</v>
       </c>
       <c r="W44">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X44">
         <v>970</v>
@@ -11674,7 +11674,7 @@
         <v>10</v>
       </c>
       <c r="AD44">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE44">
         <v>1000</v>
@@ -11809,7 +11809,7 @@
         <v>1000</v>
       </c>
       <c r="BW44">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX44">
         <v>1000</v>
@@ -11877,7 +11877,7 @@
         <v>2.74</v>
       </c>
       <c r="Q45">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R45">
         <v>1.74</v>
@@ -11889,7 +11889,7 @@
         <v>1.39</v>
       </c>
       <c r="U45">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="V45">
         <v>1.44</v>
@@ -12137,7 +12137,7 @@
         <v>1.58</v>
       </c>
       <c r="W46">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12328,13 +12328,13 @@
         <v>257</v>
       </c>
       <c r="F47">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G47">
         <v>1.51</v>
       </c>
       <c r="H47">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I47">
         <v>11</v>
@@ -12343,10 +12343,10 @@
         <v>4.7</v>
       </c>
       <c r="K47">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M47">
         <v>1.04</v>
@@ -12364,7 +12364,7 @@
         <v>1.66</v>
       </c>
       <c r="R47">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S47">
         <v>2.68</v>
@@ -12430,7 +12430,7 @@
         <v>160</v>
       </c>
       <c r="AN47">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO47">
         <v>190</v>
@@ -12490,7 +12490,7 @@
         <v>7.2</v>
       </c>
       <c r="BH47">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI47">
         <v>3.15</v>
@@ -12517,7 +12517,7 @@
         <v>1000</v>
       </c>
       <c r="BQ47">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR47">
         <v>1000</v>
@@ -12573,25 +12573,25 @@
         <v>1.28</v>
       </c>
       <c r="G48">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H48">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I48">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J48">
         <v>6.4</v>
       </c>
       <c r="K48">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L48">
         <v>1.29</v>
       </c>
       <c r="M48">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N48">
         <v>6</v>
@@ -12603,25 +12603,25 @@
         <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R48">
         <v>1.68</v>
       </c>
       <c r="S48">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T48">
         <v>2.12</v>
       </c>
       <c r="U48">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V48">
         <v>1.07</v>
       </c>
       <c r="W48">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X48">
         <v>27</v>
@@ -12669,7 +12669,7 @@
         <v>38</v>
       </c>
       <c r="AM48">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN48">
         <v>4.1</v>
@@ -12702,13 +12702,13 @@
         <v>48</v>
       </c>
       <c r="AX48">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY48">
         <v>10.5</v>
       </c>
       <c r="AZ48">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA48">
         <v>44</v>
@@ -12735,10 +12735,10 @@
         <v>970</v>
       </c>
       <c r="BI48">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ48">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BK48">
         <v>1.01</v>
@@ -12815,13 +12815,13 @@
         <v>2.72</v>
       </c>
       <c r="G49">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H49">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I49">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J49">
         <v>3.65</v>
@@ -12833,124 +12833,124 @@
         <v>1.31</v>
       </c>
       <c r="M49">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N49">
         <v>4</v>
       </c>
       <c r="O49">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P49">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q49">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R49">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S49">
         <v>2.8</v>
       </c>
       <c r="T49">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="U49">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V49">
         <v>1.58</v>
       </c>
       <c r="W49">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X49">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y49">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Z49">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AA49">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AB49">
+        <v>14</v>
+      </c>
+      <c r="AC49">
+        <v>8.6</v>
+      </c>
+      <c r="AD49">
+        <v>13</v>
+      </c>
+      <c r="AE49">
+        <v>28</v>
+      </c>
+      <c r="AF49">
+        <v>22</v>
+      </c>
+      <c r="AG49">
+        <v>13.5</v>
+      </c>
+      <c r="AH49">
         <v>17</v>
       </c>
-      <c r="AC49">
-        <v>10</v>
-      </c>
-      <c r="AD49">
-        <v>15.5</v>
-      </c>
-      <c r="AE49">
+      <c r="AI49">
         <v>38</v>
       </c>
-      <c r="AF49">
-        <v>26</v>
-      </c>
-      <c r="AG49">
-        <v>16</v>
-      </c>
-      <c r="AH49">
-        <v>20</v>
-      </c>
-      <c r="AI49">
+      <c r="AJ49">
         <v>46</v>
       </c>
-      <c r="AJ49">
-        <v>60</v>
-      </c>
       <c r="AK49">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AL49">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM49">
         <v>100</v>
       </c>
       <c r="AN49">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AO49">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AP49">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ49">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR49">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS49">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AT49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU49">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV49">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW49">
         <v>16.5</v>
       </c>
       <c r="AX49">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AY49">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ49">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA49">
         <v>1.01</v>
@@ -12959,19 +12959,19 @@
         <v>1.01</v>
       </c>
       <c r="BC49">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD49">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE49">
         <v>1.01</v>
       </c>
       <c r="BF49">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BG49">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BH49">
         <v>970</v>
@@ -12992,7 +12992,7 @@
         <v>1.01</v>
       </c>
       <c r="BN49">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="BO49">
         <v>1.01</v>
@@ -13010,7 +13010,7 @@
         <v>1.01</v>
       </c>
       <c r="BT49">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU49">
         <v>1.01</v>
@@ -13054,22 +13054,22 @@
         <v>260</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G50">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H50">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I50">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J50">
         <v>3.15</v>
       </c>
       <c r="K50">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L50">
         <v>1.33</v>
@@ -13081,13 +13081,13 @@
         <v>3.7</v>
       </c>
       <c r="O50">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P50">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q50">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R50">
         <v>1.34</v>
@@ -13102,7 +13102,7 @@
         <v>2.14</v>
       </c>
       <c r="V50">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W50">
         <v>1.35</v>
@@ -13123,7 +13123,7 @@
         <v>48</v>
       </c>
       <c r="AC50">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD50">
         <v>22</v>
@@ -13165,7 +13165,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ50">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR50">
         <v>1.01</v>
@@ -13177,7 +13177,7 @@
         <v>1.01</v>
       </c>
       <c r="AU50">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV50">
         <v>1.01</v>
@@ -13216,7 +13216,7 @@
         <v>1.01</v>
       </c>
       <c r="BH50">
-        <v>4</v>
+        <v>970</v>
       </c>
       <c r="BI50">
         <v>1.01</v>
@@ -13252,7 +13252,7 @@
         <v>1.01</v>
       </c>
       <c r="BT50">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="BU50">
         <v>1.01</v>
@@ -13296,7 +13296,7 @@
         <v>261</v>
       </c>
       <c r="F51">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G51">
         <v>2.58</v>
@@ -13305,13 +13305,13 @@
         <v>2.96</v>
       </c>
       <c r="I51">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J51">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K51">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L51">
         <v>1.37</v>
@@ -13344,7 +13344,7 @@
         <v>2.06</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
         <v>1.64</v>
@@ -13362,13 +13362,13 @@
         <v>1000</v>
       </c>
       <c r="AB51">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC51">
         <v>9</v>
       </c>
       <c r="AD51">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="AE51">
         <v>1000</v>
@@ -13377,7 +13377,7 @@
         <v>65</v>
       </c>
       <c r="AG51">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH51">
         <v>90</v>
@@ -13404,58 +13404,58 @@
         <v>1000</v>
       </c>
       <c r="AP51">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ51">
-        <v>8.6</v>
+        <v>1.68</v>
       </c>
       <c r="AR51">
-        <v>4.4</v>
+        <v>1.81</v>
       </c>
       <c r="AS51">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT51">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU51">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV51">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW51">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX51">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AY51">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AZ51">
-        <v>12.5</v>
+        <v>1.81</v>
       </c>
       <c r="BA51">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB51">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC51">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BD51">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE51">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="BF51">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="BG51">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="BH51">
         <v>970</v>
@@ -13538,19 +13538,19 @@
         <v>262</v>
       </c>
       <c r="F52">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G52">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H52">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I52">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J52">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K52">
         <v>4.6</v>
@@ -13562,7 +13562,7 @@
         <v>1.07</v>
       </c>
       <c r="N52">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O52">
         <v>1.32</v>
@@ -13586,7 +13586,7 @@
         <v>1.89</v>
       </c>
       <c r="V52">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W52">
         <v>2.06</v>
@@ -13595,7 +13595,7 @@
         <v>34</v>
       </c>
       <c r="Y52">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z52">
         <v>1000</v>
@@ -13676,7 +13676,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ52">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA52">
         <v>1.01</v>
@@ -13789,13 +13789,13 @@
         <v>2.12</v>
       </c>
       <c r="I53">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J53">
         <v>3.65</v>
       </c>
       <c r="K53">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L53">
         <v>1.28</v>
@@ -13807,10 +13807,10 @@
         <v>3.9</v>
       </c>
       <c r="O53">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P53">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="Q53">
         <v>1.78</v>
@@ -13828,7 +13828,7 @@
         <v>1.01</v>
       </c>
       <c r="V53">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W53">
         <v>1.37</v>
@@ -14025,7 +14025,7 @@
         <v>2.4</v>
       </c>
       <c r="G54">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H54">
         <v>3.15</v>
@@ -14055,7 +14055,7 @@
         <v>2.12</v>
       </c>
       <c r="Q54">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R54">
         <v>1.44</v>
@@ -14067,13 +14067,13 @@
         <v>1.69</v>
       </c>
       <c r="U54">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V54">
         <v>1.45</v>
       </c>
       <c r="W54">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X54">
         <v>16</v>
@@ -14091,10 +14091,10 @@
         <v>12</v>
       </c>
       <c r="AC54">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD54">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE54">
         <v>34</v>
@@ -14112,7 +14112,7 @@
         <v>40</v>
       </c>
       <c r="AJ54">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK54">
         <v>24</v>
@@ -14121,10 +14121,10 @@
         <v>32</v>
       </c>
       <c r="AM54">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN54">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO54">
         <v>28</v>
@@ -14217,7 +14217,7 @@
         <v>1000</v>
       </c>
       <c r="BS54">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT54">
         <v>970</v>
@@ -14264,16 +14264,16 @@
         <v>265</v>
       </c>
       <c r="F55">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G55">
         <v>1.98</v>
       </c>
       <c r="H55">
+        <v>3.9</v>
+      </c>
+      <c r="I55">
         <v>3.95</v>
-      </c>
-      <c r="I55">
-        <v>4</v>
       </c>
       <c r="J55">
         <v>4.1</v>
@@ -14300,7 +14300,7 @@
         <v>1.64</v>
       </c>
       <c r="R55">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S55">
         <v>2.56</v>
@@ -14506,19 +14506,19 @@
         <v>266</v>
       </c>
       <c r="F56">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G56">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H56">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I56">
         <v>3.4</v>
       </c>
       <c r="J56">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K56">
         <v>3.3</v>
@@ -14533,7 +14533,7 @@
         <v>2.76</v>
       </c>
       <c r="O56">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P56">
         <v>1.58</v>
@@ -14542,10 +14542,10 @@
         <v>2.24</v>
       </c>
       <c r="R56">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S56">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T56">
         <v>1.86</v>
@@ -14557,7 +14557,7 @@
         <v>1.42</v>
       </c>
       <c r="W56">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X56">
         <v>10.5</v>
@@ -14572,7 +14572,7 @@
         <v>70</v>
       </c>
       <c r="AB56">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC56">
         <v>7.4</v>
@@ -14596,7 +14596,7 @@
         <v>75</v>
       </c>
       <c r="AJ56">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK56">
         <v>34</v>
@@ -14623,7 +14623,7 @@
         <v>18.5</v>
       </c>
       <c r="AS56">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT56">
         <v>7.8</v>
@@ -14635,7 +14635,7 @@
         <v>12.5</v>
       </c>
       <c r="AW56">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX56">
         <v>14</v>
@@ -14647,25 +14647,25 @@
         <v>17</v>
       </c>
       <c r="BA56">
+        <v>10</v>
+      </c>
+      <c r="BB56">
+        <v>9</v>
+      </c>
+      <c r="BC56">
+        <v>8.6</v>
+      </c>
+      <c r="BD56">
         <v>9.800000000000001</v>
       </c>
-      <c r="BB56">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC56">
-        <v>8.4</v>
-      </c>
-      <c r="BD56">
-        <v>9.4</v>
-      </c>
       <c r="BE56">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF56">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG56">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH56">
         <v>3.2</v>
@@ -14748,10 +14748,10 @@
         <v>267</v>
       </c>
       <c r="F57">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G57">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H57">
         <v>8</v>
@@ -14772,28 +14772,28 @@
         <v>1.05</v>
       </c>
       <c r="N57">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O57">
         <v>1.25</v>
       </c>
       <c r="P57">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R57">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S57">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T57">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U57">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V57">
         <v>1.13</v>
@@ -14874,10 +14874,10 @@
         <v>9.6</v>
       </c>
       <c r="AV57">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW57">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX57">
         <v>7.8</v>
@@ -14898,10 +14898,10 @@
         <v>13</v>
       </c>
       <c r="BD57">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE57">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF57">
         <v>6.2</v>
@@ -15002,7 +15002,7 @@
         <v>4.1</v>
       </c>
       <c r="J58">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K58">
         <v>3.45</v>
@@ -15026,7 +15026,7 @@
         <v>2.86</v>
       </c>
       <c r="R58">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S58">
         <v>5.7</v>
@@ -15041,7 +15041,7 @@
         <v>1.34</v>
       </c>
       <c r="W58">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X58">
         <v>9.800000000000001</v>
@@ -15104,7 +15104,7 @@
         <v>6.4</v>
       </c>
       <c r="AR58">
-        <v>2.38</v>
+        <v>12.5</v>
       </c>
       <c r="AS58">
         <v>2.32</v>
@@ -15113,7 +15113,7 @@
         <v>5.3</v>
       </c>
       <c r="AU58">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV58">
         <v>11</v>
@@ -15134,10 +15134,10 @@
         <v>2.32</v>
       </c>
       <c r="BB58">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="BC58">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="BD58">
         <v>2.32</v>
@@ -15241,16 +15241,16 @@
         <v>2.74</v>
       </c>
       <c r="I59">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J59">
         <v>2.7</v>
       </c>
       <c r="K59">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="L59">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="M59">
         <v>1.14</v>
@@ -15262,136 +15262,136 @@
         <v>1.76</v>
       </c>
       <c r="P59">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q59">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R59">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S59">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T59">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U59">
+        <v>1.56</v>
+      </c>
+      <c r="V59">
         <v>1.52</v>
-      </c>
-      <c r="V59">
-        <v>1.51</v>
       </c>
       <c r="W59">
         <v>1.39</v>
       </c>
       <c r="X59">
+        <v>6.6</v>
+      </c>
+      <c r="Y59">
+        <v>7</v>
+      </c>
+      <c r="Z59">
+        <v>19</v>
+      </c>
+      <c r="AA59">
+        <v>990</v>
+      </c>
+      <c r="AB59">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y59">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z59">
-        <v>1000</v>
-      </c>
-      <c r="AA59">
-        <v>1000</v>
-      </c>
-      <c r="AB59">
-        <v>11.5</v>
-      </c>
       <c r="AC59">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AD59">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE59">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AF59">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG59">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH59">
+        <v>36</v>
+      </c>
+      <c r="AI59">
         <v>990</v>
       </c>
-      <c r="AI59">
-        <v>1000</v>
-      </c>
       <c r="AJ59">
-        <v>980</v>
+        <v>890</v>
       </c>
       <c r="AK59">
-        <v>970</v>
+        <v>880</v>
       </c>
       <c r="AL59">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AM59">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AN59">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AO59">
-        <v>980</v>
+        <v>880</v>
       </c>
       <c r="AP59">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AQ59">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AR59">
-        <v>2.02</v>
+        <v>13.5</v>
       </c>
       <c r="AS59">
-        <v>1.85</v>
+        <v>7.8</v>
       </c>
       <c r="AT59">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU59">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV59">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW59">
-        <v>1.85</v>
+        <v>7.8</v>
       </c>
       <c r="AX59">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY59">
-        <v>1.96</v>
+        <v>15</v>
       </c>
       <c r="AZ59">
-        <v>1.85</v>
+        <v>7</v>
       </c>
       <c r="BA59">
-        <v>1.85</v>
+        <v>8.4</v>
       </c>
       <c r="BB59">
-        <v>1.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC59">
-        <v>1.81</v>
+        <v>8</v>
       </c>
       <c r="BD59">
-        <v>1.85</v>
+        <v>8.4</v>
       </c>
       <c r="BE59">
-        <v>1.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF59">
-        <v>1.85</v>
+        <v>8.4</v>
       </c>
       <c r="BG59">
-        <v>1.82</v>
+        <v>8</v>
       </c>
       <c r="BH59">
         <v>2.42</v>
@@ -15474,22 +15474,22 @@
         <v>270</v>
       </c>
       <c r="F60">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G60">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H60">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I60">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="J60">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K60">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L60">
         <v>1.4</v>
@@ -15501,145 +15501,145 @@
         <v>3.15</v>
       </c>
       <c r="O60">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P60">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q60">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R60">
         <v>1.26</v>
       </c>
       <c r="S60">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T60">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U60">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V60">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="W60">
         <v>1.33</v>
       </c>
       <c r="X60">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="Y60">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="Z60">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AA60">
         <v>1000</v>
       </c>
       <c r="AB60">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AC60">
+        <v>38</v>
+      </c>
+      <c r="AD60">
+        <v>60</v>
+      </c>
+      <c r="AE60">
+        <v>1000</v>
+      </c>
+      <c r="AF60">
+        <v>990</v>
+      </c>
+      <c r="AG60">
+        <v>990</v>
+      </c>
+      <c r="AH60">
+        <v>990</v>
+      </c>
+      <c r="AI60">
+        <v>1000</v>
+      </c>
+      <c r="AJ60">
+        <v>1000</v>
+      </c>
+      <c r="AK60">
+        <v>1000</v>
+      </c>
+      <c r="AL60">
+        <v>1000</v>
+      </c>
+      <c r="AM60">
+        <v>1000</v>
+      </c>
+      <c r="AN60">
+        <v>1000</v>
+      </c>
+      <c r="AO60">
+        <v>1000</v>
+      </c>
+      <c r="AP60">
+        <v>2.88</v>
+      </c>
+      <c r="AQ60">
+        <v>1.36</v>
+      </c>
+      <c r="AR60">
+        <v>3</v>
+      </c>
+      <c r="AS60">
+        <v>9.6</v>
+      </c>
+      <c r="AT60">
+        <v>9</v>
+      </c>
+      <c r="AU60">
+        <v>6</v>
+      </c>
+      <c r="AV60">
+        <v>1.41</v>
+      </c>
+      <c r="AW60">
+        <v>8.6</v>
+      </c>
+      <c r="AX60">
+        <v>4.3</v>
+      </c>
+      <c r="AY60">
+        <v>1.48</v>
+      </c>
+      <c r="AZ60">
+        <v>12.5</v>
+      </c>
+      <c r="BA60">
+        <v>12</v>
+      </c>
+      <c r="BB60">
+        <v>13</v>
+      </c>
+      <c r="BC60">
+        <v>12</v>
+      </c>
+      <c r="BD60">
+        <v>13</v>
+      </c>
+      <c r="BE60">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD60">
-        <v>23</v>
-      </c>
-      <c r="AE60">
-        <v>1000</v>
-      </c>
-      <c r="AF60">
-        <v>1000</v>
-      </c>
-      <c r="AG60">
-        <v>1000</v>
-      </c>
-      <c r="AH60">
-        <v>1000</v>
-      </c>
-      <c r="AI60">
-        <v>1000</v>
-      </c>
-      <c r="AJ60">
-        <v>1000</v>
-      </c>
-      <c r="AK60">
-        <v>1000</v>
-      </c>
-      <c r="AL60">
-        <v>1000</v>
-      </c>
-      <c r="AM60">
-        <v>1000</v>
-      </c>
-      <c r="AN60">
-        <v>1000</v>
-      </c>
-      <c r="AO60">
-        <v>1000</v>
-      </c>
-      <c r="AP60">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ60">
-        <v>6.8</v>
-      </c>
-      <c r="AR60">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS60">
-        <v>1.01</v>
-      </c>
-      <c r="AT60">
-        <v>8.4</v>
-      </c>
-      <c r="AU60">
-        <v>5.7</v>
-      </c>
-      <c r="AV60">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW60">
-        <v>1.01</v>
-      </c>
-      <c r="AX60">
-        <v>1.01</v>
-      </c>
-      <c r="AY60">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ60">
-        <v>12</v>
-      </c>
-      <c r="BA60">
-        <v>1.01</v>
-      </c>
-      <c r="BB60">
-        <v>1.01</v>
-      </c>
-      <c r="BC60">
-        <v>1.01</v>
-      </c>
-      <c r="BD60">
-        <v>1.01</v>
-      </c>
-      <c r="BE60">
-        <v>1.01</v>
-      </c>
       <c r="BF60">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BG60">
-        <v>12.5</v>
+        <v>1.51</v>
       </c>
       <c r="BH60">
         <v>1000</v>
       </c>
       <c r="BI60">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ60">
         <v>1000</v>
@@ -15716,31 +15716,31 @@
         <v>271</v>
       </c>
       <c r="F61">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="G61">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="H61">
         <v>3</v>
       </c>
       <c r="I61">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="J61">
-        <v>2.62</v>
+        <v>1.1</v>
       </c>
       <c r="K61">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="L61">
         <v>1.01</v>
       </c>
       <c r="M61">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N61">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O61">
         <v>1.35</v>
@@ -15749,10 +15749,10 @@
         <v>1.79</v>
       </c>
       <c r="Q61">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="R61">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S61">
         <v>3.2</v>
@@ -15764,10 +15764,10 @@
         <v>1.01</v>
       </c>
       <c r="V61">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W61">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="X61">
         <v>1000</v>
@@ -15958,13 +15958,13 @@
         <v>272</v>
       </c>
       <c r="F62">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G62">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H62">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I62">
         <v>4.3</v>
@@ -15973,7 +15973,7 @@
         <v>2.76</v>
       </c>
       <c r="K62">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="L62">
         <v>1.55</v>
@@ -15982,10 +15982,10 @@
         <v>1.09</v>
       </c>
       <c r="N62">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O62">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P62">
         <v>1.48</v>
@@ -16003,10 +16003,10 @@
         <v>2.06</v>
       </c>
       <c r="U62">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V62">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W62">
         <v>1.62</v>
@@ -16203,16 +16203,16 @@
         <v>1.68</v>
       </c>
       <c r="G63">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="H63">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I63">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J63">
-        <v>3.45</v>
+        <v>2.82</v>
       </c>
       <c r="K63">
         <v>4</v>
@@ -16248,10 +16248,10 @@
         <v>1.01</v>
       </c>
       <c r="V63">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W63">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16445,19 +16445,19 @@
         <v>1.45</v>
       </c>
       <c r="G64">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="H64">
+        <v>6.4</v>
+      </c>
+      <c r="I64">
+        <v>12.5</v>
+      </c>
+      <c r="J64">
+        <v>4.3</v>
+      </c>
+      <c r="K64">
         <v>6.6</v>
-      </c>
-      <c r="I64">
-        <v>10</v>
-      </c>
-      <c r="J64">
-        <v>4.8</v>
-      </c>
-      <c r="K64">
-        <v>5.2</v>
       </c>
       <c r="L64">
         <v>1.33</v>
@@ -16466,13 +16466,13 @@
         <v>1.04</v>
       </c>
       <c r="N64">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O64">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P64">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q64">
         <v>1.64</v>
@@ -16493,7 +16493,7 @@
         <v>1.11</v>
       </c>
       <c r="W64">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="X64">
         <v>26</v>
@@ -16520,7 +16520,7 @@
         <v>140</v>
       </c>
       <c r="AF64">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG64">
         <v>10.5</v>
@@ -16538,7 +16538,7 @@
         <v>15.5</v>
       </c>
       <c r="AL64">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM64">
         <v>150</v>
@@ -16553,13 +16553,13 @@
         <v>18.5</v>
       </c>
       <c r="AQ64">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR64">
         <v>10.5</v>
       </c>
       <c r="AS64">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT64">
         <v>8.199999999999999</v>
@@ -16568,10 +16568,10 @@
         <v>10</v>
       </c>
       <c r="AV64">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW64">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX64">
         <v>8.199999999999999</v>
@@ -16583,7 +16583,7 @@
         <v>20</v>
       </c>
       <c r="BA64">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB64">
         <v>11</v>
@@ -16592,10 +16592,10 @@
         <v>13</v>
       </c>
       <c r="BD64">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE64">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF64">
         <v>5.7</v>
@@ -16684,13 +16684,13 @@
         <v>275</v>
       </c>
       <c r="F65">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G65">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H65">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I65">
         <v>3.05</v>
@@ -16699,7 +16699,7 @@
         <v>3.5</v>
       </c>
       <c r="K65">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L65">
         <v>1.32</v>
@@ -16717,7 +16717,7 @@
         <v>1.96</v>
       </c>
       <c r="Q65">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R65">
         <v>1.37</v>
@@ -16735,16 +16735,16 @@
         <v>1.48</v>
       </c>
       <c r="W65">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X65">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y65">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z65">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA65">
         <v>55</v>
@@ -16759,10 +16759,10 @@
         <v>13.5</v>
       </c>
       <c r="AE65">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF65">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG65">
         <v>12.5</v>
@@ -16801,7 +16801,7 @@
         <v>17.5</v>
       </c>
       <c r="AS65">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT65">
         <v>10.5</v>
@@ -16813,7 +16813,7 @@
         <v>11.5</v>
       </c>
       <c r="AW65">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX65">
         <v>15</v>
@@ -16825,19 +16825,19 @@
         <v>14.5</v>
       </c>
       <c r="BA65">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB65">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC65">
         <v>20</v>
       </c>
       <c r="BD65">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE65">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF65">
         <v>16.5</v>
@@ -16864,7 +16864,7 @@
         <v>1.01</v>
       </c>
       <c r="BN65">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO65">
         <v>1.01</v>
